--- a/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2525.13</v>
+        <v>33206.76</v>
       </c>
       <c r="C4" t="n">
-        <v>557424</v>
+        <v>5764752</v>
       </c>
       <c r="D4" t="n">
-        <v>437976</v>
+        <v>4529448</v>
       </c>
       <c r="E4" t="n">
-        <v>141300</v>
+        <v>1440000</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>6180</v>
+        <v>97650</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>10080</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>18870</v>
+        <v>217950</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3816.54</v>
+        <v>40658.76</v>
       </c>
       <c r="C5" t="n">
-        <v>640080</v>
+        <v>5703264</v>
       </c>
       <c r="D5" t="n">
-        <v>502920</v>
+        <v>4481136</v>
       </c>
       <c r="E5" t="n">
-        <v>106200</v>
+        <v>1150200</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>9090</v>
+        <v>97050</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>12750</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>21270</v>
+        <v>252660</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3829.95</v>
+        <v>30954.6</v>
       </c>
       <c r="C6" t="n">
-        <v>396144</v>
+        <v>2499336</v>
       </c>
       <c r="D6" t="n">
-        <v>311256</v>
+        <v>1963764</v>
       </c>
       <c r="E6" t="n">
-        <v>61200</v>
+        <v>254700</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>7710</v>
+        <v>67530</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>5640</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>21210</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2490.39</v>
+        <v>22275.27</v>
       </c>
       <c r="C7" t="n">
-        <v>185976</v>
+        <v>1492344</v>
       </c>
       <c r="D7" t="n">
-        <v>146124</v>
+        <v>1172556</v>
       </c>
       <c r="E7" t="n">
-        <v>31500</v>
+        <v>108900</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4770</v>
+        <v>41430</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8550</v>
+        <v>72180</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1287.27</v>
+        <v>9743.76</v>
       </c>
       <c r="C8" t="n">
-        <v>55440</v>
+        <v>690480</v>
       </c>
       <c r="D8" t="n">
-        <v>43560</v>
+        <v>542520</v>
       </c>
       <c r="E8" t="n">
-        <v>5400</v>
+        <v>34200</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1530</v>
+        <v>12690</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3540</v>
+        <v>37620</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>628.38</v>
+        <v>1022.4</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>94248</v>
       </c>
       <c r="D9" t="n">
-        <v>13860</v>
+        <v>74052</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>900</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>2160</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>840</v>
+        <v>9030</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>385.47</v>
+        <v>234.63</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>19656</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>15444</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>660</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>540</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="11">
@@ -10109,13 +10103,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>216.09</v>
+        <v>219.24</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>5544</v>
       </c>
       <c r="D11" t="n">
-        <v>2376</v>
+        <v>4356</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10124,10 +10118,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.96</v>
+        <v>46.62</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>2016</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>1584</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>169.29</v>
+        <v>14.58</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.93</v>
+        <v>17.82</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1188</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>8.01</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>4.32</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0.72</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1717.44</v>
+        <v>18296.44</v>
       </c>
       <c r="C5" t="n">
-        <v>352044</v>
+        <v>3136795.2</v>
       </c>
       <c r="D5" t="n">
-        <v>166466.52</v>
+        <v>1483256.02</v>
       </c>
       <c r="E5" t="n">
-        <v>11713.86</v>
+        <v>126867.06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4590</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4466.7</v>
+        <v>53058.6</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3063.96</v>
+        <v>24763.68</v>
       </c>
       <c r="C6" t="n">
-        <v>356529.6</v>
+        <v>2249402.4</v>
       </c>
       <c r="D6" t="n">
-        <v>157806.79</v>
+        <v>995628.35</v>
       </c>
       <c r="E6" t="n">
-        <v>10342.8</v>
+        <v>43044.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>385.5</v>
+        <v>3376.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3214.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7847.7</v>
+        <v>54390</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2365.87</v>
+        <v>21161.51</v>
       </c>
       <c r="C7" t="n">
-        <v>185976</v>
+        <v>1492344</v>
       </c>
       <c r="D7" t="n">
-        <v>93227.11</v>
+        <v>748090.73</v>
       </c>
       <c r="E7" t="n">
-        <v>6700.05</v>
+        <v>23163.03</v>
       </c>
       <c r="F7" t="n">
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>715.5</v>
+        <v>6214.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>569.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5130</v>
+        <v>43308</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1287.27</v>
+        <v>9743.76</v>
       </c>
       <c r="C8" t="n">
-        <v>55440</v>
+        <v>690480</v>
       </c>
       <c r="D8" t="n">
-        <v>32060.16</v>
+        <v>399294.72</v>
       </c>
       <c r="E8" t="n">
-        <v>1324.62</v>
+        <v>8389.26</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>994.5</v>
+        <v>8248.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2513.4</v>
+        <v>26710.2</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>628.38</v>
+        <v>1022.4</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>94248</v>
       </c>
       <c r="D9" t="n">
-        <v>11129.58</v>
+        <v>59463.76</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>240.93</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>1836</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11927,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>680.4</v>
+        <v>7314.3</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>385.47</v>
+        <v>234.63</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>19656</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>13436.28</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>660</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>480.6</v>
+        <v>3764.7</v>
       </c>
     </row>
     <row r="11">
@@ -11973,13 +11967,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>216.09</v>
+        <v>219.24</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>5544</v>
       </c>
       <c r="D11" t="n">
-        <v>2134.84</v>
+        <v>3913.87</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11988,10 +11982,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.96</v>
+        <v>46.62</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>2016</v>
       </c>
       <c r="D12" t="n">
-        <v>734.1799999999999</v>
+        <v>1468.37</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>169.29</v>
+        <v>14.58</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1504.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.93</v>
+        <v>17.82</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1154.74</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>8.01</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1171.37</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>4.32</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0.72</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3778374.6</v>
+        <v>40252172.4</v>
       </c>
       <c r="C5" t="n">
-        <v>19362420</v>
+        <v>172523736</v>
       </c>
       <c r="D5" t="n">
-        <v>16868052.47</v>
+        <v>150298332.1</v>
       </c>
       <c r="E5" t="n">
-        <v>2158161.57</v>
+        <v>23373987.13</v>
       </c>
       <c r="F5" t="n">
-        <v>4166.7</v>
+        <v>8333.4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1269823.5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>42076.31</v>
+        <v>499812.01</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>6740712</v>
+        <v>54480096</v>
       </c>
       <c r="C6" t="n">
-        <v>19609128</v>
+        <v>123717132</v>
       </c>
       <c r="D6" t="n">
-        <v>15990562.23</v>
+        <v>100887020.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1905557.47</v>
+        <v>7930481.83</v>
       </c>
       <c r="F6" t="n">
-        <v>16666.8</v>
+        <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>7131.75</v>
+        <v>62465.25</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>889374.42</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>87499.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>73925.33</v>
+        <v>512353.8</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5204915.1</v>
+        <v>46555314.3</v>
       </c>
       <c r="C7" t="n">
-        <v>10228680</v>
+        <v>82078920</v>
       </c>
       <c r="D7" t="n">
-        <v>9446703.26</v>
+        <v>75804033.47</v>
       </c>
       <c r="E7" t="n">
-        <v>1234417.21</v>
+        <v>4267556.65</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13236.75</v>
+        <v>114968.25</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>157524.51</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>81666.2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>48324.6</v>
+        <v>407961.36</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2831994</v>
+        <v>21436272</v>
       </c>
       <c r="C8" t="n">
-        <v>3049200</v>
+        <v>37976400</v>
       </c>
       <c r="D8" t="n">
-        <v>3248656.01</v>
+        <v>40460533.98</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>1545637.26</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>18398.25</v>
+        <v>152597.25</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>14109.15</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>49583.05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>23676.23</v>
+        <v>251610.08</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1382436</v>
+        <v>2249280</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>5183640</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>6025462.4</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>44388.94</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13209</v>
+        <v>33966</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12859,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6409.37</v>
+        <v>68900.71000000001</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>848034</v>
+        <v>516186</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>1081080</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>1361498.25</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>48086.64</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7215</v>
+        <v>12210</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4527.25</v>
+        <v>35463.47</v>
       </c>
     </row>
     <row r="11">
@@ -12905,13 +12899,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>475398</v>
+        <v>482328</v>
       </c>
       <c r="C11" t="n">
-        <v>166320</v>
+        <v>304920</v>
       </c>
       <c r="D11" t="n">
-        <v>216322.93</v>
+        <v>396592.04</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12920,10 +12914,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>4440</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>35042.4</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>345312</v>
+        <v>102564</v>
       </c>
       <c r="C12" t="n">
-        <v>55440</v>
+        <v>110880</v>
       </c>
       <c r="D12" t="n">
-        <v>74394.86</v>
+        <v>148789.73</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>79260.05</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>6660</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>21477.6</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>372438</v>
+        <v>32076</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>152401.13</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>8195.4</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>94446</v>
+        <v>39204</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>83160</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>117009.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>2775</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>2543.4</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>9504</v>
+        <v>17622</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>118694.72</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>9504</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>4804.2</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>1584</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>69930</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3108.6</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>166320</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>240760.08</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>33206.76</v>
+        <v>22119.75</v>
       </c>
       <c r="C4" t="n">
-        <v>5764752</v>
+        <v>2252880</v>
       </c>
       <c r="D4" t="n">
-        <v>4529448</v>
+        <v>1770120</v>
       </c>
       <c r="E4" t="n">
-        <v>1440000</v>
+        <v>820800</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>97650</v>
+        <v>62040</v>
       </c>
       <c r="H4" t="n">
-        <v>10080</v>
+        <v>4470</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>217950</v>
+        <v>223170</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>40658.76</v>
+        <v>5573.52</v>
       </c>
       <c r="C5" t="n">
-        <v>5703264</v>
+        <v>434952</v>
       </c>
       <c r="D5" t="n">
-        <v>4481136</v>
+        <v>341748</v>
       </c>
       <c r="E5" t="n">
-        <v>1150200</v>
+        <v>189900</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>97050</v>
+        <v>13080</v>
       </c>
       <c r="H5" t="n">
-        <v>12750</v>
+        <v>1140</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>252660</v>
+        <v>62820</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>30954.6</v>
+        <v>527.13</v>
       </c>
       <c r="C6" t="n">
-        <v>2499336</v>
+        <v>55440</v>
       </c>
       <c r="D6" t="n">
-        <v>1963764</v>
+        <v>43560</v>
       </c>
       <c r="E6" t="n">
-        <v>254700</v>
+        <v>15300</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>67530</v>
+        <v>1350</v>
       </c>
       <c r="H6" t="n">
-        <v>5640</v>
+        <v>210</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>147000</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>22275.27</v>
+        <v>90.36</v>
       </c>
       <c r="C7" t="n">
-        <v>1492344</v>
+        <v>9576</v>
       </c>
       <c r="D7" t="n">
-        <v>1172556</v>
+        <v>7524</v>
       </c>
       <c r="E7" t="n">
-        <v>108900</v>
+        <v>2700</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>41430</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>72180</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>9743.76</v>
+        <v>6.3</v>
       </c>
       <c r="C8" t="n">
-        <v>690480</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>542520</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>34200</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>12690</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>37620</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1022.4</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>94248</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>74052</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2160</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13791,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9030</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>234.63</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>19656</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>15444</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4230</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,13 +13831,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>219.24</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5544</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>4356</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13852,22 +13846,22 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>30</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3720</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>46.62</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>14.58</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>17.82</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>8.01</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3780</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14106,10 +14100,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14144,10 +14138,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>18296.44</v>
+        <v>2508.08</v>
       </c>
       <c r="C5" t="n">
-        <v>3136795.2</v>
+        <v>239223.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1483256.02</v>
+        <v>113118.59</v>
       </c>
       <c r="E5" t="n">
-        <v>126867.06</v>
+        <v>20945.97</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4590</v>
+        <v>410.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>53058.6</v>
+        <v>13192.2</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>24763.68</v>
+        <v>421.7</v>
       </c>
       <c r="C6" t="n">
-        <v>2249402.4</v>
+        <v>49896</v>
       </c>
       <c r="D6" t="n">
-        <v>995628.35</v>
+        <v>22084.92</v>
       </c>
       <c r="E6" t="n">
-        <v>43044.3</v>
+        <v>2585.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3376.5</v>
+        <v>67.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3214.8</v>
+        <v>119.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>54390</v>
+        <v>3696.3</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>21161.51</v>
+        <v>85.84</v>
       </c>
       <c r="C7" t="n">
-        <v>1492344</v>
+        <v>9576</v>
       </c>
       <c r="D7" t="n">
-        <v>748090.73</v>
+        <v>4800.31</v>
       </c>
       <c r="E7" t="n">
-        <v>23163.03</v>
+        <v>574.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6214.5</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>569.4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>43308</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>9743.76</v>
+        <v>6.3</v>
       </c>
       <c r="C8" t="n">
-        <v>690480</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>399294.72</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>8389.26</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8248.5</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26710.2</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1022.4</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>94248</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>59463.76</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>240.93</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1836</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7314.3</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>234.63</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>19656</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>13436.28</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3764.7</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,13 +14763,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>219.24</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5544</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3913.87</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14784,22 +14778,22 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>30</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3720</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>46.62</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1468.37</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>430.2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>14.58</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1504.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>17.82</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1154.74</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>8.01</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1171.37</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3780</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15038,10 +15032,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15076,10 +15070,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>40252172.4</v>
+        <v>5517784.8</v>
       </c>
       <c r="C5" t="n">
-        <v>172523736</v>
+        <v>13157298</v>
       </c>
       <c r="D5" t="n">
-        <v>150298332.1</v>
+        <v>11462306.52</v>
       </c>
       <c r="E5" t="n">
-        <v>23373987.13</v>
+        <v>3859085.51</v>
       </c>
       <c r="F5" t="n">
-        <v>8333.4</v>
+        <v>5000.04</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1269823.5</v>
+        <v>113537.16</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>499812.01</v>
+        <v>124270.52</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>54480096</v>
+        <v>927748.8</v>
       </c>
       <c r="C6" t="n">
-        <v>123717132</v>
+        <v>2744280</v>
       </c>
       <c r="D6" t="n">
-        <v>100887020.5</v>
+        <v>2237864.94</v>
       </c>
       <c r="E6" t="n">
-        <v>7930481.83</v>
+        <v>476389.37</v>
       </c>
       <c r="F6" t="n">
-        <v>4166.7</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>62465.25</v>
+        <v>1248.75</v>
       </c>
       <c r="H6" t="n">
-        <v>889374.42</v>
+        <v>33115</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>512353.8</v>
+        <v>34819.15</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>46555314.3</v>
+        <v>188852.4</v>
       </c>
       <c r="C7" t="n">
-        <v>82078920</v>
+        <v>526680</v>
       </c>
       <c r="D7" t="n">
-        <v>75804033.47</v>
+        <v>486415.61</v>
       </c>
       <c r="E7" t="n">
-        <v>4267556.65</v>
+        <v>105807.19</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>114968.25</v>
+        <v>83.25</v>
       </c>
       <c r="H7" t="n">
-        <v>157524.51</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>407961.36</v>
+        <v>3560.76</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>21436272</v>
+        <v>13860</v>
       </c>
       <c r="C8" t="n">
-        <v>37976400</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>40460533.98</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1545637.26</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>152597.25</v>
+        <v>721.5</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>251610.08</v>
+        <v>1203.88</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>2249280</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>5183640</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6025462.4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>33966</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15655,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>68900.71000000001</v>
+        <v>686.72</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>516186</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1081080</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1361498.25</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12210</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>35463.47</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,13 +15695,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>482328</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>304920</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>396592.04</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15716,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4440</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>35042.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>102564</v>
-      </c>
-      <c r="C12" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D12" t="n">
-        <v>148789.73</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6660</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>21477.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>32076</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>8195.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>39204</v>
-      </c>
-      <c r="C14" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>117009.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2543.4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>17622</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4239</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>9504</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4804.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1584</v>
-      </c>
-      <c r="C17" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D17" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>69930</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3108.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D19" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D20" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D24" t="n">
-        <v>240760.08</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5284.89</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1016064</v>
-      </c>
-      <c r="D4" t="n">
-        <v>798336</v>
-      </c>
-      <c r="E4" t="n">
-        <v>276300</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13590</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3450</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>38280</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6753.33</v>
-      </c>
-      <c r="C5" t="n">
-        <v>760536</v>
-      </c>
-      <c r="D5" t="n">
-        <v>597564</v>
-      </c>
-      <c r="E5" t="n">
-        <v>153000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15390</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1980</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>32820</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5800.05</v>
-      </c>
-      <c r="C6" t="n">
-        <v>400680</v>
-      </c>
-      <c r="D6" t="n">
-        <v>314820</v>
-      </c>
-      <c r="E6" t="n">
-        <v>73800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8460</v>
-      </c>
-      <c r="H6" t="n">
-        <v>390</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>19530</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4132.53</v>
-      </c>
-      <c r="C7" t="n">
-        <v>212688</v>
-      </c>
-      <c r="D7" t="n">
-        <v>167112</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4110</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15480</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2723.22</v>
-      </c>
-      <c r="C8" t="n">
-        <v>70056</v>
-      </c>
-      <c r="D8" t="n">
-        <v>55044</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2280</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6150</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1777.86</v>
-      </c>
-      <c r="C9" t="n">
-        <v>30744</v>
-      </c>
-      <c r="D9" t="n">
-        <v>24156</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>450</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>908.1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6552</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5148</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>240</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>537.12</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>401.67</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>366.03</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.76</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>792</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>249.39</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27.45</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3039</v>
-      </c>
-      <c r="C5" t="n">
-        <v>418294.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>197793.68</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16875.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>712.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6892.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4640.04</v>
-      </c>
-      <c r="C6" t="n">
-        <v>360612</v>
-      </c>
-      <c r="D6" t="n">
-        <v>159613.74</v>
-      </c>
-      <c r="E6" t="n">
-        <v>12472.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>423</v>
-      </c>
-      <c r="H6" t="n">
-        <v>222.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7226.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3925.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>212688</v>
-      </c>
-      <c r="D7" t="n">
-        <v>106617.46</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6508.62</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9288</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2723.22</v>
-      </c>
-      <c r="C8" t="n">
-        <v>70056</v>
-      </c>
-      <c r="D8" t="n">
-        <v>40512.38</v>
-      </c>
-      <c r="E8" t="n">
-        <v>662.3099999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1482</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4366.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1777.86</v>
-      </c>
-      <c r="C9" t="n">
-        <v>30744</v>
-      </c>
-      <c r="D9" t="n">
-        <v>19397.27</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>382.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>908.1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6552</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4478.76</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>240</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>186.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>537.12</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2490.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>401.67</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1101.28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>366.03</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1504.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.76</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>769.8200000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>249.39</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27.45</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6685796.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>23006214</v>
-      </c>
-      <c r="D5" t="n">
-        <v>20042434</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3109215.82</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000.04</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>197196.12</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>64924.52</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>10208088</v>
-      </c>
-      <c r="C6" t="n">
-        <v>19833660</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16173660.27</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2297878.13</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7825.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>61499.29</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>68069.86</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8636987.699999999</v>
-      </c>
-      <c r="C7" t="n">
-        <v>11697840</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10803546.82</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1199148.15</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>11405.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>87492.96000000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5991084</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3853080</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4105119.87</v>
-      </c>
-      <c r="E8" t="n">
-        <v>122023.99</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>27417</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>41132.43</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3911292</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1690920</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1965525.17</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7076.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9156.24</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1997820</v>
-      </c>
-      <c r="C10" t="n">
-        <v>360360</v>
-      </c>
-      <c r="D10" t="n">
-        <v>453832.75</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1760.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1181664</v>
-      </c>
-      <c r="C11" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D11" t="n">
-        <v>252376.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>883674</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111592.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>805266</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1081872</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78006.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>548658</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>93852</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>60390</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>22119.75</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2252880</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1770120</v>
-      </c>
-      <c r="E4" t="n">
-        <v>820800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27</v>
-      </c>
-      <c r="G4" t="n">
-        <v>62040</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4470</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>223170</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5573.52</v>
-      </c>
-      <c r="C5" t="n">
-        <v>434952</v>
-      </c>
-      <c r="D5" t="n">
-        <v>341748</v>
-      </c>
-      <c r="E5" t="n">
-        <v>189900</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13080</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1140</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>62820</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>527.13</v>
-      </c>
-      <c r="C6" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D6" t="n">
-        <v>43560</v>
-      </c>
-      <c r="E6" t="n">
-        <v>15300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1350</v>
-      </c>
-      <c r="H6" t="n">
-        <v>210</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9990</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>90.36</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9576</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7524</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2508.08</v>
-      </c>
-      <c r="C5" t="n">
-        <v>239223.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>113118.59</v>
-      </c>
-      <c r="E5" t="n">
-        <v>20945.97</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>410.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>13192.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>421.7</v>
-      </c>
-      <c r="C6" t="n">
-        <v>49896</v>
-      </c>
-      <c r="D6" t="n">
-        <v>22084.92</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2585.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3696.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>85.84</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9576</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4800.31</v>
-      </c>
-      <c r="E7" t="n">
-        <v>574.29</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>127.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>72.90000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
+        <v>282.6</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5517784.8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>13157298</v>
-      </c>
-      <c r="D5" t="n">
-        <v>11462306.52</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3859085.51</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000.04</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>113537.16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>124270.52</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>927748.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2744280</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2237864.94</v>
-      </c>
-      <c r="E6" t="n">
-        <v>476389.37</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1248.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>33115</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>34819.15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>188852.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>526680</v>
-      </c>
-      <c r="D7" t="n">
-        <v>486415.61</v>
-      </c>
-      <c r="E7" t="n">
-        <v>105807.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3560.76</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>13860</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>721.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1203.88</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>686.72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>282.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>70620</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
         <v>35</v>
@@ -576,7 +576,7 @@
         <v>71400</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>19</v>
@@ -614,7 +614,7 @@
         <v>21090</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
         <v>11</v>
@@ -690,7 +690,7 @@
         <v>5400</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
@@ -804,7 +804,7 @@
         <v>930</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1546,7 +1546,7 @@
         <v>5610</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1622,7 +1622,7 @@
         <v>4800</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1736,7 +1736,7 @@
         <v>870</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>3197.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>0.5</v>
@@ -2554,7 +2554,7 @@
         <v>4080</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
@@ -2668,7 +2668,7 @@
         <v>870</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>884643.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>29166.5</v>
@@ -3486,7 +3486,7 @@
         <v>1128732</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>49583.05</v>
@@ -3600,7 +3600,7 @@
         <v>240685.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>10080</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>12750</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -9934,7 +9934,7 @@
         <v>5640</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -10010,7 +10010,7 @@
         <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -10828,7 +10828,7 @@
         <v>25704</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>5.7</v>
@@ -10866,7 +10866,7 @@
         <v>12021.3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
         <v>5.5</v>
@@ -10942,7 +10942,7 @@
         <v>4590</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
@@ -11056,7 +11056,7 @@
         <v>930</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -11760,7 +11760,7 @@
         <v>4590</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -11798,7 +11798,7 @@
         <v>3214.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
@@ -11874,7 +11874,7 @@
         <v>51</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
@@ -12692,7 +12692,7 @@
         <v>1269823.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>122499.3</v>
@@ -12730,7 +12730,7 @@
         <v>889374.42</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>268331</v>
       </c>
       <c r="J6" t="n">
         <v>87499.5</v>
@@ -12806,7 +12806,7 @@
         <v>14109.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>49583.05</v>
@@ -13586,7 +13586,7 @@
         <v>4470</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -16420,7 +16420,7 @@
         <v>7111011.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>332498.1</v>
@@ -16458,7 +16458,7 @@
         <v>3325692.64</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>536662</v>
       </c>
       <c r="J6" t="n">
         <v>320831.5</v>
@@ -16534,7 +16534,7 @@
         <v>1269823.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>827992.8</v>
       </c>
       <c r="J8" t="n">
         <v>198332.2</v>
@@ -16648,7 +16648,7 @@
         <v>257284.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>116666</v>
@@ -17314,7 +17314,7 @@
         <v>15720</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
@@ -17390,7 +17390,7 @@
         <v>3240</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -18322,7 +18322,7 @@
         <v>1846.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -19254,7 +19254,7 @@
         <v>510917.22</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>174999</v>
@@ -20110,7 +20110,7 @@
         <v>28020</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>10</v>

--- a/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>867</v>
       </c>
       <c r="L4" t="n">
         <v>1256010</v>
@@ -582,7 +582,7 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="L5" t="n">
         <v>911640</v>
@@ -620,7 +620,7 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>437</v>
       </c>
       <c r="L6" t="n">
         <v>593760</v>
@@ -658,7 +658,7 @@
         <v>11</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="L7" t="n">
         <v>360930</v>
@@ -696,7 +696,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="L8" t="n">
         <v>248850</v>
@@ -734,7 +734,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L9" t="n">
         <v>192750</v>
@@ -772,7 +772,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L10" t="n">
         <v>114870</v>
@@ -810,7 +810,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
         <v>54150</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L12" t="n">
         <v>20010</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>8310</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4380</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1320</v>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L4" t="n">
         <v>32250</v>
@@ -1514,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
         <v>47940</v>
@@ -1552,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
         <v>55530</v>
@@ -1590,7 +1590,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
         <v>48540</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
         <v>63600</v>
@@ -1666,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
         <v>93720</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L10" t="n">
         <v>61440</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
         <v>29760</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
         <v>12990</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>5550</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>3660</v>
@@ -2446,7 +2446,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="L5" t="n">
         <v>10067.4</v>
@@ -2484,7 +2484,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="L6" t="n">
         <v>20546.1</v>
@@ -2522,7 +2522,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>18.04</v>
       </c>
       <c r="L7" t="n">
         <v>29124</v>
@@ -2560,7 +2560,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="L8" t="n">
         <v>45156</v>
@@ -2598,7 +2598,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
         <v>75913.2</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L10" t="n">
         <v>54681.6</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
         <v>29760</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
         <v>12990</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>5550</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>3660</v>
@@ -3378,7 +3378,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>268808.4</v>
       </c>
       <c r="L5" t="n">
         <v>94834.91</v>
@@ -3416,7 +3416,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>526949.8</v>
       </c>
       <c r="L6" t="n">
         <v>193544.26</v>
@@ -3454,7 +3454,7 @@
         <v>163332.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>384865.36</v>
       </c>
       <c r="L7" t="n">
         <v>274348.08</v>
@@ -3492,7 +3492,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>595218.6</v>
       </c>
       <c r="L8" t="n">
         <v>425369.52</v>
@@ -3530,7 +3530,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>810692</v>
       </c>
       <c r="L9" t="n">
         <v>715102.34</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>746690</v>
       </c>
       <c r="L10" t="n">
         <v>515100.67</v>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>298676</v>
       </c>
       <c r="L11" t="n">
         <v>280339.2</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>192006</v>
       </c>
       <c r="L12" t="n">
         <v>122365.8</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L13" t="n">
         <v>52281</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L15" t="n">
         <v>34477.2</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L4" t="n">
         <v>103050</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>35070</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>8190</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="L5" t="n">
         <v>7364.7</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
         <v>3030.3</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>134404.2</v>
       </c>
       <c r="L5" t="n">
         <v>69375.47</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27734.2</v>
       </c>
       <c r="L6" t="n">
         <v>28545.43</v>
@@ -7068,7 +7068,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L4" t="n">
         <v>55230</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>14040</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>2640</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>510</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="L5" t="n">
         <v>2948.4</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="L6" t="n">
         <v>976.8</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="n">
         <v>306</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>80642.52</v>
       </c>
       <c r="L5" t="n">
         <v>27773.93</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>41601.3</v>
       </c>
       <c r="L6" t="n">
         <v>9201.459999999999</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34987.76</v>
       </c>
       <c r="L7" t="n">
         <v>2882.52</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="L4" t="n">
         <v>217950</v>
@@ -9902,7 +9902,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="L5" t="n">
         <v>252660</v>
@@ -9940,7 +9940,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="L6" t="n">
         <v>147000</v>
@@ -9978,7 +9978,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="L7" t="n">
         <v>72180</v>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L8" t="n">
         <v>37620</v>
@@ -10054,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>9030</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>4230</v>
@@ -10320,7 +10320,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>510</v>
@@ -10834,7 +10834,7 @@
         <v>5.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>289.8</v>
       </c>
       <c r="L5" t="n">
         <v>191444.4</v>
@@ -10872,7 +10872,7 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>284.05</v>
       </c>
       <c r="L6" t="n">
         <v>219691.2</v>
@@ -10910,7 +10910,7 @@
         <v>7.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>265.68</v>
       </c>
       <c r="L7" t="n">
         <v>216558</v>
@@ -10948,7 +10948,7 @@
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="L8" t="n">
         <v>176683.5</v>
@@ -10986,7 +10986,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L9" t="n">
         <v>156127.5</v>
@@ -11024,7 +11024,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L10" t="n">
         <v>102234.3</v>
@@ -11062,7 +11062,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
         <v>54150</v>
@@ -11100,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L12" t="n">
         <v>20010</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>8310</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4380</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1320</v>
@@ -11766,7 +11766,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>107.52</v>
       </c>
       <c r="L5" t="n">
         <v>53058.6</v>
@@ -11804,7 +11804,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>85.8</v>
       </c>
       <c r="L6" t="n">
         <v>54390</v>
@@ -11842,7 +11842,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>68.06</v>
       </c>
       <c r="L7" t="n">
         <v>43308</v>
@@ -11880,7 +11880,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="L8" t="n">
         <v>26710.2</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>7314.3</v>
@@ -11956,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>3764.7</v>
@@ -12184,7 +12184,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>510</v>
@@ -12698,7 +12698,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2293831.68</v>
       </c>
       <c r="L5" t="n">
         <v>499812.01</v>
@@ -12736,7 +12736,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1830457.2</v>
       </c>
       <c r="L6" t="n">
         <v>512353.8</v>
@@ -12774,7 +12774,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1451992.04</v>
       </c>
       <c r="L7" t="n">
         <v>407961.36</v>
@@ -12812,7 +12812,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>672021</v>
       </c>
       <c r="L8" t="n">
         <v>251610.08</v>
@@ -12850,7 +12850,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>128004</v>
       </c>
       <c r="L9" t="n">
         <v>68900.71000000001</v>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L10" t="n">
         <v>35463.47</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>4804.2</v>
@@ -13592,7 +13592,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="L4" t="n">
         <v>223170</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
         <v>62820</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="L5" t="n">
         <v>13192.2</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>170245.32</v>
       </c>
       <c r="L5" t="n">
         <v>124270.52</v>
@@ -16426,7 +16426,7 @@
         <v>332498.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6182593.2</v>
       </c>
       <c r="L5" t="n">
         <v>1803406.25</v>
@@ -16464,7 +16464,7 @@
         <v>320831.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6059922.7</v>
       </c>
       <c r="L6" t="n">
         <v>2069491.1</v>
@@ -16502,7 +16502,7 @@
         <v>449164.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5668017.12</v>
       </c>
       <c r="L7" t="n">
         <v>2039976.36</v>
@@ -16540,7 +16540,7 @@
         <v>198332.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4032126</v>
       </c>
       <c r="L8" t="n">
         <v>1664358.57</v>
@@ -16578,7 +16578,7 @@
         <v>221665.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2922758</v>
       </c>
       <c r="L9" t="n">
         <v>1470721.05</v>
@@ -16616,7 +16616,7 @@
         <v>58333</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2048064</v>
       </c>
       <c r="L10" t="n">
         <v>963047.11</v>
@@ -16654,7 +16654,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>768024</v>
       </c>
       <c r="L11" t="n">
         <v>510093</v>
@@ -16692,7 +16692,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>277342</v>
       </c>
       <c r="L12" t="n">
         <v>188494.2</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L13" t="n">
         <v>78280.2</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L15" t="n">
         <v>41259.6</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>12434.4</v>
@@ -17320,7 +17320,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="L4" t="n">
         <v>200850</v>
@@ -17358,7 +17358,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="L5" t="n">
         <v>270810</v>
@@ -17396,7 +17396,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="L6" t="n">
         <v>260580</v>
@@ -17434,7 +17434,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="L7" t="n">
         <v>202800</v>
@@ -17472,7 +17472,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="L8" t="n">
         <v>134010</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L9" t="n">
         <v>86400</v>
@@ -17548,7 +17548,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L10" t="n">
         <v>47550</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L11" t="n">
         <v>20040</v>
@@ -17624,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>4650</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>270</v>
@@ -18290,7 +18290,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>56870.1</v>
@@ -18328,7 +18328,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>139.1</v>
       </c>
       <c r="L6" t="n">
         <v>96414.60000000001</v>
@@ -18366,7 +18366,7 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>173.84</v>
       </c>
       <c r="L7" t="n">
         <v>121680</v>
@@ -18404,7 +18404,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>127.8</v>
       </c>
       <c r="L8" t="n">
         <v>95147.10000000001</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L9" t="n">
         <v>69984</v>
@@ -18480,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L10" t="n">
         <v>42319.5</v>
@@ -18518,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L11" t="n">
         <v>20040</v>
@@ -18556,7 +18556,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>4650</v>
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>270</v>
@@ -19222,7 +19222,7 @@
         <v>87499.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1980221.88</v>
       </c>
       <c r="L5" t="n">
         <v>535716.34</v>
@@ -19260,7 +19260,7 @@
         <v>174999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2967559.4</v>
       </c>
       <c r="L6" t="n">
         <v>908225.53</v>
@@ -19298,7 +19298,7 @@
         <v>204165.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3708702.56</v>
       </c>
       <c r="L7" t="n">
         <v>1146225.6</v>
@@ -19336,7 +19336,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2726485.2</v>
       </c>
       <c r="L8" t="n">
         <v>896285.6800000001</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1962728</v>
       </c>
       <c r="L9" t="n">
         <v>659249.28</v>
@@ -19412,7 +19412,7 @@
         <v>58333</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1258706</v>
       </c>
       <c r="L10" t="n">
         <v>398649.69</v>
@@ -19450,7 +19450,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>469348</v>
       </c>
       <c r="L11" t="n">
         <v>188776.8</v>
@@ -19488,7 +19488,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L12" t="n">
         <v>43803</v>
@@ -19602,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L15" t="n">
         <v>2543.4</v>
@@ -20116,7 +20116,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="L4" t="n">
         <v>360480</v>
@@ -20154,7 +20154,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L5" t="n">
         <v>165690</v>
@@ -20192,7 +20192,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L6" t="n">
         <v>64500</v>
@@ -20230,7 +20230,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>9030</v>
@@ -21086,7 +21086,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>57.54</v>
       </c>
       <c r="L5" t="n">
         <v>34794.9</v>
@@ -21124,7 +21124,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>30.55</v>
       </c>
       <c r="L6" t="n">
         <v>23865</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>5418</v>
@@ -22018,7 +22018,7 @@
         <v>104999.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1227558.36</v>
       </c>
       <c r="L5" t="n">
         <v>327767.96</v>
@@ -22056,7 +22056,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>651753.7</v>
       </c>
       <c r="L6" t="n">
         <v>224808.3</v>
@@ -22094,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>87469.39999999999</v>
       </c>
       <c r="L7" t="n">
         <v>51037.56</v>

--- a/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>152931.78</v>
+        <v>152782.29</v>
       </c>
       <c r="C4" t="n">
         <v>30154824</v>
@@ -532,7 +537,7 @@
         <v>156</v>
       </c>
       <c r="G4" t="n">
-        <v>472440</v>
+        <v>470070</v>
       </c>
       <c r="H4" t="n">
         <v>70620</v>
@@ -544,10 +549,13 @@
         <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="L4" t="n">
-        <v>1256010</v>
+        <v>1253130</v>
+      </c>
+      <c r="M4" t="n">
+        <v>69570</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>113909.58</v>
+        <v>113784.21</v>
       </c>
       <c r="C5" t="n">
         <v>19073376</v>
@@ -570,7 +578,7 @@
         <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>347640</v>
+        <v>346140</v>
       </c>
       <c r="H5" t="n">
         <v>71400</v>
@@ -582,10 +590,13 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="L5" t="n">
-        <v>911640</v>
+        <v>909630</v>
+      </c>
+      <c r="M5" t="n">
+        <v>44400</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>84418.28999999999</v>
+        <v>84294.63</v>
       </c>
       <c r="C6" t="n">
         <v>10488744</v>
@@ -608,7 +619,7 @@
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>249570</v>
+        <v>248820</v>
       </c>
       <c r="H6" t="n">
         <v>21090</v>
@@ -620,10 +631,13 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L6" t="n">
-        <v>593760</v>
+        <v>592020</v>
+      </c>
+      <c r="M6" t="n">
+        <v>21510</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>66701.88</v>
+        <v>66656.97</v>
       </c>
       <c r="C7" t="n">
         <v>6697656</v>
@@ -646,7 +660,7 @@
         <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>153660</v>
+        <v>153210</v>
       </c>
       <c r="H7" t="n">
         <v>5160</v>
@@ -661,7 +675,10 @@
         <v>324</v>
       </c>
       <c r="L7" t="n">
-        <v>360930</v>
+        <v>359910</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13290</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +686,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>45772.74</v>
+        <v>45772.47</v>
       </c>
       <c r="C8" t="n">
         <v>4033512</v>
@@ -684,7 +701,7 @@
         <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>115110</v>
+        <v>114660</v>
       </c>
       <c r="H8" t="n">
         <v>5400</v>
@@ -699,7 +716,10 @@
         <v>210</v>
       </c>
       <c r="L8" t="n">
-        <v>248850</v>
+        <v>248160</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9960</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +727,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>28622.34</v>
+        <v>28622.25</v>
       </c>
       <c r="C9" t="n">
         <v>2162160</v>
@@ -722,7 +742,7 @@
         <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>77610</v>
+        <v>77280</v>
       </c>
       <c r="H9" t="n">
         <v>4260</v>
@@ -737,7 +757,10 @@
         <v>137</v>
       </c>
       <c r="L9" t="n">
-        <v>192750</v>
+        <v>192390</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5130</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +768,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>18588.96</v>
+        <v>18588.69</v>
       </c>
       <c r="C10" t="n">
         <v>1226232</v>
@@ -775,7 +798,10 @@
         <v>96</v>
       </c>
       <c r="L10" t="n">
-        <v>114870</v>
+        <v>114780</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="11">
@@ -813,7 +839,10 @@
         <v>36</v>
       </c>
       <c r="L11" t="n">
-        <v>54150</v>
+        <v>53850</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3120</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>13</v>
       </c>
       <c r="L12" t="n">
-        <v>20010</v>
+        <v>19830</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1830</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>8310</v>
       </c>
+      <c r="M13" t="n">
+        <v>990</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>2940</v>
       </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>4380</v>
       </c>
+      <c r="M15" t="n">
+        <v>2700</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>1320</v>
       </c>
+      <c r="M16" t="n">
+        <v>870</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>1080</v>
       </c>
+      <c r="M17" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1464,7 +1541,7 @@
         <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>9150</v>
+        <v>9270</v>
       </c>
       <c r="H4" t="n">
         <v>3270</v>
@@ -1479,7 +1556,10 @@
         <v>20</v>
       </c>
       <c r="L4" t="n">
-        <v>32250</v>
+        <v>32340</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11190</v>
       </c>
     </row>
     <row r="5">
@@ -1487,7 +1567,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3005.55</v>
+        <v>3005.46</v>
       </c>
       <c r="C5" t="n">
         <v>813960</v>
@@ -1517,7 +1597,10 @@
         <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>47940</v>
+        <v>48270</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14100</v>
       </c>
     </row>
     <row r="6">
@@ -1540,7 +1623,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>22470</v>
+        <v>22530</v>
       </c>
       <c r="H6" t="n">
         <v>5610</v>
@@ -1555,7 +1638,10 @@
         <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>55530</v>
+        <v>55590</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7080</v>
       </c>
     </row>
     <row r="7">
@@ -1578,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>17790</v>
+        <v>17820</v>
       </c>
       <c r="H7" t="n">
         <v>3180</v>
@@ -1593,7 +1679,10 @@
         <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>48540</v>
+        <v>48600</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4560</v>
       </c>
     </row>
     <row r="8">
@@ -1616,7 +1705,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>25410</v>
+        <v>25470</v>
       </c>
       <c r="H8" t="n">
         <v>4800</v>
@@ -1631,7 +1720,10 @@
         <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>63600</v>
+        <v>63780</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="9">
@@ -1654,7 +1746,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>33420</v>
+        <v>33390</v>
       </c>
       <c r="H9" t="n">
         <v>4200</v>
@@ -1669,7 +1761,10 @@
         <v>38</v>
       </c>
       <c r="L9" t="n">
-        <v>93720</v>
+        <v>93810</v>
+      </c>
+      <c r="M9" t="n">
+        <v>960</v>
       </c>
     </row>
     <row r="10">
@@ -1707,7 +1802,10 @@
         <v>35</v>
       </c>
       <c r="L10" t="n">
-        <v>61440</v>
+        <v>61500</v>
+      </c>
+      <c r="M10" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="11">
@@ -1730,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>13020</v>
+        <v>13050</v>
       </c>
       <c r="H11" t="n">
         <v>870</v>
@@ -1745,7 +1843,10 @@
         <v>14</v>
       </c>
       <c r="L11" t="n">
-        <v>29760</v>
+        <v>29850</v>
+      </c>
+      <c r="M11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="12">
@@ -1783,7 +1884,10 @@
         <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>12990</v>
+        <v>13020</v>
+      </c>
+      <c r="M12" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="13">
@@ -1823,6 +1927,9 @@
       <c r="L13" t="n">
         <v>5550</v>
       </c>
+      <c r="M13" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1861,6 +1968,9 @@
       <c r="L14" t="n">
         <v>1620</v>
       </c>
+      <c r="M14" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>3660</v>
       </c>
+      <c r="M15" t="n">
+        <v>2580</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>750</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>630</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1352.5</v>
+        <v>1352.46</v>
       </c>
       <c r="C5" t="n">
         <v>447678</v>
@@ -2446,10 +2598,13 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>12.6</v>
+        <v>9.93</v>
       </c>
       <c r="L5" t="n">
-        <v>10067.4</v>
+        <v>10136.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>282</v>
       </c>
     </row>
     <row r="6">
@@ -2472,22 +2627,25 @@
         <v>0.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1123.5</v>
+        <v>1126.5</v>
       </c>
       <c r="H6" t="n">
         <v>3197.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>24.7</v>
+        <v>19.27</v>
       </c>
       <c r="L6" t="n">
-        <v>20546.1</v>
+        <v>20568.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>566.4</v>
       </c>
     </row>
     <row r="7">
@@ -2510,7 +2668,7 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2668.5</v>
+        <v>2673</v>
       </c>
       <c r="H7" t="n">
         <v>2321.4</v>
@@ -2522,10 +2680,13 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>18.04</v>
+        <v>14.04</v>
       </c>
       <c r="L7" t="n">
-        <v>29124</v>
+        <v>29160</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1596</v>
       </c>
     </row>
     <row r="8">
@@ -2548,22 +2709,25 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>16516.5</v>
+        <v>16555.5</v>
       </c>
       <c r="H8" t="n">
         <v>4080</v>
       </c>
       <c r="I8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>27.9</v>
+        <v>22.82</v>
       </c>
       <c r="L8" t="n">
-        <v>45156</v>
+        <v>45283.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1080</v>
       </c>
     </row>
     <row r="9">
@@ -2586,7 +2750,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>28407</v>
+        <v>28381.5</v>
       </c>
       <c r="H9" t="n">
         <v>4200</v>
@@ -2598,10 +2762,13 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>38</v>
+        <v>30.51</v>
       </c>
       <c r="L9" t="n">
-        <v>75913.2</v>
+        <v>75986.10000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>960</v>
       </c>
     </row>
     <row r="10">
@@ -2636,10 +2803,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>35</v>
+        <v>30.45</v>
       </c>
       <c r="L10" t="n">
-        <v>54681.6</v>
+        <v>54735</v>
+      </c>
+      <c r="M10" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="11">
@@ -2662,22 +2832,25 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>13020</v>
+        <v>13050</v>
       </c>
       <c r="H11" t="n">
         <v>870</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>12.58</v>
       </c>
       <c r="L11" t="n">
-        <v>29760</v>
+        <v>29850</v>
+      </c>
+      <c r="M11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="12">
@@ -2712,10 +2885,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>9</v>
+        <v>8.34</v>
       </c>
       <c r="L12" t="n">
-        <v>12990</v>
+        <v>13020</v>
+      </c>
+      <c r="M12" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="13">
@@ -2750,10 +2926,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="L13" t="n">
         <v>5550</v>
+      </c>
+      <c r="M13" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="14">
@@ -2793,6 +2972,9 @@
       <c r="L14" t="n">
         <v>1620</v>
       </c>
+      <c r="M14" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2826,10 +3008,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
         <v>3660</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2580</v>
       </c>
     </row>
     <row r="16">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>750</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>630</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,16 +3575,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>2975494.5</v>
+        <v>2975405.4</v>
       </c>
       <c r="C5" t="n">
-        <v>24622290</v>
+        <v>18802476</v>
       </c>
       <c r="D5" t="n">
-        <v>21450318.69</v>
+        <v>40644046.08</v>
       </c>
       <c r="E5" t="n">
-        <v>10461596.75</v>
+        <v>19589941.8</v>
       </c>
       <c r="F5" t="n">
         <v>8333.4</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>283842.9</v>
+        <v>5848200</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>268808.4</v>
+        <v>482161.08</v>
       </c>
       <c r="L5" t="n">
-        <v>94834.91</v>
+        <v>1824606</v>
+      </c>
+      <c r="M5" t="n">
+        <v>84600</v>
       </c>
     </row>
     <row r="6">
@@ -3392,34 +3619,37 @@
         <v>9406267.199999999</v>
       </c>
       <c r="C6" t="n">
-        <v>43509312</v>
+        <v>33225292.8</v>
       </c>
       <c r="D6" t="n">
-        <v>35480331.47</v>
+        <v>67228102.66</v>
       </c>
       <c r="E6" t="n">
-        <v>14880162.02</v>
+        <v>27863959.5</v>
       </c>
       <c r="F6" t="n">
         <v>29166.9</v>
       </c>
       <c r="G6" t="n">
-        <v>20784.75</v>
+        <v>60831</v>
       </c>
       <c r="H6" t="n">
-        <v>884643.7</v>
+        <v>18226890</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>526949.8</v>
+        <v>935479.9</v>
       </c>
       <c r="L6" t="n">
-        <v>193544.26</v>
+        <v>3702294</v>
+      </c>
+      <c r="M6" t="n">
+        <v>169920</v>
       </c>
     </row>
     <row r="7">
@@ -3430,34 +3660,37 @@
         <v>13071821.4</v>
       </c>
       <c r="C7" t="n">
-        <v>38142720</v>
+        <v>29127168</v>
       </c>
       <c r="D7" t="n">
-        <v>35226730.85</v>
+        <v>66747580.42</v>
       </c>
       <c r="E7" t="n">
-        <v>10333835.52</v>
+        <v>19350701.55</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>49367.25</v>
+        <v>144342</v>
       </c>
       <c r="H7" t="n">
-        <v>642215.3100000001</v>
+        <v>13231980</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>163332.4</v>
+        <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>384865.36</v>
+        <v>681532.02</v>
       </c>
       <c r="L7" t="n">
-        <v>274348.08</v>
+        <v>5248800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>478800</v>
       </c>
     </row>
     <row r="8">
@@ -3468,34 +3701,37 @@
         <v>12300156</v>
       </c>
       <c r="C8" t="n">
-        <v>36451800</v>
+        <v>27835920</v>
       </c>
       <c r="D8" t="n">
-        <v>38836205.97</v>
+        <v>73586810.88</v>
       </c>
       <c r="E8" t="n">
-        <v>10005967.54</v>
+        <v>18736749.9</v>
       </c>
       <c r="F8" t="n">
         <v>356252.85</v>
       </c>
       <c r="G8" t="n">
-        <v>305555.25</v>
+        <v>893997</v>
       </c>
       <c r="H8" t="n">
-        <v>1128732</v>
+        <v>23256000</v>
       </c>
       <c r="I8" t="n">
-        <v>551995.2</v>
+        <v>285897.73</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>595218.6</v>
+        <v>1107853.7</v>
       </c>
       <c r="L8" t="n">
-        <v>425369.52</v>
+        <v>8151084</v>
+      </c>
+      <c r="M8" t="n">
+        <v>324000</v>
       </c>
     </row>
     <row r="9">
@@ -3506,34 +3742,37 @@
         <v>14886828</v>
       </c>
       <c r="C9" t="n">
-        <v>33679800</v>
+        <v>25719120</v>
       </c>
       <c r="D9" t="n">
-        <v>39149394.71</v>
+        <v>74180240.64</v>
       </c>
       <c r="E9" t="n">
-        <v>6880286.2</v>
+        <v>12883731.75</v>
       </c>
       <c r="F9" t="n">
         <v>416670</v>
       </c>
       <c r="G9" t="n">
-        <v>525529.5</v>
+        <v>1532601</v>
       </c>
       <c r="H9" t="n">
-        <v>1161930</v>
+        <v>23940000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>55416.35</v>
+        <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>810692</v>
+        <v>1481637.78</v>
       </c>
       <c r="L9" t="n">
-        <v>715102.34</v>
+        <v>13677498</v>
+      </c>
+      <c r="M9" t="n">
+        <v>288000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,22 +3783,22 @@
         <v>12944646</v>
       </c>
       <c r="C10" t="n">
-        <v>25225200</v>
+        <v>19262880</v>
       </c>
       <c r="D10" t="n">
-        <v>31768292.56</v>
+        <v>60194534.4</v>
       </c>
       <c r="E10" t="n">
-        <v>6684042.96</v>
+        <v>12516255</v>
       </c>
       <c r="F10" t="n">
         <v>333336</v>
       </c>
       <c r="G10" t="n">
-        <v>510600</v>
+        <v>1490400</v>
       </c>
       <c r="H10" t="n">
-        <v>348579</v>
+        <v>7182000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3568,10 +3807,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>746690</v>
+        <v>1478530.2</v>
       </c>
       <c r="L10" t="n">
-        <v>515100.67</v>
+        <v>9852300</v>
+      </c>
+      <c r="M10" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,34 +3824,37 @@
         <v>6643098</v>
       </c>
       <c r="C11" t="n">
-        <v>13860000</v>
+        <v>10584000</v>
       </c>
       <c r="D11" t="n">
-        <v>18026910.99</v>
+        <v>34157376</v>
       </c>
       <c r="E11" t="n">
-        <v>3873229.62</v>
+        <v>7252845.3</v>
       </c>
       <c r="F11" t="n">
         <v>41667</v>
       </c>
       <c r="G11" t="n">
-        <v>240870</v>
+        <v>704700</v>
       </c>
       <c r="H11" t="n">
-        <v>240685.5</v>
+        <v>4959000</v>
       </c>
       <c r="I11" t="n">
-        <v>383330</v>
+        <v>174510.26</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>298676</v>
+        <v>610785.92</v>
       </c>
       <c r="L11" t="n">
-        <v>280339.2</v>
+        <v>5373000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="12">
@@ -3620,22 +3865,22 @@
         <v>3497670</v>
       </c>
       <c r="C12" t="n">
-        <v>7623000</v>
+        <v>5821200</v>
       </c>
       <c r="D12" t="n">
-        <v>10229293.9</v>
+        <v>19382457.6</v>
       </c>
       <c r="E12" t="n">
-        <v>2853361.73</v>
+        <v>5343084</v>
       </c>
       <c r="F12" t="n">
         <v>41667</v>
       </c>
       <c r="G12" t="n">
-        <v>106560</v>
+        <v>311040</v>
       </c>
       <c r="H12" t="n">
-        <v>41497.5</v>
+        <v>855000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3644,10 +3889,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>192006</v>
+        <v>405102.71</v>
       </c>
       <c r="L12" t="n">
-        <v>122365.8</v>
+        <v>2343600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>117000</v>
       </c>
     </row>
     <row r="13">
@@ -3658,22 +3906,22 @@
         <v>1528560</v>
       </c>
       <c r="C13" t="n">
-        <v>2439360</v>
+        <v>1862784</v>
       </c>
       <c r="D13" t="n">
-        <v>3352824.87</v>
+        <v>6352929.79</v>
       </c>
       <c r="E13" t="n">
-        <v>526498.96</v>
+        <v>985899.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>23310</v>
+        <v>68040</v>
       </c>
       <c r="H13" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3682,10 +3930,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>64002</v>
+        <v>138311.77</v>
       </c>
       <c r="L13" t="n">
-        <v>52281</v>
+        <v>999000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>225000</v>
       </c>
     </row>
     <row r="14">
@@ -3696,10 +3947,10 @@
         <v>1180080</v>
       </c>
       <c r="C14" t="n">
-        <v>637560</v>
+        <v>486864</v>
       </c>
       <c r="D14" t="n">
-        <v>897072.0600000001</v>
+        <v>1699771.39</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3708,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8880</v>
+        <v>25920</v>
       </c>
       <c r="H14" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3723,7 +3974,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>15260.4</v>
+        <v>291600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="15">
@@ -3734,22 +3988,22 @@
         <v>432630</v>
       </c>
       <c r="C15" t="n">
-        <v>942480</v>
+        <v>719712</v>
       </c>
       <c r="D15" t="n">
-        <v>1345206.82</v>
+        <v>2548896.77</v>
       </c>
       <c r="E15" t="n">
-        <v>197752.16</v>
+        <v>370302.3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H15" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3758,10 +4012,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>21334</v>
+        <v>47876.22</v>
       </c>
       <c r="L15" t="n">
-        <v>34477.2</v>
+        <v>658800</v>
+      </c>
+      <c r="M15" t="n">
+        <v>774000</v>
       </c>
     </row>
     <row r="16">
@@ -3772,10 +4029,10 @@
         <v>266706</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3799,7 +4056,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7065</v>
+        <v>135000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3822,10 +4082,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3837,7 +4097,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>5934.6</v>
+        <v>113400</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3877,6 +4140,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3915,6 +4181,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>30540</v>
+        <v>30600</v>
       </c>
       <c r="H4" t="n">
         <v>1740</v>
@@ -4275,7 +4568,10 @@
         <v>44</v>
       </c>
       <c r="L4" t="n">
-        <v>103050</v>
+        <v>103260</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4298,7 +4594,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>9840</v>
+        <v>9870</v>
       </c>
       <c r="H5" t="n">
         <v>480</v>
@@ -4313,7 +4609,10 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>35070</v>
+        <v>35310</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4353,6 +4652,9 @@
       <c r="L6" t="n">
         <v>8190</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>1560</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>360</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>150</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.3</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>7364.7</v>
+        <v>7415.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>3030.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5323,6 +5697,9 @@
       <c r="L7" t="n">
         <v>936</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>255.6</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>121.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>2894948.1</v>
       </c>
       <c r="C5" t="n">
-        <v>12455982</v>
+        <v>9511840.800000001</v>
       </c>
       <c r="D5" t="n">
-        <v>10851337.69</v>
+        <v>20561105.66</v>
       </c>
       <c r="E5" t="n">
-        <v>2395925.13</v>
+        <v>4486507.65</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>47805.12</v>
+        <v>984960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>134404.2</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>69375.47</v>
+        <v>1334718</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>314265.6</v>
       </c>
       <c r="C6" t="n">
-        <v>4191264</v>
+        <v>3200601.6</v>
       </c>
       <c r="D6" t="n">
-        <v>3417830.1</v>
+        <v>6476101.63</v>
       </c>
       <c r="E6" t="n">
-        <v>1345099.39</v>
+        <v>2518776</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1498.5</v>
+        <v>4374</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>27734.2</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>28545.43</v>
+        <v>545454</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>68280.3</v>
       </c>
       <c r="C7" t="n">
-        <v>748440</v>
+        <v>571536</v>
       </c>
       <c r="D7" t="n">
-        <v>691222.1899999999</v>
+        <v>1309727.23</v>
       </c>
       <c r="E7" t="n">
-        <v>70538.13</v>
+        <v>132086.7</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>666</v>
+        <v>1944</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6253,7 +6699,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8817.120000000001</v>
+        <v>168480</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6264,10 +6713,10 @@
         <v>38610</v>
       </c>
       <c r="C8" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D8" t="n">
-        <v>88599.71000000001</v>
+        <v>167878.66</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2525.25</v>
+        <v>7371</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2407.75</v>
+        <v>46008</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6302,13 +6754,13 @@
         <v>24552</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6329,7 +6781,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1144.53</v>
+        <v>21870</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>43050</v>
+        <v>43110</v>
       </c>
       <c r="H4" t="n">
         <v>3480</v>
@@ -7071,7 +7580,10 @@
         <v>66</v>
       </c>
       <c r="L4" t="n">
-        <v>55230</v>
+        <v>55260</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7111,6 +7623,9 @@
       <c r="L5" t="n">
         <v>14040</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>2640</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>510</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3.78</v>
+        <v>2.98</v>
       </c>
       <c r="L5" t="n">
         <v>2948.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="L6" t="n">
         <v>976.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
         <v>306</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8157,6 +8750,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>2313214.2</v>
       </c>
       <c r="C5" t="n">
-        <v>8278578</v>
+        <v>6321823.2</v>
       </c>
       <c r="D5" t="n">
-        <v>7212088.58</v>
+        <v>13665459.46</v>
       </c>
       <c r="E5" t="n">
-        <v>695001.1800000001</v>
+        <v>1301429.7</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>245001.24</v>
+        <v>5047920</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>80642.52</v>
+        <v>144648.32</v>
       </c>
       <c r="L5" t="n">
-        <v>27773.93</v>
+        <v>530712</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>658627.2</v>
       </c>
       <c r="C6" t="n">
-        <v>2419956</v>
+        <v>1847966.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1973390</v>
+        <v>3739177.73</v>
       </c>
       <c r="E6" t="n">
-        <v>252206.14</v>
+        <v>472270.5</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2608.5</v>
+        <v>7614</v>
       </c>
       <c r="H6" t="n">
-        <v>70960.72</v>
+        <v>1462050</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>41601.3</v>
+        <v>73853.67999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>9201.459999999999</v>
+        <v>175824</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,19 +9684,19 @@
         <v>150103.8</v>
       </c>
       <c r="C7" t="n">
-        <v>360360</v>
+        <v>275184</v>
       </c>
       <c r="D7" t="n">
-        <v>332810.68</v>
+        <v>630609.41</v>
       </c>
       <c r="E7" t="n">
-        <v>35269.06</v>
+        <v>66043.35000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2164.5</v>
+        <v>6318</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>34987.76</v>
+        <v>61957.46</v>
       </c>
       <c r="L7" t="n">
-        <v>2882.52</v>
+        <v>55080</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,10 +9725,10 @@
         <v>26334</v>
       </c>
       <c r="C8" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D8" t="n">
-        <v>29533.24</v>
+        <v>55959.55</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -9087,6 +9752,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>97650</v>
+        <v>97740</v>
       </c>
       <c r="H4" t="n">
-        <v>10080</v>
+        <v>10050</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -9867,7 +10592,10 @@
         <v>224</v>
       </c>
       <c r="L4" t="n">
-        <v>217950</v>
+        <v>218280</v>
+      </c>
+      <c r="M4" t="n">
+        <v>18540</v>
       </c>
     </row>
     <row r="5">
@@ -9890,7 +10618,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>97050</v>
+        <v>97020</v>
       </c>
       <c r="H5" t="n">
         <v>12750</v>
@@ -9905,7 +10633,10 @@
         <v>256</v>
       </c>
       <c r="L5" t="n">
-        <v>252660</v>
+        <v>252630</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14850</v>
       </c>
     </row>
     <row r="6">
@@ -9928,7 +10659,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>67530</v>
+        <v>67590</v>
       </c>
       <c r="H6" t="n">
         <v>5640</v>
@@ -9943,7 +10674,10 @@
         <v>132</v>
       </c>
       <c r="L6" t="n">
-        <v>147000</v>
+        <v>147120</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6870</v>
       </c>
     </row>
     <row r="7">
@@ -9966,7 +10700,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>41430</v>
+        <v>41550</v>
       </c>
       <c r="H7" t="n">
         <v>780</v>
@@ -9981,7 +10715,10 @@
         <v>83</v>
       </c>
       <c r="L7" t="n">
-        <v>72180</v>
+        <v>72240</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3420</v>
       </c>
     </row>
     <row r="8">
@@ -10016,10 +10753,13 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
         <v>37620</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="9">
@@ -10059,6 +10799,9 @@
       <c r="L9" t="n">
         <v>9030</v>
       </c>
+      <c r="M9" t="n">
+        <v>990</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>4230</v>
       </c>
+      <c r="M10" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>3720</v>
       </c>
+      <c r="M11" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>2280</v>
       </c>
+      <c r="M12" t="n">
+        <v>510</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>870</v>
       </c>
+      <c r="M13" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>270</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>450</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>510</v>
       </c>
+      <c r="M16" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>330</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>51259.31</v>
+        <v>51202.89</v>
       </c>
       <c r="C5" t="n">
         <v>10490356.8</v>
@@ -10828,16 +11628,19 @@
         <v>25704</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>5.7</v>
       </c>
       <c r="K5" t="n">
-        <v>289.8</v>
+        <v>225.41</v>
       </c>
       <c r="L5" t="n">
-        <v>191444.4</v>
+        <v>191022.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>888</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>67534.63</v>
+        <v>67435.7</v>
       </c>
       <c r="C6" t="n">
         <v>9439869.6</v>
@@ -10860,22 +11663,25 @@
         <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>12478.5</v>
+        <v>12441</v>
       </c>
       <c r="H6" t="n">
         <v>12021.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="J6" t="n">
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>284.05</v>
+        <v>221.05</v>
       </c>
       <c r="L6" t="n">
-        <v>219691.2</v>
+        <v>219047.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1720.8</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>63366.79</v>
+        <v>63324.12</v>
       </c>
       <c r="C7" t="n">
         <v>6697656</v>
@@ -10898,7 +11704,7 @@
         <v>8.4</v>
       </c>
       <c r="G7" t="n">
-        <v>23049</v>
+        <v>22981.5</v>
       </c>
       <c r="H7" t="n">
         <v>3766.8</v>
@@ -10910,10 +11716,13 @@
         <v>7.7</v>
       </c>
       <c r="K7" t="n">
-        <v>265.68</v>
+        <v>206.71</v>
       </c>
       <c r="L7" t="n">
-        <v>216558</v>
+        <v>215946</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4651.5</v>
       </c>
     </row>
     <row r="8">
@@ -10921,7 +11730,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>45772.74</v>
+        <v>45772.47</v>
       </c>
       <c r="C8" t="n">
         <v>4033512</v>
@@ -10936,22 +11745,25 @@
         <v>21.85</v>
       </c>
       <c r="G8" t="n">
-        <v>74821.5</v>
+        <v>74529</v>
       </c>
       <c r="H8" t="n">
         <v>4590</v>
       </c>
       <c r="I8" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>189</v>
+        <v>154.56</v>
       </c>
       <c r="L8" t="n">
-        <v>176683.5</v>
+        <v>176193.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5976</v>
       </c>
     </row>
     <row r="9">
@@ -10959,7 +11771,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>28622.34</v>
+        <v>28622.25</v>
       </c>
       <c r="C9" t="n">
         <v>2162160</v>
@@ -10974,7 +11786,7 @@
         <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>65968.5</v>
+        <v>65688</v>
       </c>
       <c r="H9" t="n">
         <v>4260</v>
@@ -10986,10 +11798,13 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>137</v>
+        <v>110.01</v>
       </c>
       <c r="L9" t="n">
-        <v>156127.5</v>
+        <v>155835.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5130</v>
       </c>
     </row>
     <row r="10">
@@ -10997,7 +11812,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>18588.96</v>
+        <v>18588.69</v>
       </c>
       <c r="C10" t="n">
         <v>1226232</v>
@@ -11024,10 +11839,13 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>96</v>
+        <v>83.52</v>
       </c>
       <c r="L10" t="n">
-        <v>102234.3</v>
+        <v>102154.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="11">
@@ -11056,16 +11874,19 @@
         <v>930</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>32.35</v>
       </c>
       <c r="L11" t="n">
-        <v>54150</v>
+        <v>53850</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3120</v>
       </c>
     </row>
     <row r="12">
@@ -11100,10 +11921,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="L12" t="n">
-        <v>20010</v>
+        <v>19830</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1830</v>
       </c>
     </row>
     <row r="13">
@@ -11138,10 +11962,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="L13" t="n">
         <v>8310</v>
+      </c>
+      <c r="M13" t="n">
+        <v>990</v>
       </c>
     </row>
     <row r="14">
@@ -11181,6 +12008,9 @@
       <c r="L14" t="n">
         <v>2940</v>
       </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11214,10 +12044,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="L15" t="n">
         <v>4380</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2700</v>
       </c>
     </row>
     <row r="16">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>1320</v>
       </c>
+      <c r="M16" t="n">
+        <v>870</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>1080</v>
       </c>
+      <c r="M17" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11760,16 +12632,19 @@
         <v>4590</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>107.52</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>53058.6</v>
+        <v>53052.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>297</v>
       </c>
     </row>
     <row r="6">
@@ -11792,22 +12667,25 @@
         <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3376.5</v>
+        <v>3379.5</v>
       </c>
       <c r="H6" t="n">
         <v>3214.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>85.8</v>
+        <v>66.92</v>
       </c>
       <c r="L6" t="n">
-        <v>54390</v>
+        <v>54434.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>549.6</v>
       </c>
     </row>
     <row r="7">
@@ -11830,7 +12708,7 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6214.5</v>
+        <v>6232.5</v>
       </c>
       <c r="H7" t="n">
         <v>569.4</v>
@@ -11842,10 +12720,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>68.06</v>
+        <v>52.95</v>
       </c>
       <c r="L7" t="n">
-        <v>43308</v>
+        <v>43344</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1197</v>
       </c>
     </row>
     <row r="8">
@@ -11874,16 +12755,19 @@
         <v>51</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>31.5</v>
+        <v>26.5</v>
       </c>
       <c r="L8" t="n">
         <v>26710.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1440</v>
       </c>
     </row>
     <row r="9">
@@ -11918,10 +12802,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>4.82</v>
       </c>
       <c r="L9" t="n">
         <v>7314.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>990</v>
       </c>
     </row>
     <row r="10">
@@ -11956,10 +12843,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="L10" t="n">
         <v>3764.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="11">
@@ -11999,6 +12889,9 @@
       <c r="L11" t="n">
         <v>3720</v>
       </c>
+      <c r="M11" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>2280</v>
       </c>
+      <c r="M12" t="n">
+        <v>510</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>870</v>
       </c>
+      <c r="M13" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>270</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>450</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>510</v>
       </c>
+      <c r="M16" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>330</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>40252172.4</v>
       </c>
       <c r="C5" t="n">
-        <v>172523736</v>
+        <v>131745398.4</v>
       </c>
       <c r="D5" t="n">
-        <v>150298332.1</v>
+        <v>284785155.07</v>
       </c>
       <c r="E5" t="n">
-        <v>23373987.13</v>
+        <v>43769135.7</v>
       </c>
       <c r="F5" t="n">
         <v>8333.4</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1269823.5</v>
+        <v>26163000</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2293831.68</v>
+        <v>4114441.22</v>
       </c>
       <c r="L5" t="n">
-        <v>499812.01</v>
+        <v>9549414</v>
+      </c>
+      <c r="M5" t="n">
+        <v>89100</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>54480096</v>
       </c>
       <c r="C6" t="n">
-        <v>123717132</v>
+        <v>94474900.8</v>
       </c>
       <c r="D6" t="n">
-        <v>100887020.5</v>
+        <v>191160642.82</v>
       </c>
       <c r="E6" t="n">
-        <v>7930481.83</v>
+        <v>14850283.5</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>62465.25</v>
+        <v>182493</v>
       </c>
       <c r="H6" t="n">
-        <v>889374.42</v>
+        <v>18324360</v>
       </c>
       <c r="I6" t="n">
-        <v>268331</v>
+        <v>196943.14</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>1830457.2</v>
+        <v>3249561.74</v>
       </c>
       <c r="L6" t="n">
-        <v>512353.8</v>
+        <v>9798192</v>
+      </c>
+      <c r="M6" t="n">
+        <v>164880</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>46555314.3</v>
       </c>
       <c r="C7" t="n">
-        <v>82078920</v>
+        <v>62678448</v>
       </c>
       <c r="D7" t="n">
-        <v>75804033.47</v>
+        <v>143633419.78</v>
       </c>
       <c r="E7" t="n">
-        <v>4267556.65</v>
+        <v>7991245.35</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>114968.25</v>
+        <v>336555</v>
       </c>
       <c r="H7" t="n">
-        <v>157524.51</v>
+        <v>3245580</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1451992.04</v>
+        <v>2571234.42</v>
       </c>
       <c r="L7" t="n">
-        <v>407961.36</v>
+        <v>7801920</v>
+      </c>
+      <c r="M7" t="n">
+        <v>359100</v>
       </c>
     </row>
     <row r="8">
@@ -12788,34 +13741,37 @@
         <v>21436272</v>
       </c>
       <c r="C8" t="n">
-        <v>37976400</v>
+        <v>29000160</v>
       </c>
       <c r="D8" t="n">
-        <v>40460533.98</v>
+        <v>76664586.23999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1545637.26</v>
+        <v>2894294.7</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>152597.25</v>
+        <v>445419</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>672021</v>
+        <v>1286539.78</v>
       </c>
       <c r="L8" t="n">
-        <v>251610.08</v>
+        <v>4807836</v>
+      </c>
+      <c r="M8" t="n">
+        <v>432000</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>2249280</v>
       </c>
       <c r="C9" t="n">
-        <v>5183640</v>
+        <v>3958416</v>
       </c>
       <c r="D9" t="n">
-        <v>6025462.4</v>
+        <v>11417041.15</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>33966</v>
+        <v>99144</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12850,10 +13806,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>128004</v>
+        <v>233942.81</v>
       </c>
       <c r="L9" t="n">
-        <v>68900.71000000001</v>
+        <v>1316574</v>
+      </c>
+      <c r="M9" t="n">
+        <v>297000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,19 +13823,19 @@
         <v>516186</v>
       </c>
       <c r="C10" t="n">
-        <v>1081080</v>
+        <v>825552</v>
       </c>
       <c r="D10" t="n">
-        <v>1361498.25</v>
+        <v>2579765.76</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12210</v>
+        <v>35640</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12888,10 +13847,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>21334</v>
+        <v>42243.72</v>
       </c>
       <c r="L10" t="n">
-        <v>35463.47</v>
+        <v>677646</v>
+      </c>
+      <c r="M10" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,10 +13864,10 @@
         <v>482328</v>
       </c>
       <c r="C11" t="n">
-        <v>304920</v>
+        <v>232848</v>
       </c>
       <c r="D11" t="n">
-        <v>396592.04</v>
+        <v>751462.27</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12914,10 +13876,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12929,7 +13891,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>35042.4</v>
+        <v>669600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,19 +13905,19 @@
         <v>102564</v>
       </c>
       <c r="C12" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D12" t="n">
-        <v>148789.73</v>
+        <v>281926.66</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>21477.6</v>
+        <v>410400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>153000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>32076</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8195.4</v>
+        <v>156600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="14">
@@ -13016,19 +13987,19 @@
         <v>39204</v>
       </c>
       <c r="C14" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D14" t="n">
-        <v>117009.4</v>
+        <v>221709.31</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2543.4</v>
+        <v>48600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>17622</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13081,7 +14055,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4239</v>
+        <v>81000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="16">
@@ -13092,10 +14069,10 @@
         <v>9504</v>
       </c>
       <c r="C16" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D16" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13116,10 +14093,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>4804.2</v>
+        <v>91800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="17">
@@ -13130,10 +14110,10 @@
         <v>1584</v>
       </c>
       <c r="C17" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D17" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13142,7 +14122,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>69930</v>
+        <v>204120</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13157,7 +14137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3108.6</v>
+        <v>59400</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -13168,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13195,6 +14178,9 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13206,10 +14192,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D19" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13233,6 +14219,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D20" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D24" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>62040</v>
+        <v>62070</v>
       </c>
       <c r="H4" t="n">
         <v>4470</v>
@@ -13595,7 +14608,10 @@
         <v>78</v>
       </c>
       <c r="L4" t="n">
-        <v>223170</v>
+        <v>225420</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13618,7 +14634,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>13080</v>
+        <v>13050</v>
       </c>
       <c r="H5" t="n">
         <v>1140</v>
@@ -13633,7 +14649,10 @@
         <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>62820</v>
+        <v>62580</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="H6" t="n">
         <v>210</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9990</v>
+        <v>10350</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>630</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>180</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>90</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>180</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7.98</v>
+        <v>6.29</v>
       </c>
       <c r="L5" t="n">
-        <v>13192.2</v>
+        <v>13141.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="H6" t="n">
         <v>119.7</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3696.3</v>
+        <v>3829.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>378</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>127.8</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>160.2</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>5517784.8</v>
       </c>
       <c r="C5" t="n">
-        <v>13157298</v>
+        <v>10047391.2</v>
       </c>
       <c r="D5" t="n">
-        <v>11462306.52</v>
+        <v>21718768.9</v>
       </c>
       <c r="E5" t="n">
-        <v>3859085.51</v>
+        <v>7226359.65</v>
       </c>
       <c r="F5" t="n">
         <v>5000.04</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>113537.16</v>
+        <v>2339280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>170245.32</v>
+        <v>305368.68</v>
       </c>
       <c r="L5" t="n">
-        <v>124270.52</v>
+        <v>2365524</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>927748.8</v>
       </c>
       <c r="C6" t="n">
-        <v>2744280</v>
+        <v>2095632</v>
       </c>
       <c r="D6" t="n">
-        <v>2237864.94</v>
+        <v>4240304.64</v>
       </c>
       <c r="E6" t="n">
-        <v>476389.37</v>
+        <v>892066.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1248.75</v>
+        <v>4050</v>
       </c>
       <c r="H6" t="n">
-        <v>33115</v>
+        <v>682290</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>34819.15</v>
+        <v>689310</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>188852.4</v>
       </c>
       <c r="C7" t="n">
-        <v>526680</v>
+        <v>402192</v>
       </c>
       <c r="D7" t="n">
-        <v>486415.61</v>
+        <v>921659.9</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83.25</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3560.76</v>
+        <v>68040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1203.88</v>
+        <v>23004</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>686.72</v>
+        <v>13122</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1509.08</v>
+        <v>28836</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>112770484.2</v>
+        <v>112646367.9</v>
       </c>
       <c r="C5" t="n">
-        <v>576969624</v>
+        <v>440594985.6</v>
       </c>
       <c r="D5" t="n">
-        <v>502641399.79</v>
+        <v>952404507.65</v>
       </c>
       <c r="E5" t="n">
-        <v>96257663.76000001</v>
+        <v>180248013.45</v>
       </c>
       <c r="F5" t="n">
         <v>67500.53999999999</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7111011.6</v>
+        <v>146512800</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>332498.1</v>
+        <v>138384.6</v>
       </c>
       <c r="K5" t="n">
-        <v>6182593.2</v>
+        <v>10945056.52</v>
       </c>
       <c r="L5" t="n">
-        <v>1803406.25</v>
+        <v>34384014</v>
+      </c>
+      <c r="M5" t="n">
+        <v>266400</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>148576190.4</v>
+        <v>148358548.8</v>
       </c>
       <c r="C6" t="n">
-        <v>519192828</v>
+        <v>396474523.2</v>
       </c>
       <c r="D6" t="n">
-        <v>423383703.1</v>
+        <v>802227089.66</v>
       </c>
       <c r="E6" t="n">
-        <v>77763558.59999999</v>
+        <v>145616737.5</v>
       </c>
       <c r="F6" t="n">
         <v>133334.4</v>
       </c>
       <c r="G6" t="n">
-        <v>230852.25</v>
+        <v>671814</v>
       </c>
       <c r="H6" t="n">
-        <v>3325692.64</v>
+        <v>68521410</v>
       </c>
       <c r="I6" t="n">
-        <v>536662</v>
+        <v>393886.27</v>
       </c>
       <c r="J6" t="n">
-        <v>320831.5</v>
+        <v>133529</v>
       </c>
       <c r="K6" t="n">
-        <v>6059922.7</v>
+        <v>10733400.91</v>
       </c>
       <c r="L6" t="n">
-        <v>2069491.1</v>
+        <v>39428532</v>
+      </c>
+      <c r="M6" t="n">
+        <v>516240</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>139406929.2</v>
+        <v>139313067.3</v>
       </c>
       <c r="C7" t="n">
-        <v>368371080</v>
+        <v>281301552</v>
       </c>
       <c r="D7" t="n">
-        <v>340209321.43</v>
+        <v>644628340.22</v>
       </c>
       <c r="E7" t="n">
-        <v>57418034.89</v>
+        <v>107518573.8</v>
       </c>
       <c r="F7" t="n">
         <v>350002.8</v>
       </c>
       <c r="G7" t="n">
-        <v>426406.5</v>
+        <v>1241001</v>
       </c>
       <c r="H7" t="n">
-        <v>1042085.22</v>
+        <v>21470760</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>449164.1</v>
+        <v>186940.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5668017.12</v>
+        <v>10037107.87</v>
       </c>
       <c r="L7" t="n">
-        <v>2039976.36</v>
+        <v>38870280</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1395450</v>
       </c>
     </row>
     <row r="8">
@@ -16513,37 +17754,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>100700028</v>
+        <v>100699434</v>
       </c>
       <c r="C8" t="n">
-        <v>221843160</v>
+        <v>169407504</v>
       </c>
       <c r="D8" t="n">
-        <v>236354491.55</v>
+        <v>447844294.66</v>
       </c>
       <c r="E8" t="n">
-        <v>40064544.83</v>
+        <v>75023165.25</v>
       </c>
       <c r="F8" t="n">
         <v>910423.95</v>
       </c>
       <c r="G8" t="n">
-        <v>1384197.75</v>
+        <v>4024566</v>
       </c>
       <c r="H8" t="n">
-        <v>1269823.5</v>
+        <v>26163000</v>
       </c>
       <c r="I8" t="n">
-        <v>827992.8</v>
+        <v>428846.59</v>
       </c>
       <c r="J8" t="n">
-        <v>198332.2</v>
+        <v>82545.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4032126</v>
+        <v>7504815.36</v>
       </c>
       <c r="L8" t="n">
-        <v>1664358.57</v>
+        <v>31714848</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1792800</v>
       </c>
     </row>
     <row r="9">
@@ -16551,37 +17795,40 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>62969148</v>
+        <v>62968950</v>
       </c>
       <c r="C9" t="n">
-        <v>118918800</v>
+        <v>90810720</v>
       </c>
       <c r="D9" t="n">
-        <v>138231196.13</v>
+        <v>261920355.84</v>
       </c>
       <c r="E9" t="n">
-        <v>27254811.12</v>
+        <v>51036201.9</v>
       </c>
       <c r="F9" t="n">
         <v>1291677</v>
       </c>
       <c r="G9" t="n">
-        <v>1220417.25</v>
+        <v>3547152</v>
       </c>
       <c r="H9" t="n">
-        <v>1178529</v>
+        <v>24282000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>221665.4</v>
+        <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>2922758</v>
+        <v>5341694.12</v>
       </c>
       <c r="L9" t="n">
-        <v>1470721.05</v>
+        <v>28050462</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1539000</v>
       </c>
     </row>
     <row r="10">
@@ -16589,37 +17836,40 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>40895712</v>
+        <v>40895118</v>
       </c>
       <c r="C10" t="n">
-        <v>67442760</v>
+        <v>51501744</v>
       </c>
       <c r="D10" t="n">
-        <v>84936544.81999999</v>
+        <v>160937694.72</v>
       </c>
       <c r="E10" t="n">
-        <v>15580071.36</v>
+        <v>29174580</v>
       </c>
       <c r="F10" t="n">
         <v>458337</v>
       </c>
       <c r="G10" t="n">
-        <v>854145</v>
+        <v>2493180</v>
       </c>
       <c r="H10" t="n">
-        <v>356878.5</v>
+        <v>7353000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>2048064</v>
+        <v>4055397.12</v>
       </c>
       <c r="L10" t="n">
-        <v>963047.11</v>
+        <v>18387756</v>
+      </c>
+      <c r="M10" t="n">
+        <v>900000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,34 +17880,37 @@
         <v>23979384</v>
       </c>
       <c r="C11" t="n">
-        <v>30270240</v>
+        <v>23115456</v>
       </c>
       <c r="D11" t="n">
-        <v>39370773.6</v>
+        <v>74599709.18000001</v>
       </c>
       <c r="E11" t="n">
-        <v>6455382.7</v>
+        <v>12088075.5</v>
       </c>
       <c r="F11" t="n">
         <v>83334</v>
       </c>
       <c r="G11" t="n">
-        <v>553890</v>
+        <v>1616760</v>
       </c>
       <c r="H11" t="n">
-        <v>257284.5</v>
+        <v>5301000</v>
       </c>
       <c r="I11" t="n">
-        <v>383330</v>
+        <v>174510.26</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>768024</v>
+        <v>1570592.38</v>
       </c>
       <c r="L11" t="n">
-        <v>510093</v>
+        <v>9693000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>936000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,22 +17921,22 @@
         <v>11501820</v>
       </c>
       <c r="C12" t="n">
-        <v>10533600</v>
+        <v>8043840</v>
       </c>
       <c r="D12" t="n">
-        <v>14135024.3</v>
+        <v>26783032.32</v>
       </c>
       <c r="E12" t="n">
-        <v>3249661.97</v>
+        <v>6085179</v>
       </c>
       <c r="F12" t="n">
         <v>166668</v>
       </c>
       <c r="G12" t="n">
-        <v>198135</v>
+        <v>578340</v>
       </c>
       <c r="H12" t="n">
-        <v>41497.5</v>
+        <v>855000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16692,10 +17945,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>277342</v>
+        <v>585148.36</v>
       </c>
       <c r="L12" t="n">
-        <v>188494.2</v>
+        <v>3569400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>549000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,22 +17962,22 @@
         <v>4663296</v>
       </c>
       <c r="C13" t="n">
-        <v>3742200</v>
+        <v>2857680</v>
       </c>
       <c r="D13" t="n">
-        <v>5143538.16</v>
+        <v>9745971.84</v>
       </c>
       <c r="E13" t="n">
-        <v>789748.4399999999</v>
+        <v>1478849.4</v>
       </c>
       <c r="F13" t="n">
         <v>41667</v>
       </c>
       <c r="G13" t="n">
-        <v>44955</v>
+        <v>131220</v>
       </c>
       <c r="H13" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -16730,10 +17986,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>64002</v>
+        <v>138311.77</v>
       </c>
       <c r="L13" t="n">
-        <v>78280.2</v>
+        <v>1495800</v>
+      </c>
+      <c r="M13" t="n">
+        <v>297000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,22 +18003,22 @@
         <v>3205620</v>
       </c>
       <c r="C14" t="n">
-        <v>1108800</v>
+        <v>846720</v>
       </c>
       <c r="D14" t="n">
-        <v>1560125.32</v>
+        <v>2956124.16</v>
       </c>
       <c r="E14" t="n">
-        <v>188798.1</v>
+        <v>353535.3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>34965</v>
+        <v>102060</v>
       </c>
       <c r="H14" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -16771,7 +18030,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>27694.8</v>
+        <v>529200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,22 +18044,22 @@
         <v>1376694</v>
       </c>
       <c r="C15" t="n">
-        <v>1191960</v>
+        <v>910224</v>
       </c>
       <c r="D15" t="n">
-        <v>1701290.98</v>
+        <v>3223604.74</v>
       </c>
       <c r="E15" t="n">
-        <v>197752.16</v>
+        <v>370302.3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>7770</v>
+        <v>22680</v>
       </c>
       <c r="H15" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -16806,10 +18068,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>42668</v>
+        <v>95752.42999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>41259.6</v>
+        <v>788400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>810000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,10 +18085,10 @@
         <v>633798</v>
       </c>
       <c r="C16" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D16" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16832,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -16844,10 +18109,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>12434.4</v>
+        <v>237600</v>
+      </c>
+      <c r="M16" t="n">
+        <v>261000</v>
       </c>
     </row>
     <row r="17">
@@ -16858,10 +18126,10 @@
         <v>399168</v>
       </c>
       <c r="C17" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D17" t="n">
-        <v>321013.44</v>
+        <v>608256</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16870,10 +18138,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>73260</v>
+        <v>213840</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -16885,7 +18153,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>10173.6</v>
+        <v>194400</v>
+      </c>
+      <c r="M17" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="18">
@@ -16896,10 +18167,10 @@
         <v>48708</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16908,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -16924,6 +18195,9 @@
       </c>
       <c r="L18" t="n">
         <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="19">
@@ -16934,10 +18208,10 @@
         <v>15246</v>
       </c>
       <c r="C19" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D19" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16962,6 +18236,9 @@
       </c>
       <c r="L19" t="n">
         <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="20">
@@ -16972,10 +18249,10 @@
         <v>2574</v>
       </c>
       <c r="C20" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D20" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17000,6 +18277,9 @@
       </c>
       <c r="L20" t="n">
         <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="21">
@@ -17010,10 +18290,10 @@
         <v>12474</v>
       </c>
       <c r="C21" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D21" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17038,6 +18318,9 @@
       </c>
       <c r="L21" t="n">
         <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="22">
@@ -17048,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17075,6 +18358,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D24" t="n">
-        <v>321013.44</v>
+        <v>608256</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>17699.13</v>
+        <v>17615.07</v>
       </c>
       <c r="C4" t="n">
         <v>3892896</v>
@@ -17308,10 +18609,10 @@
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>71190</v>
+        <v>68970</v>
       </c>
       <c r="H4" t="n">
-        <v>15720</v>
+        <v>15750</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -17320,10 +18621,13 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="L4" t="n">
-        <v>200850</v>
+        <v>198180</v>
+      </c>
+      <c r="M4" t="n">
+        <v>30900</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>29344.86</v>
+        <v>29315.79</v>
       </c>
       <c r="C5" t="n">
         <v>4530960</v>
@@ -17346,7 +18650,7 @@
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>93450</v>
+        <v>92580</v>
       </c>
       <c r="H5" t="n">
         <v>23070</v>
@@ -17358,10 +18662,13 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="L5" t="n">
-        <v>270810</v>
+        <v>269340</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10590</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>29924.64</v>
+        <v>29920.5</v>
       </c>
       <c r="C6" t="n">
         <v>4410504</v>
@@ -17384,7 +18691,7 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>104310</v>
+        <v>103650</v>
       </c>
       <c r="H6" t="n">
         <v>3240</v>
@@ -17396,10 +18703,13 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L6" t="n">
-        <v>260580</v>
+        <v>259890</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4890</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>30897.72</v>
+        <v>30897.27</v>
       </c>
       <c r="C7" t="n">
         <v>3866184</v>
@@ -17422,7 +18732,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>82740</v>
+        <v>82380</v>
       </c>
       <c r="H7" t="n">
         <v>600</v>
@@ -17437,7 +18747,10 @@
         <v>212</v>
       </c>
       <c r="L7" t="n">
-        <v>202800</v>
+        <v>201870</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3660</v>
       </c>
     </row>
     <row r="8">
@@ -17445,7 +18758,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>26311.23</v>
+        <v>26311.14</v>
       </c>
       <c r="C8" t="n">
         <v>2520504</v>
@@ -17460,7 +18773,7 @@
         <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>72180</v>
+        <v>71730</v>
       </c>
       <c r="H8" t="n">
         <v>270</v>
@@ -17475,7 +18788,10 @@
         <v>142</v>
       </c>
       <c r="L8" t="n">
-        <v>134010</v>
+        <v>133350</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4530</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>40560</v>
+        <v>40230</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -17513,7 +18829,10 @@
         <v>92</v>
       </c>
       <c r="L9" t="n">
-        <v>86400</v>
+        <v>86070</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2940</v>
       </c>
     </row>
     <row r="10">
@@ -17536,7 +18855,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>17280</v>
+        <v>17310</v>
       </c>
       <c r="H10" t="n">
         <v>30</v>
@@ -17548,10 +18867,13 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L10" t="n">
-        <v>47550</v>
+        <v>47520</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1890</v>
       </c>
     </row>
     <row r="11">
@@ -17589,7 +18911,10 @@
         <v>22</v>
       </c>
       <c r="L11" t="n">
-        <v>20040</v>
+        <v>19740</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2490</v>
       </c>
     </row>
     <row r="12">
@@ -17627,7 +18952,10 @@
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>4650</v>
+        <v>4470</v>
+      </c>
+      <c r="M12" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="13">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>1740</v>
       </c>
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>510</v>
       </c>
+      <c r="M14" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>270</v>
       </c>
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>570</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>120</v>
       </c>
+      <c r="M17" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13205.19</v>
+        <v>13192.11</v>
       </c>
       <c r="C5" t="n">
         <v>2492028</v>
@@ -18290,10 +19666,13 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>92.81999999999999</v>
+        <v>70.17</v>
       </c>
       <c r="L5" t="n">
-        <v>56870.1</v>
+        <v>56561.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>211.8</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>23939.71</v>
+        <v>23936.4</v>
       </c>
       <c r="C6" t="n">
         <v>3969453.6</v>
@@ -18316,22 +19695,25 @@
         <v>0.8</v>
       </c>
       <c r="G6" t="n">
-        <v>5215.5</v>
+        <v>5182.5</v>
       </c>
       <c r="H6" t="n">
         <v>1846.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>139.1</v>
+        <v>107.99</v>
       </c>
       <c r="L6" t="n">
-        <v>96414.60000000001</v>
+        <v>96159.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>391.2</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>29352.83</v>
+        <v>29352.41</v>
       </c>
       <c r="C7" t="n">
         <v>3866184</v>
@@ -18354,7 +19736,7 @@
         <v>5.4</v>
       </c>
       <c r="G7" t="n">
-        <v>12411</v>
+        <v>12357</v>
       </c>
       <c r="H7" t="n">
         <v>438</v>
@@ -18366,10 +19748,13 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>173.84</v>
+        <v>135.26</v>
       </c>
       <c r="L7" t="n">
-        <v>121680</v>
+        <v>121122</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1281</v>
       </c>
     </row>
     <row r="8">
@@ -18377,7 +19762,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>26311.23</v>
+        <v>26311.14</v>
       </c>
       <c r="C8" t="n">
         <v>2520504</v>
@@ -18392,7 +19777,7 @@
         <v>12.35</v>
       </c>
       <c r="G8" t="n">
-        <v>46917</v>
+        <v>46624.5</v>
       </c>
       <c r="H8" t="n">
         <v>229.5</v>
@@ -18404,10 +19789,13 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>127.8</v>
+        <v>104.51</v>
       </c>
       <c r="L8" t="n">
-        <v>95147.10000000001</v>
+        <v>94678.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2718</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>34476</v>
+        <v>34195.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -18442,10 +19830,13 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>92</v>
+        <v>73.88</v>
       </c>
       <c r="L9" t="n">
-        <v>69984</v>
+        <v>69716.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2940</v>
       </c>
     </row>
     <row r="10">
@@ -18468,7 +19859,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>17280</v>
+        <v>17310</v>
       </c>
       <c r="H10" t="n">
         <v>30</v>
@@ -18480,10 +19871,13 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>52.2</v>
       </c>
       <c r="L10" t="n">
-        <v>42319.5</v>
+        <v>42292.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1890</v>
       </c>
     </row>
     <row r="11">
@@ -18518,10 +19912,13 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>22</v>
+        <v>19.77</v>
       </c>
       <c r="L11" t="n">
-        <v>20040</v>
+        <v>19740</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2490</v>
       </c>
     </row>
     <row r="12">
@@ -18556,10 +19953,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="L12" t="n">
-        <v>4650</v>
+        <v>4470</v>
+      </c>
+      <c r="M12" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="13">
@@ -18599,6 +19999,9 @@
       <c r="L13" t="n">
         <v>1740</v>
       </c>
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>510</v>
       </c>
+      <c r="M14" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18670,10 +20076,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
         <v>270</v>
+      </c>
+      <c r="M15" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>570</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>120</v>
       </c>
+      <c r="M17" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>29051411.4</v>
+        <v>29022632.1</v>
       </c>
       <c r="C5" t="n">
-        <v>137061540</v>
+        <v>104665176</v>
       </c>
       <c r="D5" t="n">
-        <v>119404560.41</v>
+        <v>226247662.08</v>
       </c>
       <c r="E5" t="n">
-        <v>37749537.91</v>
+        <v>70688181.59999999</v>
       </c>
       <c r="F5" t="n">
         <v>23333.52</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2297633.58</v>
+        <v>47339640</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>1980221.88</v>
+        <v>3407271.63</v>
       </c>
       <c r="L5" t="n">
-        <v>535716.34</v>
+        <v>10181052</v>
+      </c>
+      <c r="M5" t="n">
+        <v>63540</v>
       </c>
     </row>
     <row r="6">
@@ -19233,37 +20684,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>52667366.4</v>
+        <v>52660080</v>
       </c>
       <c r="C6" t="n">
-        <v>218319948</v>
+        <v>166717051.2</v>
       </c>
       <c r="D6" t="n">
-        <v>178032328.38</v>
+        <v>337335508.22</v>
       </c>
       <c r="E6" t="n">
-        <v>43687707.34</v>
+        <v>81807745.5</v>
       </c>
       <c r="F6" t="n">
         <v>33333.6</v>
       </c>
       <c r="G6" t="n">
-        <v>96486.75</v>
+        <v>279855</v>
       </c>
       <c r="H6" t="n">
-        <v>510917.22</v>
+        <v>10526760</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>2967559.4</v>
+        <v>5243611</v>
       </c>
       <c r="L6" t="n">
-        <v>908225.53</v>
+        <v>17308674</v>
+      </c>
+      <c r="M6" t="n">
+        <v>117360</v>
       </c>
     </row>
     <row r="7">
@@ -19271,37 +20725,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>64576234.8</v>
+        <v>64575294.3</v>
       </c>
       <c r="C7" t="n">
-        <v>212640120</v>
+        <v>162379728</v>
       </c>
       <c r="D7" t="n">
-        <v>196383904.33</v>
+        <v>372108059.14</v>
       </c>
       <c r="E7" t="n">
-        <v>39395543.59</v>
+        <v>73770421.95</v>
       </c>
       <c r="F7" t="n">
         <v>225001.8</v>
       </c>
       <c r="G7" t="n">
-        <v>229603.5</v>
+        <v>667278</v>
       </c>
       <c r="H7" t="n">
-        <v>121172.7</v>
+        <v>2496600</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>204165.5</v>
+        <v>84973</v>
       </c>
       <c r="K7" t="n">
-        <v>3708702.56</v>
+        <v>6567490.34</v>
       </c>
       <c r="L7" t="n">
-        <v>1146225.6</v>
+        <v>21801960</v>
+      </c>
+      <c r="M7" t="n">
+        <v>384300</v>
       </c>
     </row>
     <row r="8">
@@ -19309,37 +20766,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>57884706</v>
+        <v>57884508</v>
       </c>
       <c r="C8" t="n">
-        <v>138627720</v>
+        <v>105861168</v>
       </c>
       <c r="D8" t="n">
-        <v>147695715.64</v>
+        <v>279853719.55</v>
       </c>
       <c r="E8" t="n">
-        <v>28065518.71</v>
+        <v>52554298.5</v>
       </c>
       <c r="F8" t="n">
         <v>514587.45</v>
       </c>
       <c r="G8" t="n">
-        <v>867964.5</v>
+        <v>2517723</v>
       </c>
       <c r="H8" t="n">
-        <v>63491.18</v>
+        <v>1308150</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2726485.2</v>
+        <v>5074684.67</v>
       </c>
       <c r="L8" t="n">
-        <v>896285.6800000001</v>
+        <v>17042130</v>
+      </c>
+      <c r="M8" t="n">
+        <v>815400</v>
       </c>
     </row>
     <row r="9">
@@ -19350,19 +20810,19 @@
         <v>40448826</v>
       </c>
       <c r="C9" t="n">
-        <v>77006160</v>
+        <v>58804704</v>
       </c>
       <c r="D9" t="n">
-        <v>89511949.38</v>
+        <v>169607167.49</v>
       </c>
       <c r="E9" t="n">
-        <v>19886246.55</v>
+        <v>37238140.8</v>
       </c>
       <c r="F9" t="n">
         <v>833340</v>
       </c>
       <c r="G9" t="n">
-        <v>637806</v>
+        <v>1846557</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -19371,13 +20831,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>166249.05</v>
+        <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>1962728</v>
+        <v>3587123.06</v>
       </c>
       <c r="L9" t="n">
-        <v>659249.28</v>
+        <v>12549006</v>
+      </c>
+      <c r="M9" t="n">
+        <v>882000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,34 +20851,37 @@
         <v>24571206</v>
       </c>
       <c r="C10" t="n">
-        <v>40637520</v>
+        <v>31032288</v>
       </c>
       <c r="D10" t="n">
-        <v>51178370.21</v>
+        <v>96972733.44</v>
       </c>
       <c r="E10" t="n">
-        <v>8847941.76</v>
+        <v>16568280</v>
       </c>
       <c r="F10" t="n">
         <v>125001</v>
       </c>
       <c r="G10" t="n">
-        <v>319680</v>
+        <v>934740</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>1258706</v>
+        <v>2534623.2</v>
       </c>
       <c r="L10" t="n">
-        <v>398649.69</v>
+        <v>7612704</v>
+      </c>
+      <c r="M10" t="n">
+        <v>567000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,19 +20892,19 @@
         <v>15194322</v>
       </c>
       <c r="C11" t="n">
-        <v>15689520</v>
+        <v>11981088</v>
       </c>
       <c r="D11" t="n">
-        <v>20406463.24</v>
+        <v>38666149.63</v>
       </c>
       <c r="E11" t="n">
-        <v>2514201.68</v>
+        <v>4707987.3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>306360</v>
+        <v>894240</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -19447,13 +20913,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>469348</v>
+        <v>959806.45</v>
       </c>
       <c r="L11" t="n">
-        <v>188776.8</v>
+        <v>3553200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>747000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>6672006</v>
       </c>
       <c r="C12" t="n">
-        <v>2661120</v>
+        <v>2032128</v>
       </c>
       <c r="D12" t="n">
-        <v>3570953.51</v>
+        <v>6766239.74</v>
       </c>
       <c r="E12" t="n">
-        <v>317040.19</v>
+        <v>593676</v>
       </c>
       <c r="F12" t="n">
         <v>83334</v>
       </c>
       <c r="G12" t="n">
-        <v>82695</v>
+        <v>241380</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19488,10 +20957,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>85336</v>
+        <v>180045.65</v>
       </c>
       <c r="L12" t="n">
-        <v>43803</v>
+        <v>804600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>270000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,19 +20974,19 @@
         <v>1924956</v>
       </c>
       <c r="C13" t="n">
-        <v>1081080</v>
+        <v>825552</v>
       </c>
       <c r="D13" t="n">
-        <v>1485911.02</v>
+        <v>2815502.98</v>
       </c>
       <c r="E13" t="n">
-        <v>263249.48</v>
+        <v>492949.8</v>
       </c>
       <c r="F13" t="n">
         <v>41667</v>
       </c>
       <c r="G13" t="n">
-        <v>17205</v>
+        <v>50220</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19529,7 +21001,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16390.8</v>
+        <v>313200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="14">
@@ -19540,19 +21015,19 @@
         <v>810018</v>
       </c>
       <c r="C14" t="n">
-        <v>304920</v>
+        <v>232848</v>
       </c>
       <c r="D14" t="n">
-        <v>429034.46</v>
+        <v>812934.14</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>14985</v>
+        <v>43740</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -19567,7 +21042,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4804.2</v>
+        <v>91800</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="15">
@@ -19578,10 +21056,10 @@
         <v>368280</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19590,7 +21068,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19602,10 +21080,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>21334</v>
+        <v>47876.22</v>
       </c>
       <c r="L15" t="n">
-        <v>2543.4</v>
+        <v>48600</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="16">
@@ -19643,7 +21124,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>171000</v>
       </c>
     </row>
     <row r="17">
@@ -19654,10 +21138,10 @@
         <v>262350</v>
       </c>
       <c r="C17" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D17" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19666,7 +21150,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -19681,7 +21165,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M17" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="18">
@@ -19704,7 +21191,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -19720,6 +21207,9 @@
       </c>
       <c r="L18" t="n">
         <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="19">
@@ -19759,6 +21249,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19806,10 +21302,10 @@
         <v>12474</v>
       </c>
       <c r="C21" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D21" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19834,6 +21330,9 @@
       </c>
       <c r="L21" t="n">
         <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="22">
@@ -19873,6 +21372,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19920,10 +21425,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D24" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19947,6 +21452,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,10 +21621,10 @@
         <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>130380</v>
+        <v>130440</v>
       </c>
       <c r="H4" t="n">
-        <v>28020</v>
+        <v>28080</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -20119,7 +21636,10 @@
         <v>257</v>
       </c>
       <c r="L4" t="n">
-        <v>360480</v>
+        <v>358890</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,7 +21662,7 @@
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>75690</v>
+        <v>75900</v>
       </c>
       <c r="H5" t="n">
         <v>25470</v>
@@ -20157,7 +21677,10 @@
         <v>137</v>
       </c>
       <c r="L5" t="n">
-        <v>165690</v>
+        <v>166680</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>29130</v>
+        <v>29280</v>
       </c>
       <c r="H6" t="n">
-        <v>4800</v>
+        <v>4860</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>47</v>
       </c>
       <c r="L6" t="n">
-        <v>64500</v>
+        <v>64350</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20235,6 +21761,9 @@
       <c r="L7" t="n">
         <v>9030</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -20271,7 +21800,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2940</v>
+        <v>2910</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -20294,7 +21826,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H9" t="n">
         <v>60</v>
@@ -20310,6 +21842,9 @@
       </c>
       <c r="L9" t="n">
         <v>690</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>270</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21086,10 +22678,13 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>57.54</v>
+        <v>45.35</v>
       </c>
       <c r="L5" t="n">
-        <v>34794.9</v>
+        <v>35002.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1456.5</v>
+        <v>1464</v>
       </c>
       <c r="H6" t="n">
-        <v>2736</v>
+        <v>2770.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>30.55</v>
+        <v>23.83</v>
       </c>
       <c r="L6" t="n">
-        <v>23865</v>
+        <v>23809.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21162,10 +22760,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.19</v>
       </c>
       <c r="L7" t="n">
         <v>5418</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21203,7 +22804,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2087.4</v>
+        <v>2066.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21226,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25.5</v>
+        <v>51</v>
       </c>
       <c r="H9" t="n">
         <v>60</v>
@@ -21242,6 +22846,9 @@
       </c>
       <c r="L9" t="n">
         <v>558.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>240.3</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>19301287.5</v>
       </c>
       <c r="C5" t="n">
-        <v>69049134</v>
+        <v>52728429.6</v>
       </c>
       <c r="D5" t="n">
-        <v>60153865.86</v>
+        <v>113979495.17</v>
       </c>
       <c r="E5" t="n">
-        <v>4883297.78</v>
+        <v>9144256.050000001</v>
       </c>
       <c r="F5" t="n">
         <v>6666.72</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2536659.18</v>
+        <v>52264440</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>104999.4</v>
+        <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1227558.36</v>
+        <v>2201868.93</v>
       </c>
       <c r="L5" t="n">
-        <v>327767.96</v>
+        <v>6300504</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,34 +23699,37 @@
         <v>13173019.2</v>
       </c>
       <c r="C6" t="n">
-        <v>37646532</v>
+        <v>28748260.8</v>
       </c>
       <c r="D6" t="n">
-        <v>30699438.18</v>
+        <v>58169270.02</v>
       </c>
       <c r="E6" t="n">
-        <v>2185786.51</v>
+        <v>4093011</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>26945.25</v>
+        <v>79056</v>
       </c>
       <c r="H6" t="n">
-        <v>756914.4</v>
+        <v>15790140</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>651753.7</v>
+        <v>1157040.92</v>
       </c>
       <c r="L6" t="n">
-        <v>224808.3</v>
+        <v>4285710</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,22 +23740,22 @@
         <v>954419.4</v>
       </c>
       <c r="C7" t="n">
-        <v>6458760</v>
+        <v>4932144</v>
       </c>
       <c r="D7" t="n">
-        <v>5964991.49</v>
+        <v>11302460.93</v>
       </c>
       <c r="E7" t="n">
-        <v>317421.57</v>
+        <v>594390.15</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2747.25</v>
+        <v>8019</v>
       </c>
       <c r="H7" t="n">
-        <v>121172.7</v>
+        <v>2496600</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22094,10 +23764,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>87469.39999999999</v>
+        <v>154893.64</v>
       </c>
       <c r="L7" t="n">
-        <v>51037.56</v>
+        <v>975240</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,10 +23781,10 @@
         <v>177012</v>
       </c>
       <c r="C8" t="n">
-        <v>720720</v>
+        <v>550368</v>
       </c>
       <c r="D8" t="n">
-        <v>767864.15</v>
+        <v>1454948.35</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22120,10 +23793,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3968.25</v>
+        <v>11583</v>
       </c>
       <c r="H8" t="n">
-        <v>63491.18</v>
+        <v>1308150</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22135,7 +23808,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>19663.31</v>
+        <v>371898</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>62370</v>
       </c>
       <c r="C9" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D9" t="n">
-        <v>128886.9</v>
+        <v>244214.78</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22158,10 +23834,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>2754</v>
       </c>
       <c r="H9" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5264.84</v>
+        <v>100602</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2263.63</v>
+        <v>43254</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22237,7 +23919,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22249,7 +23931,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -22289,6 +23974,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>860</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
         <v>1253130</v>
@@ -590,7 +590,7 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>681</v>
+        <v>242</v>
       </c>
       <c r="L5" t="n">
         <v>909630</v>
@@ -631,7 +631,7 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>436</v>
+        <v>119</v>
       </c>
       <c r="L6" t="n">
         <v>592020</v>
@@ -672,7 +672,7 @@
         <v>11</v>
       </c>
       <c r="K7" t="n">
-        <v>324</v>
+        <v>89</v>
       </c>
       <c r="L7" t="n">
         <v>359910</v>
@@ -713,7 +713,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>210</v>
+        <v>44</v>
       </c>
       <c r="L8" t="n">
         <v>248160</v>
@@ -754,7 +754,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
         <v>192390</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>114780</v>
@@ -836,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>53850</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>19830</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>8310</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4380</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1320</v>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>32340</v>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
         <v>48270</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>55590</v>
@@ -1676,7 +1676,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>48600</v>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>63780</v>
@@ -1758,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>93810</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>61500</v>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>29850</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>13020</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>5550</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3660</v>
@@ -2598,7 +2598,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>9.93</v>
+        <v>5.63</v>
       </c>
       <c r="L5" t="n">
         <v>10136.7</v>
@@ -2639,7 +2639,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>19.27</v>
+        <v>7.6</v>
       </c>
       <c r="L6" t="n">
         <v>20568.3</v>
@@ -2680,7 +2680,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>14.04</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>29160</v>
@@ -2721,7 +2721,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>22.82</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
         <v>45283.8</v>
@@ -2762,7 +2762,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>30.51</v>
+        <v>3.21</v>
       </c>
       <c r="L9" t="n">
         <v>75986.10000000001</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>30.45</v>
+        <v>5.22</v>
       </c>
       <c r="L10" t="n">
         <v>54735</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>12.58</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>29850</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>8.34</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>13020</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>5550</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3660</v>
@@ -3602,7 +3602,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>482161.08</v>
+        <v>273224.61</v>
       </c>
       <c r="L5" t="n">
         <v>1824606</v>
@@ -3643,7 +3643,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>935479.9</v>
+        <v>369268.38</v>
       </c>
       <c r="L6" t="n">
         <v>3702294</v>
@@ -3684,7 +3684,7 @@
         <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>681532.02</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
         <v>5248800</v>
@@ -3725,7 +3725,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1107853.7</v>
+        <v>142948.86</v>
       </c>
       <c r="L8" t="n">
         <v>8151084</v>
@@ -3766,7 +3766,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>1481637.78</v>
+        <v>155961.87</v>
       </c>
       <c r="L9" t="n">
         <v>13677498</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1478530.2</v>
+        <v>253462.32</v>
       </c>
       <c r="L10" t="n">
         <v>9852300</v>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>610785.92</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>5373000</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>405102.71</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>2343600</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>138311.77</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>999000</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>47876.22</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>658800</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>103260</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>35310</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>8190</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.96</v>
+        <v>2.32</v>
       </c>
       <c r="L5" t="n">
         <v>7415.1</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>3030.3</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>241080.54</v>
+        <v>112504.25</v>
       </c>
       <c r="L5" t="n">
         <v>1334718</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>49235.78</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>545454</v>
@@ -7577,7 +7577,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>55260</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>14040</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2640</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>510</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2948.4</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>976.8</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>306</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>144648.32</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>530712</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>73853.67999999999</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>175824</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>61957.46</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>55080</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>224</v>
+        <v>124</v>
       </c>
       <c r="L4" t="n">
         <v>218280</v>
@@ -10630,7 +10630,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>256</v>
+        <v>99</v>
       </c>
       <c r="L5" t="n">
         <v>252630</v>
@@ -10671,7 +10671,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>132</v>
+        <v>39</v>
       </c>
       <c r="L6" t="n">
         <v>147120</v>
@@ -10712,7 +10712,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
         <v>72240</v>
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>37620</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>9030</v>
@@ -11081,7 +11081,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>510</v>
@@ -11634,7 +11634,7 @@
         <v>5.7</v>
       </c>
       <c r="K5" t="n">
-        <v>225.41</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>191022.3</v>
@@ -11675,7 +11675,7 @@
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>221.05</v>
+        <v>60.33</v>
       </c>
       <c r="L6" t="n">
         <v>219047.4</v>
@@ -11716,7 +11716,7 @@
         <v>7.7</v>
       </c>
       <c r="K7" t="n">
-        <v>206.71</v>
+        <v>56.78</v>
       </c>
       <c r="L7" t="n">
         <v>215946</v>
@@ -11757,7 +11757,7 @@
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>154.56</v>
+        <v>32.38</v>
       </c>
       <c r="L8" t="n">
         <v>176193.6</v>
@@ -11798,7 +11798,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>110.01</v>
+        <v>25.7</v>
       </c>
       <c r="L9" t="n">
         <v>155835.9</v>
@@ -11839,7 +11839,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>83.52</v>
+        <v>10.44</v>
       </c>
       <c r="L10" t="n">
         <v>102154.2</v>
@@ -11880,7 +11880,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>32.35</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
         <v>53850</v>
@@ -11921,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>12.05</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>19830</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>8310</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4380</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1320</v>
@@ -12638,7 +12638,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>84.73999999999999</v>
+        <v>32.77</v>
       </c>
       <c r="L5" t="n">
         <v>53052.3</v>
@@ -12679,7 +12679,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>66.92</v>
+        <v>19.77</v>
       </c>
       <c r="L6" t="n">
         <v>54434.4</v>
@@ -12720,7 +12720,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>52.95</v>
+        <v>18.5</v>
       </c>
       <c r="L7" t="n">
         <v>43344</v>
@@ -12761,7 +12761,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>26.5</v>
+        <v>4.42</v>
       </c>
       <c r="L8" t="n">
         <v>26710.2</v>
@@ -12802,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.82</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>7314.3</v>
@@ -13089,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>510</v>
@@ -13642,7 +13642,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4114441.22</v>
+        <v>1591131.56</v>
       </c>
       <c r="L5" t="n">
         <v>9549414</v>
@@ -13683,7 +13683,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>3249561.74</v>
+        <v>960097.79</v>
       </c>
       <c r="L6" t="n">
         <v>9798192</v>
@@ -13724,7 +13724,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2571234.42</v>
+        <v>898383.11</v>
       </c>
       <c r="L7" t="n">
         <v>7801920</v>
@@ -13765,7 +13765,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1286539.78</v>
+        <v>214423.3</v>
       </c>
       <c r="L8" t="n">
         <v>4807836</v>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>233942.81</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
         <v>1316574</v>
@@ -14093,7 +14093,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>91800</v>
@@ -14605,7 +14605,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
         <v>225420</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>62580</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.29</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>13141.8</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>305368.68</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>2365524</v>
@@ -17658,7 +17658,7 @@
         <v>138384.6</v>
       </c>
       <c r="K5" t="n">
-        <v>10945056.52</v>
+        <v>3889432.71</v>
       </c>
       <c r="L5" t="n">
         <v>34384014</v>
@@ -17699,7 +17699,7 @@
         <v>133529</v>
       </c>
       <c r="K6" t="n">
-        <v>10733400.91</v>
+        <v>2929529.15</v>
       </c>
       <c r="L6" t="n">
         <v>39428532</v>
@@ -17740,7 +17740,7 @@
         <v>186940.6</v>
       </c>
       <c r="K7" t="n">
-        <v>10037107.87</v>
+        <v>2757106.79</v>
       </c>
       <c r="L7" t="n">
         <v>38870280</v>
@@ -17781,7 +17781,7 @@
         <v>82545.2</v>
       </c>
       <c r="K8" t="n">
-        <v>7504815.36</v>
+        <v>1572437.5</v>
       </c>
       <c r="L8" t="n">
         <v>31714848</v>
@@ -17822,7 +17822,7 @@
         <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>5341694.12</v>
+        <v>1247694.98</v>
       </c>
       <c r="L9" t="n">
         <v>28050462</v>
@@ -17863,7 +17863,7 @@
         <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>4055397.12</v>
+        <v>506924.64</v>
       </c>
       <c r="L10" t="n">
         <v>18387756</v>
@@ -17904,7 +17904,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>1570592.38</v>
+        <v>43627.57</v>
       </c>
       <c r="L11" t="n">
         <v>9693000</v>
@@ -17945,7 +17945,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>585148.36</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>3569400</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>138311.77</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1495800</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>95752.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>788400</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>237600</v>
@@ -18621,7 +18621,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
         <v>198180</v>
@@ -18662,7 +18662,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>212</v>
+        <v>68</v>
       </c>
       <c r="L5" t="n">
         <v>269340</v>
@@ -18703,7 +18703,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>213</v>
+        <v>57</v>
       </c>
       <c r="L6" t="n">
         <v>259890</v>
@@ -18744,7 +18744,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>212</v>
+        <v>57</v>
       </c>
       <c r="L7" t="n">
         <v>201870</v>
@@ -18785,7 +18785,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
         <v>133350</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
         <v>86070</v>
@@ -18867,7 +18867,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>47520</v>
@@ -18908,7 +18908,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>19740</v>
@@ -18949,7 +18949,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>4470</v>
@@ -19072,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>270</v>
@@ -19666,7 +19666,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>70.17</v>
+        <v>22.51</v>
       </c>
       <c r="L5" t="n">
         <v>56561.4</v>
@@ -19707,7 +19707,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>107.99</v>
+        <v>28.9</v>
       </c>
       <c r="L6" t="n">
         <v>96159.3</v>
@@ -19748,7 +19748,7 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>135.26</v>
+        <v>36.37</v>
       </c>
       <c r="L7" t="n">
         <v>121122</v>
@@ -19789,7 +19789,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>104.51</v>
+        <v>25.02</v>
       </c>
       <c r="L8" t="n">
         <v>94678.5</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>73.88</v>
+        <v>19.27</v>
       </c>
       <c r="L9" t="n">
         <v>69716.7</v>
@@ -19871,7 +19871,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>52.2</v>
+        <v>4.35</v>
       </c>
       <c r="L10" t="n">
         <v>42292.8</v>
@@ -19912,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>19.77</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
         <v>19740</v>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>4470</v>
@@ -20076,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>270</v>
@@ -20670,7 +20670,7 @@
         <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>3407271.63</v>
+        <v>1092898.45</v>
       </c>
       <c r="L5" t="n">
         <v>10181052</v>
@@ -20711,7 +20711,7 @@
         <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>5243611</v>
+        <v>1403219.84</v>
       </c>
       <c r="L6" t="n">
         <v>17308674</v>
@@ -20752,7 +20752,7 @@
         <v>84973</v>
       </c>
       <c r="K7" t="n">
-        <v>6567490.34</v>
+        <v>1765787.5</v>
       </c>
       <c r="L7" t="n">
         <v>21801960</v>
@@ -20793,7 +20793,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5074684.67</v>
+        <v>1215065.34</v>
       </c>
       <c r="L8" t="n">
         <v>17042130</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3587123.06</v>
+        <v>935771.23</v>
       </c>
       <c r="L9" t="n">
         <v>12549006</v>
@@ -20875,7 +20875,7 @@
         <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>2534623.2</v>
+        <v>211218.6</v>
       </c>
       <c r="L10" t="n">
         <v>7612704</v>
@@ -20916,7 +20916,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>959806.45</v>
+        <v>43627.57</v>
       </c>
       <c r="L11" t="n">
         <v>3553200</v>
@@ -20957,7 +20957,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>180045.65</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>804600</v>
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>47876.22</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>48600</v>
@@ -21633,7 +21633,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>257</v>
+        <v>70</v>
       </c>
       <c r="L4" t="n">
         <v>358890</v>
@@ -21674,7 +21674,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
         <v>166680</v>
@@ -21715,7 +21715,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>64350</v>
@@ -21756,7 +21756,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>9030</v>
@@ -22678,7 +22678,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>45.35</v>
+        <v>13.24</v>
       </c>
       <c r="L5" t="n">
         <v>35002.8</v>
@@ -22719,7 +22719,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>23.83</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>23809.5</v>
@@ -22760,7 +22760,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5418</v>
@@ -23682,7 +23682,7 @@
         <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2201868.93</v>
+        <v>642881.4399999999</v>
       </c>
       <c r="L5" t="n">
         <v>6300504</v>
@@ -23723,7 +23723,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>1157040.92</v>
+        <v>172325.24</v>
       </c>
       <c r="L6" t="n">
         <v>4285710</v>
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>154893.64</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>975240</v>

--- a/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Future_Breaches.xlsx
@@ -560,7 +560,7 @@
         <v>470070</v>
       </c>
       <c r="H4" t="n">
-        <v>70620</v>
+        <v>76290</v>
       </c>
       <c r="I4" t="n">
         <v>8</v>
@@ -572,22 +572,22 @@
         <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>1253130</v>
+        <v>1349340</v>
       </c>
       <c r="M4" t="n">
-        <v>69570</v>
+        <v>50400</v>
       </c>
       <c r="N4" t="n">
-        <v>56130</v>
+        <v>64050</v>
       </c>
       <c r="O4" t="n">
-        <v>227490</v>
+        <v>240720</v>
       </c>
       <c r="P4" t="n">
-        <v>56730</v>
+        <v>19680</v>
       </c>
       <c r="Q4" t="n">
-        <v>189450.04</v>
+        <v>1963252.43</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>346140</v>
       </c>
       <c r="H5" t="n">
-        <v>71400</v>
+        <v>76650</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -625,22 +625,22 @@
         <v>242</v>
       </c>
       <c r="L5" t="n">
-        <v>909630</v>
+        <v>937920</v>
       </c>
       <c r="M5" t="n">
-        <v>44400</v>
+        <v>39240</v>
       </c>
       <c r="N5" t="n">
-        <v>21600</v>
+        <v>31380</v>
       </c>
       <c r="O5" t="n">
-        <v>172830</v>
+        <v>194310</v>
       </c>
       <c r="P5" t="n">
-        <v>70560</v>
+        <v>48660</v>
       </c>
       <c r="Q5" t="n">
-        <v>141092.42</v>
+        <v>1462127.1</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>248820</v>
       </c>
       <c r="H6" t="n">
-        <v>21090</v>
+        <v>23760</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
@@ -678,22 +678,22 @@
         <v>119</v>
       </c>
       <c r="L6" t="n">
-        <v>592020</v>
+        <v>617460</v>
       </c>
       <c r="M6" t="n">
-        <v>21510</v>
+        <v>29190</v>
       </c>
       <c r="N6" t="n">
-        <v>5070</v>
+        <v>9270</v>
       </c>
       <c r="O6" t="n">
-        <v>101400</v>
+        <v>116700</v>
       </c>
       <c r="P6" t="n">
-        <v>68790</v>
+        <v>53250</v>
       </c>
       <c r="Q6" t="n">
-        <v>104525.34</v>
+        <v>1083186</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>153210</v>
       </c>
       <c r="H7" t="n">
-        <v>5160</v>
+        <v>6480</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -731,22 +731,22 @@
         <v>89</v>
       </c>
       <c r="L7" t="n">
-        <v>359910</v>
+        <v>397200</v>
       </c>
       <c r="M7" t="n">
-        <v>13290</v>
+        <v>29760</v>
       </c>
       <c r="N7" t="n">
-        <v>690</v>
+        <v>2940</v>
       </c>
       <c r="O7" t="n">
-        <v>72510</v>
+        <v>80580</v>
       </c>
       <c r="P7" t="n">
-        <v>73050</v>
+        <v>59820</v>
       </c>
       <c r="Q7" t="n">
-        <v>82654.64</v>
+        <v>856542.0600000001</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>114660</v>
       </c>
       <c r="H8" t="n">
-        <v>5400</v>
+        <v>5580</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -784,22 +784,22 @@
         <v>44</v>
       </c>
       <c r="L8" t="n">
-        <v>248160</v>
+        <v>275850</v>
       </c>
       <c r="M8" t="n">
-        <v>9960</v>
+        <v>33090</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O8" t="n">
-        <v>32220</v>
+        <v>52200</v>
       </c>
       <c r="P8" t="n">
-        <v>80040</v>
+        <v>78480</v>
       </c>
       <c r="Q8" t="n">
-        <v>56757.86</v>
+        <v>588176.24</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>77280</v>
       </c>
       <c r="H9" t="n">
-        <v>4260</v>
+        <v>4920</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>192390</v>
+        <v>226470</v>
       </c>
       <c r="M9" t="n">
-        <v>5130</v>
+        <v>28410</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>9420</v>
+        <v>21210</v>
       </c>
       <c r="P9" t="n">
-        <v>82260</v>
+        <v>94530</v>
       </c>
       <c r="Q9" t="n">
-        <v>35491.59</v>
+        <v>367795.91</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>46170</v>
       </c>
       <c r="H10" t="n">
-        <v>1290</v>
+        <v>1770</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>114780</v>
+        <v>164310</v>
       </c>
       <c r="M10" t="n">
-        <v>3000</v>
+        <v>25620</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4050</v>
+        <v>12060</v>
       </c>
       <c r="P10" t="n">
-        <v>72240</v>
+        <v>111540</v>
       </c>
       <c r="Q10" t="n">
-        <v>23049.98</v>
+        <v>238864.67</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>29940</v>
       </c>
       <c r="H11" t="n">
-        <v>930</v>
+        <v>1080</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -943,22 +943,22 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>53850</v>
+        <v>93090</v>
       </c>
       <c r="M11" t="n">
-        <v>3120</v>
+        <v>22890</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3840</v>
+        <v>4530</v>
       </c>
       <c r="P11" t="n">
-        <v>49890</v>
+        <v>83400</v>
       </c>
       <c r="Q11" t="n">
-        <v>13515.65</v>
+        <v>140061.4</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>10710</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>510</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>19830</v>
+        <v>45630</v>
       </c>
       <c r="M12" t="n">
-        <v>1830</v>
+        <v>12420</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>570</v>
+        <v>1170</v>
       </c>
       <c r="P12" t="n">
-        <v>36990</v>
+        <v>60420</v>
       </c>
       <c r="Q12" t="n">
-        <v>6482.84</v>
+        <v>67181.09</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>2430</v>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8310</v>
+        <v>24360</v>
       </c>
       <c r="M13" t="n">
-        <v>990</v>
+        <v>6570</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="P13" t="n">
-        <v>29190</v>
+        <v>35250</v>
       </c>
       <c r="Q13" t="n">
-        <v>2628.4</v>
+        <v>27237.89</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>1890</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2940</v>
+        <v>13950</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>1650</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>39990</v>
+        <v>55650</v>
       </c>
       <c r="Q14" t="n">
-        <v>1806.8</v>
+        <v>18723.73</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>420</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4380</v>
+        <v>10020</v>
       </c>
       <c r="M15" t="n">
-        <v>2700</v>
+        <v>3690</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>22200</v>
+        <v>40740</v>
       </c>
       <c r="Q15" t="n">
-        <v>775.95</v>
+        <v>8041.14</v>
       </c>
     </row>
     <row r="16">
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1320</v>
+        <v>5310</v>
       </c>
       <c r="M16" t="n">
-        <v>870</v>
+        <v>2190</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>15240</v>
+        <v>16740</v>
       </c>
       <c r="Q16" t="n">
-        <v>357.23</v>
+        <v>3701.96</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>3960</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,22 +1261,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1080</v>
+        <v>4950</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P17" t="n">
-        <v>22680</v>
+        <v>38790</v>
       </c>
       <c r="Q17" t="n">
-        <v>224.99</v>
+        <v>2331.5</v>
       </c>
     </row>
     <row r="18">
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>600</v>
+        <v>3510</v>
       </c>
       <c r="Q18" t="n">
-        <v>27.45</v>
+        <v>284.5</v>
       </c>
     </row>
     <row r="19">
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.59</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="20">
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.45</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="21">
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.03</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="22">
@@ -1852,7 +1852,7 @@
         <v>9270</v>
       </c>
       <c r="H4" t="n">
-        <v>3270</v>
+        <v>3600</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>32340</v>
+        <v>24270</v>
       </c>
       <c r="M4" t="n">
-        <v>11190</v>
+        <v>2610</v>
       </c>
       <c r="N4" t="n">
-        <v>900</v>
+        <v>540</v>
       </c>
       <c r="O4" t="n">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>448.55</v>
+        <v>50835.78</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>16530</v>
       </c>
       <c r="H5" t="n">
-        <v>2850</v>
+        <v>2910</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>48270</v>
+        <v>38820</v>
       </c>
       <c r="M5" t="n">
-        <v>14100</v>
+        <v>8040</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>570</v>
       </c>
       <c r="O5" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>901.64</v>
+        <v>102185.64</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>22530</v>
       </c>
       <c r="H6" t="n">
-        <v>5610</v>
+        <v>5550</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1970,13 +1970,13 @@
         <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>55590</v>
+        <v>52410</v>
       </c>
       <c r="M6" t="n">
-        <v>7080</v>
+        <v>5160</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
         <v>120</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1603.34</v>
+        <v>181711.98</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>17820</v>
       </c>
       <c r="H7" t="n">
-        <v>3180</v>
+        <v>3780</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>48600</v>
+        <v>51270</v>
       </c>
       <c r="M7" t="n">
-        <v>4560</v>
+        <v>3390</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1876.34</v>
+        <v>212651.64</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>25470</v>
       </c>
       <c r="H8" t="n">
-        <v>4800</v>
+        <v>4320</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -2076,22 +2076,22 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>63780</v>
+        <v>61500</v>
       </c>
       <c r="M8" t="n">
-        <v>1800</v>
+        <v>4290</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1677.29</v>
+        <v>190093.32</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>33390</v>
       </c>
       <c r="H9" t="n">
-        <v>4200</v>
+        <v>4770</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>93810</v>
+        <v>96810</v>
       </c>
       <c r="M9" t="n">
-        <v>960</v>
+        <v>3900</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2030.02</v>
+        <v>230069.16</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>27600</v>
       </c>
       <c r="H10" t="n">
-        <v>1260</v>
+        <v>1470</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2182,10 +2182,10 @@
         <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>61500</v>
+        <v>72000</v>
       </c>
       <c r="M10" t="n">
-        <v>360</v>
+        <v>3450</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1765.18</v>
+        <v>200053.62</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>13050</v>
       </c>
       <c r="H11" t="n">
-        <v>870</v>
+        <v>810</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>29850</v>
+        <v>36030</v>
       </c>
       <c r="M11" t="n">
-        <v>360</v>
+        <v>3450</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>905.88</v>
+        <v>102666.06</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>5760</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13020</v>
+        <v>18000</v>
       </c>
       <c r="M12" t="n">
-        <v>390</v>
+        <v>3390</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>476.95</v>
+        <v>54054.9</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>1260</v>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5550</v>
+        <v>11250</v>
       </c>
       <c r="M13" t="n">
-        <v>750</v>
+        <v>2220</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>208.44</v>
+        <v>23623.2</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>480</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1620</v>
+        <v>3600</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>630</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>160.92</v>
+        <v>18237.6</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3660</v>
+        <v>5460</v>
       </c>
       <c r="M15" t="n">
-        <v>2580</v>
+        <v>3540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>58.99</v>
+        <v>6686.1</v>
       </c>
     </row>
     <row r="16">
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>750</v>
+        <v>1920</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36.37</v>
+        <v>4121.82</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>60</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>630</v>
+        <v>1980</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.83</v>
+        <v>1113.84</v>
       </c>
     </row>
     <row r="18">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.86</v>
+        <v>211.14</v>
       </c>
     </row>
     <row r="19">
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.19</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="20">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1026</v>
+        <v>1047.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>5.63</v>
       </c>
       <c r="L5" t="n">
-        <v>10136.7</v>
+        <v>8152.2</v>
       </c>
       <c r="M5" t="n">
-        <v>282</v>
+        <v>160.8</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>45.08</v>
+        <v>5109.28</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>1126.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3197.7</v>
+        <v>3163.5</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -3262,13 +3262,13 @@
         <v>7.6</v>
       </c>
       <c r="L6" t="n">
-        <v>20568.3</v>
+        <v>19391.7</v>
       </c>
       <c r="M6" t="n">
-        <v>566.4</v>
+        <v>412.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
         <v>30</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1202.51</v>
+        <v>136283.99</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>2673</v>
       </c>
       <c r="H7" t="n">
-        <v>2321.4</v>
+        <v>2759.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>1.91</v>
       </c>
       <c r="L7" t="n">
-        <v>29160</v>
+        <v>30762</v>
       </c>
       <c r="M7" t="n">
-        <v>1596</v>
+        <v>1186.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>31.5</v>
+        <v>63</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1501.07</v>
+        <v>170121.31</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>16555.5</v>
       </c>
       <c r="H8" t="n">
-        <v>4080</v>
+        <v>3672</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -3368,22 +3368,22 @@
         <v>2.94</v>
       </c>
       <c r="L8" t="n">
-        <v>45283.8</v>
+        <v>43665</v>
       </c>
       <c r="M8" t="n">
-        <v>990</v>
+        <v>2359.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>67.5</v>
+        <v>27</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1593.43</v>
+        <v>180588.65</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>28381.5</v>
       </c>
       <c r="H9" t="n">
-        <v>4200</v>
+        <v>4770</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>3.21</v>
       </c>
       <c r="L9" t="n">
-        <v>75986.10000000001</v>
+        <v>78416.10000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>672</v>
+        <v>2730</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>82.5</v>
+        <v>132</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1969.12</v>
+        <v>223167.09</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>27600</v>
       </c>
       <c r="H10" t="n">
-        <v>1260</v>
+        <v>1470</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3474,10 +3474,10 @@
         <v>5.22</v>
       </c>
       <c r="L10" t="n">
-        <v>54735</v>
+        <v>64080</v>
       </c>
       <c r="M10" t="n">
-        <v>306</v>
+        <v>2932.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1765.18</v>
+        <v>200053.62</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>13050</v>
       </c>
       <c r="H11" t="n">
-        <v>870</v>
+        <v>810</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>29850</v>
+        <v>36030</v>
       </c>
       <c r="M11" t="n">
-        <v>324</v>
+        <v>3105</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>905.88</v>
+        <v>102666.06</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>5760</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13020</v>
+        <v>18000</v>
       </c>
       <c r="M12" t="n">
-        <v>370.5</v>
+        <v>3220.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>476.95</v>
+        <v>54054.9</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>1260</v>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5550</v>
+        <v>11250</v>
       </c>
       <c r="M13" t="n">
-        <v>750</v>
+        <v>2220</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>208.44</v>
+        <v>23623.2</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>480</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1620</v>
+        <v>3600</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>630</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>160.92</v>
+        <v>18237.6</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3660</v>
+        <v>5460</v>
       </c>
       <c r="M15" t="n">
-        <v>2580</v>
+        <v>3540</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>59</v>
+        <v>6686.1</v>
       </c>
     </row>
     <row r="16">
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>750</v>
+        <v>1920</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36.37</v>
+        <v>4121.82</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>60</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>630</v>
+        <v>1980</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.83</v>
+        <v>1113.84</v>
       </c>
     </row>
     <row r="18">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.86</v>
+        <v>211.14</v>
       </c>
     </row>
     <row r="19">
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.19</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="20">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5848200</v>
+        <v>5971320</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>273224.61</v>
       </c>
       <c r="L5" t="n">
-        <v>1824606</v>
+        <v>1467396</v>
       </c>
       <c r="M5" t="n">
-        <v>98700</v>
+        <v>56280</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>969</v>
       </c>
       <c r="O5" t="n">
-        <v>3570</v>
+        <v>4080</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>27049.14</v>
+        <v>3065569.2</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>60831</v>
       </c>
       <c r="H6" t="n">
-        <v>18226890</v>
+        <v>18031950</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -4554,13 +4554,13 @@
         <v>369268.38</v>
       </c>
       <c r="L6" t="n">
-        <v>3702294</v>
+        <v>3490506</v>
       </c>
       <c r="M6" t="n">
-        <v>198240</v>
+        <v>144480</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
         <v>5100</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>721503.45</v>
+        <v>81770391</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>144342</v>
       </c>
       <c r="H7" t="n">
-        <v>13231980</v>
+        <v>15728580</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>5248800</v>
+        <v>5537160</v>
       </c>
       <c r="M7" t="n">
-        <v>558600</v>
+        <v>415275</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5355</v>
+        <v>10710</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>900642.24</v>
+        <v>102072787.2</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>893997</v>
       </c>
       <c r="H8" t="n">
-        <v>23256000</v>
+        <v>20930400</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -4660,22 +4660,22 @@
         <v>142948.86</v>
       </c>
       <c r="L8" t="n">
-        <v>8151084</v>
+        <v>7859700</v>
       </c>
       <c r="M8" t="n">
-        <v>346500</v>
+        <v>825825</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>11475</v>
+        <v>4590</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>956057.58</v>
+        <v>108353192.4</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>1532601</v>
       </c>
       <c r="H9" t="n">
-        <v>23940000</v>
+        <v>27189000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>155961.87</v>
       </c>
       <c r="L9" t="n">
-        <v>13677498</v>
+        <v>14114898</v>
       </c>
       <c r="M9" t="n">
-        <v>235200</v>
+        <v>955500</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14025</v>
+        <v>22440</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1181472.8</v>
+        <v>133900251.12</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>1490400</v>
       </c>
       <c r="H10" t="n">
-        <v>7182000</v>
+        <v>8379000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4766,10 +4766,10 @@
         <v>253462.32</v>
       </c>
       <c r="L10" t="n">
-        <v>9852300</v>
+        <v>11534400</v>
       </c>
       <c r="M10" t="n">
-        <v>107100</v>
+        <v>1026375</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1059107.4</v>
+        <v>120032172</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>704700</v>
       </c>
       <c r="H11" t="n">
-        <v>4959000</v>
+        <v>4617000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5373000</v>
+        <v>6485400</v>
       </c>
       <c r="M11" t="n">
-        <v>113400</v>
+        <v>1086750</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>543526.2</v>
+        <v>61599636</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>311040</v>
       </c>
       <c r="H12" t="n">
-        <v>855000</v>
+        <v>2394000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2343600</v>
+        <v>3240000</v>
       </c>
       <c r="M12" t="n">
-        <v>129675</v>
+        <v>1127175</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>286173</v>
+        <v>32432940</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>68040</v>
       </c>
       <c r="H13" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>999000</v>
+        <v>2025000</v>
       </c>
       <c r="M13" t="n">
-        <v>262500</v>
+        <v>777000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>125064</v>
+        <v>14173920</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>25920</v>
       </c>
       <c r="H14" t="n">
-        <v>513000</v>
+        <v>342000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>291600</v>
+        <v>648000</v>
       </c>
       <c r="M14" t="n">
-        <v>42000</v>
+        <v>220500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>96552</v>
+        <v>10942560</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>4860</v>
       </c>
       <c r="H15" t="n">
-        <v>342000</v>
+        <v>1197000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>658800</v>
+        <v>982800</v>
       </c>
       <c r="M15" t="n">
-        <v>903000</v>
+        <v>1239000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>35397</v>
+        <v>4011660</v>
       </c>
     </row>
     <row r="16">
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>135000</v>
+        <v>345600</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>409500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21821.4</v>
+        <v>2473092</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>3240</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>113400</v>
+        <v>356400</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>493500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5896.8</v>
+        <v>668304</v>
       </c>
     </row>
     <row r="18">
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1117.8</v>
+        <v>126684</v>
       </c>
     </row>
     <row r="19">
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.4</v>
+        <v>12852</v>
       </c>
     </row>
     <row r="20">
@@ -5728,7 +5728,7 @@
         <v>30600</v>
       </c>
       <c r="H4" t="n">
-        <v>1740</v>
+        <v>3060</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>103260</v>
+        <v>119340</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3150</v>
+        <v>3630</v>
       </c>
       <c r="O4" t="n">
-        <v>18810</v>
+        <v>20790</v>
       </c>
       <c r="P4" t="n">
-        <v>10560</v>
+        <v>9150</v>
       </c>
       <c r="Q4" t="n">
-        <v>17884.21</v>
+        <v>94127.39999999999</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>9870</v>
       </c>
       <c r="H5" t="n">
-        <v>480</v>
+        <v>810</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>35310</v>
+        <v>50190</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1350</v>
+        <v>1980</v>
       </c>
       <c r="O5" t="n">
-        <v>4380</v>
+        <v>8310</v>
       </c>
       <c r="P5" t="n">
-        <v>8340</v>
+        <v>12600</v>
       </c>
       <c r="Q5" t="n">
-        <v>6667.15</v>
+        <v>35090.28</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1620</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>11700</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>810</v>
+      </c>
+      <c r="P6" t="n">
         <v>8190</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>210</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5970</v>
-      </c>
       <c r="Q6" t="n">
-        <v>407.12</v>
+        <v>2142.72</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>240</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1560</v>
+        <v>3270</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5760</v>
+        <v>8880</v>
       </c>
       <c r="Q7" t="n">
-        <v>74.48999999999999</v>
+        <v>392.04</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>360</v>
+        <v>1620</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4890</v>
+        <v>9960</v>
       </c>
       <c r="Q8" t="n">
-        <v>40.01</v>
+        <v>210.6</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>780</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4320</v>
+        <v>11730</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.44</v>
+        <v>133.92</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>510</v>
+        <v>1440</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.82</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>172.8</v>
+        <v>291.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>2.32</v>
       </c>
       <c r="L5" t="n">
-        <v>7415.1</v>
+        <v>10539.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>13.5</v>
+        <v>19.8</v>
       </c>
       <c r="O5" t="n">
-        <v>219</v>
+        <v>415.5</v>
       </c>
       <c r="P5" t="n">
-        <v>166.8</v>
+        <v>252</v>
       </c>
       <c r="Q5" t="n">
-        <v>333.36</v>
+        <v>1754.51</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>81</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>171</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>3030.3</v>
+        <v>4329</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -7147,13 +7147,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>52.5</v>
+        <v>202.5</v>
       </c>
       <c r="P6" t="n">
-        <v>895.5</v>
+        <v>1228.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>305.34</v>
+        <v>1607.04</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>36</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>936</v>
+        <v>1962</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1440</v>
+        <v>2220</v>
       </c>
       <c r="Q7" t="n">
-        <v>59.59</v>
+        <v>313.63</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>255.6</v>
+        <v>1150.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1858.2</v>
+        <v>3784.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>38.01</v>
+        <v>200.07</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121.5</v>
+        <v>631.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2160</v>
+        <v>5865</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.68</v>
+        <v>129.9</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>433.5</v>
+        <v>1224</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.82</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>984960</v>
+        <v>1662120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>112504.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1334718</v>
+        <v>1897182</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2295</v>
+        <v>3366</v>
       </c>
       <c r="O5" t="n">
-        <v>37230</v>
+        <v>70635</v>
       </c>
       <c r="P5" t="n">
-        <v>10842</v>
+        <v>16380</v>
       </c>
       <c r="Q5" t="n">
-        <v>200014.6</v>
+        <v>1052708.4</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>4374</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>974700</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,7 +8430,7 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>545454</v>
+        <v>779220</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -8439,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8925</v>
+        <v>34425</v>
       </c>
       <c r="P6" t="n">
-        <v>58207.5</v>
+        <v>79852.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>183202.56</v>
+        <v>964224</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>1944</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>249660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>168480</v>
+        <v>353160</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>93600</v>
+        <v>144300</v>
       </c>
       <c r="Q7" t="n">
-        <v>35754.05</v>
+        <v>188179.2</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>46008</v>
+        <v>207036</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>120783</v>
+        <v>246012</v>
       </c>
       <c r="Q8" t="n">
-        <v>22807.98</v>
+        <v>120042</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21870</v>
+        <v>113724</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>140400</v>
+        <v>381225</v>
       </c>
       <c r="Q9" t="n">
-        <v>14808.87</v>
+        <v>77941.44</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>28177.5</v>
+        <v>79560</v>
       </c>
       <c r="Q10" t="n">
-        <v>492.48</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>43110</v>
       </c>
       <c r="H4" t="n">
-        <v>3480</v>
+        <v>3360</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>55260</v>
+        <v>72330</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>17250</v>
+        <v>21390</v>
       </c>
       <c r="O4" t="n">
-        <v>26940</v>
+        <v>28200</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18623.72</v>
+        <v>101058.93</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>10500</v>
       </c>
       <c r="H5" t="n">
-        <v>2460</v>
+        <v>3090</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>14040</v>
+        <v>17190</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6450</v>
+        <v>6930</v>
       </c>
       <c r="O5" t="n">
-        <v>27240</v>
+        <v>25860</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3014.19</v>
+        <v>16356.06</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>2820</v>
       </c>
       <c r="H6" t="n">
-        <v>450</v>
+        <v>660</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2640</v>
+        <v>6030</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2520</v>
+        <v>3870</v>
       </c>
       <c r="O6" t="n">
-        <v>20250</v>
+        <v>23970</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>482.74</v>
+        <v>2619.54</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>780</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>510</v>
+        <v>1170</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>150</v>
+        <v>1230</v>
       </c>
       <c r="O7" t="n">
-        <v>6210</v>
+        <v>8160</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>92.65000000000001</v>
+        <v>502.74</v>
       </c>
     </row>
     <row r="8">
@@ -9837,13 +9837,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>990</v>
+        <v>2070</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.44</v>
+        <v>83.79000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>240</v>
+        <v>540</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.97</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>885.6</v>
+        <v>1112.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2948.4</v>
+        <v>3609.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>64.5</v>
+        <v>69.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1362</v>
+        <v>1293</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>150.71</v>
+        <v>817.8</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>141</v>
       </c>
       <c r="H6" t="n">
-        <v>256.5</v>
+        <v>376.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>976.8</v>
+        <v>2231.1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>126</v>
+        <v>193.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5062.5</v>
+        <v>5992.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>362.06</v>
+        <v>1964.66</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>117</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>240.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>306</v>
+        <v>702</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>2173.5</v>
+        <v>2856</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>74.12</v>
+        <v>402.19</v>
       </c>
     </row>
     <row r="8">
@@ -11129,13 +11129,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>445.5</v>
+        <v>931.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.67</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>132</v>
+        <v>297</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.91</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5047920</v>
+        <v>6340680</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>530712</v>
+        <v>649782</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10965</v>
+        <v>11781</v>
       </c>
       <c r="O5" t="n">
-        <v>231540</v>
+        <v>219810</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>90425.64999999999</v>
+        <v>490681.8</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>7614</v>
       </c>
       <c r="H6" t="n">
-        <v>1462050</v>
+        <v>2144340</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>175824</v>
+        <v>401598</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>21420</v>
+        <v>32895</v>
       </c>
       <c r="O6" t="n">
-        <v>860625</v>
+        <v>1018725</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>217234.71</v>
+        <v>1178793</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>6318</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1373130</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>55080</v>
+        <v>126360</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1785</v>
+        <v>14637</v>
       </c>
       <c r="O7" t="n">
-        <v>369495</v>
+        <v>485520</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>44470.94</v>
+        <v>241315.2</v>
       </c>
     </row>
     <row r="8">
@@ -12421,13 +12421,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>75735</v>
+        <v>158355</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8801.540000000001</v>
+        <v>47760.3</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>22440</v>
+        <v>50490</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1148.69</v>
+        <v>6233.22</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>97740</v>
       </c>
       <c r="H4" t="n">
-        <v>10050</v>
+        <v>11640</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -13492,19 +13492,19 @@
         <v>124</v>
       </c>
       <c r="L4" t="n">
-        <v>218280</v>
+        <v>212460</v>
       </c>
       <c r="M4" t="n">
-        <v>18540</v>
+        <v>1470</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>37890</v>
+        <v>41250</v>
       </c>
       <c r="P4" t="n">
-        <v>32700</v>
+        <v>6720</v>
       </c>
       <c r="Q4" t="n">
         <v>41176.38</v>
@@ -13533,7 +13533,7 @@
         <v>97020</v>
       </c>
       <c r="H5" t="n">
-        <v>12750</v>
+        <v>12840</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -13545,19 +13545,19 @@
         <v>99</v>
       </c>
       <c r="L5" t="n">
-        <v>252630</v>
+        <v>239400</v>
       </c>
       <c r="M5" t="n">
-        <v>14850</v>
+        <v>5250</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>38940</v>
+        <v>44670</v>
       </c>
       <c r="P5" t="n">
-        <v>41670</v>
+        <v>23670</v>
       </c>
       <c r="Q5" t="n">
         <v>50416.86</v>
@@ -13586,7 +13586,7 @@
         <v>67590</v>
       </c>
       <c r="H6" t="n">
-        <v>5640</v>
+        <v>6450</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -13598,19 +13598,19 @@
         <v>39</v>
       </c>
       <c r="L6" t="n">
-        <v>147120</v>
+        <v>140880</v>
       </c>
       <c r="M6" t="n">
-        <v>6870</v>
+        <v>4890</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>27930</v>
+        <v>27900</v>
       </c>
       <c r="P6" t="n">
-        <v>37230</v>
+        <v>31350</v>
       </c>
       <c r="Q6" t="n">
         <v>38383.7</v>
@@ -13639,7 +13639,7 @@
         <v>41550</v>
       </c>
       <c r="H7" t="n">
-        <v>780</v>
+        <v>600</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -13651,19 +13651,19 @@
         <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>72240</v>
+        <v>76110</v>
       </c>
       <c r="M7" t="n">
-        <v>3420</v>
+        <v>8880</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>26850</v>
+        <v>29130</v>
       </c>
       <c r="P7" t="n">
-        <v>32640</v>
+        <v>29700</v>
       </c>
       <c r="Q7" t="n">
         <v>27621.33</v>
@@ -13692,7 +13692,7 @@
         <v>12690</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>480</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -13704,19 +13704,19 @@
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>37620</v>
+        <v>44400</v>
       </c>
       <c r="M8" t="n">
-        <v>2400</v>
+        <v>11130</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>9690</v>
+        <v>14100</v>
       </c>
       <c r="P8" t="n">
-        <v>38130</v>
+        <v>42240</v>
       </c>
       <c r="Q8" t="n">
         <v>12082.26</v>
@@ -13757,19 +13757,19 @@
         <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>9030</v>
+        <v>22260</v>
       </c>
       <c r="M9" t="n">
-        <v>990</v>
+        <v>13350</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>690</v>
+        <v>1800</v>
       </c>
       <c r="P9" t="n">
-        <v>38610</v>
+        <v>41850</v>
       </c>
       <c r="Q9" t="n">
         <v>1267.78</v>
@@ -13810,10 +13810,10 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>4230</v>
+        <v>24660</v>
       </c>
       <c r="M10" t="n">
-        <v>360</v>
+        <v>10380</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -13822,7 +13822,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>34740</v>
+        <v>54930</v>
       </c>
       <c r="Q10" t="n">
         <v>290.94</v>
@@ -13863,19 +13863,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3720</v>
+        <v>25440</v>
       </c>
       <c r="M11" t="n">
-        <v>240</v>
+        <v>12660</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>25890</v>
+        <v>49260</v>
       </c>
       <c r="Q11" t="n">
         <v>271.86</v>
@@ -13904,7 +13904,7 @@
         <v>360</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,10 +13916,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2280</v>
+        <v>16590</v>
       </c>
       <c r="M12" t="n">
-        <v>510</v>
+        <v>2760</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>15600</v>
+        <v>27180</v>
       </c>
       <c r="Q12" t="n">
         <v>57.81</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>6420</v>
       </c>
       <c r="M13" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>11820</v>
+        <v>13110</v>
       </c>
       <c r="Q13" t="n">
         <v>18.08</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>270</v>
+        <v>6000</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>15360</v>
+        <v>28290</v>
       </c>
       <c r="Q14" t="n">
         <v>22.1</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>450</v>
+        <v>2670</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6330</v>
+        <v>17640</v>
       </c>
       <c r="Q15" t="n">
         <v>9.93</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>510</v>
+        <v>2520</v>
       </c>
       <c r="M16" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3150</v>
+        <v>6840</v>
       </c>
       <c r="Q16" t="n">
         <v>5.36</v>
@@ -14181,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>330</v>
+        <v>1110</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>540</v>
+        <v>900</v>
       </c>
       <c r="Q17" t="n">
         <v>0.89</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>25704</v>
+        <v>27594</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -14837,22 +14837,22 @@
         <v>80.09999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>191022.3</v>
+        <v>196963.2</v>
       </c>
       <c r="M5" t="n">
-        <v>888</v>
+        <v>784.8</v>
       </c>
       <c r="N5" t="n">
-        <v>216</v>
+        <v>313.8</v>
       </c>
       <c r="O5" t="n">
-        <v>8641.5</v>
+        <v>9715.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1411.2</v>
+        <v>973.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>7054.62</v>
+        <v>73106.35000000001</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>12441</v>
       </c>
       <c r="H6" t="n">
-        <v>12021.3</v>
+        <v>13543.2</v>
       </c>
       <c r="I6" t="n">
         <v>2.03</v>
@@ -14890,22 +14890,22 @@
         <v>60.33</v>
       </c>
       <c r="L6" t="n">
-        <v>219047.4</v>
+        <v>228460.2</v>
       </c>
       <c r="M6" t="n">
-        <v>1720.8</v>
+        <v>2335.2</v>
       </c>
       <c r="N6" t="n">
-        <v>253.5</v>
+        <v>463.5</v>
       </c>
       <c r="O6" t="n">
-        <v>25350</v>
+        <v>29175</v>
       </c>
       <c r="P6" t="n">
-        <v>10318.5</v>
+        <v>7987.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>78394.00999999999</v>
+        <v>812389.5</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>22981.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3766.8</v>
+        <v>4730.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -14943,22 +14943,22 @@
         <v>56.78</v>
       </c>
       <c r="L7" t="n">
-        <v>215946</v>
+        <v>238320</v>
       </c>
       <c r="M7" t="n">
-        <v>4651.5</v>
+        <v>10416</v>
       </c>
       <c r="N7" t="n">
-        <v>48.3</v>
+        <v>205.8</v>
       </c>
       <c r="O7" t="n">
-        <v>25378.5</v>
+        <v>28203</v>
       </c>
       <c r="P7" t="n">
-        <v>18262.5</v>
+        <v>14955</v>
       </c>
       <c r="Q7" t="n">
-        <v>66123.71000000001</v>
+        <v>685233.65</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>74529</v>
       </c>
       <c r="H8" t="n">
-        <v>4590</v>
+        <v>4743</v>
       </c>
       <c r="I8" t="n">
         <v>2.21</v>
@@ -14996,22 +14996,22 @@
         <v>32.38</v>
       </c>
       <c r="L8" t="n">
-        <v>176193.6</v>
+        <v>195853.5</v>
       </c>
       <c r="M8" t="n">
-        <v>5478</v>
+        <v>18199.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>14499</v>
+        <v>23490</v>
       </c>
       <c r="P8" t="n">
-        <v>30415.2</v>
+        <v>29822.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>53919.97</v>
+        <v>558767.4300000001</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>65688</v>
       </c>
       <c r="H9" t="n">
-        <v>4260</v>
+        <v>4920</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>25.7</v>
       </c>
       <c r="L9" t="n">
-        <v>155835.9</v>
+        <v>183440.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3591</v>
+        <v>19887</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5181</v>
+        <v>11665.5</v>
       </c>
       <c r="P9" t="n">
-        <v>41130</v>
+        <v>47265</v>
       </c>
       <c r="Q9" t="n">
-        <v>34426.84</v>
+        <v>356762.04</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>46170</v>
       </c>
       <c r="H10" t="n">
-        <v>1290</v>
+        <v>1770</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,22 +15102,22 @@
         <v>10.44</v>
       </c>
       <c r="L10" t="n">
-        <v>102154.2</v>
+        <v>146235.9</v>
       </c>
       <c r="M10" t="n">
-        <v>2550</v>
+        <v>21777</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2835</v>
+        <v>8442</v>
       </c>
       <c r="P10" t="n">
-        <v>61404</v>
+        <v>94809</v>
       </c>
       <c r="Q10" t="n">
-        <v>23049.98</v>
+        <v>238864.67</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>29940</v>
       </c>
       <c r="H11" t="n">
-        <v>930</v>
+        <v>1080</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -15155,22 +15155,22 @@
         <v>0.9</v>
       </c>
       <c r="L11" t="n">
-        <v>53850</v>
+        <v>93090</v>
       </c>
       <c r="M11" t="n">
-        <v>2808</v>
+        <v>20601</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3264</v>
+        <v>3850.5</v>
       </c>
       <c r="P11" t="n">
-        <v>44901</v>
+        <v>75060</v>
       </c>
       <c r="Q11" t="n">
-        <v>13515.65</v>
+        <v>140061.4</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>10710</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>510</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>19830</v>
+        <v>45630</v>
       </c>
       <c r="M12" t="n">
-        <v>1738.5</v>
+        <v>11799</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>570</v>
+        <v>1170</v>
       </c>
       <c r="P12" t="n">
-        <v>36990</v>
+        <v>60420</v>
       </c>
       <c r="Q12" t="n">
-        <v>6482.84</v>
+        <v>67181.09</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>2430</v>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,22 +15261,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8310</v>
+        <v>24360</v>
       </c>
       <c r="M13" t="n">
-        <v>990</v>
+        <v>6570</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="P13" t="n">
-        <v>29190</v>
+        <v>35250</v>
       </c>
       <c r="Q13" t="n">
-        <v>2628.4</v>
+        <v>27237.89</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>1890</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -15314,10 +15314,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2940</v>
+        <v>13950</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>1650</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -15326,10 +15326,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>39990</v>
+        <v>55650</v>
       </c>
       <c r="Q14" t="n">
-        <v>1806.8</v>
+        <v>18723.73</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>420</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4380</v>
+        <v>10020</v>
       </c>
       <c r="M15" t="n">
-        <v>2700</v>
+        <v>3690</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>22200</v>
+        <v>40740</v>
       </c>
       <c r="Q15" t="n">
-        <v>775.95</v>
+        <v>8041.14</v>
       </c>
     </row>
     <row r="16">
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1320</v>
+        <v>5310</v>
       </c>
       <c r="M16" t="n">
-        <v>870</v>
+        <v>2190</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>15240</v>
+        <v>16740</v>
       </c>
       <c r="Q16" t="n">
-        <v>357.23</v>
+        <v>3701.96</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>3960</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,22 +15473,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1080</v>
+        <v>4950</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P17" t="n">
-        <v>22680</v>
+        <v>38790</v>
       </c>
       <c r="Q17" t="n">
-        <v>224.99</v>
+        <v>2331.5</v>
       </c>
     </row>
     <row r="18">
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>600</v>
+        <v>3510</v>
       </c>
       <c r="Q18" t="n">
-        <v>27.45</v>
+        <v>284.5</v>
       </c>
     </row>
     <row r="19">
@@ -15582,7 +15582,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.59</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="20">
@@ -15635,7 +15635,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15647,7 +15647,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.45</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="21">
@@ -15688,7 +15688,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.03</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="22">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4590</v>
+        <v>4622.4</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -16129,19 +16129,19 @@
         <v>32.77</v>
       </c>
       <c r="L5" t="n">
-        <v>53052.3</v>
+        <v>50274</v>
       </c>
       <c r="M5" t="n">
-        <v>297</v>
+        <v>105</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1947</v>
+        <v>2233.5</v>
       </c>
       <c r="P5" t="n">
-        <v>833.4</v>
+        <v>473.4</v>
       </c>
       <c r="Q5" t="n">
         <v>2520.84</v>
@@ -16170,7 +16170,7 @@
         <v>3379.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3214.8</v>
+        <v>3676.5</v>
       </c>
       <c r="I6" t="n">
         <v>1.01</v>
@@ -16182,19 +16182,19 @@
         <v>19.77</v>
       </c>
       <c r="L6" t="n">
-        <v>54434.4</v>
+        <v>52125.6</v>
       </c>
       <c r="M6" t="n">
-        <v>549.6</v>
+        <v>391.2</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6982.5</v>
+        <v>6975</v>
       </c>
       <c r="P6" t="n">
-        <v>5584.5</v>
+        <v>4702.5</v>
       </c>
       <c r="Q6" t="n">
         <v>28787.78</v>
@@ -16223,7 +16223,7 @@
         <v>6232.5</v>
       </c>
       <c r="H7" t="n">
-        <v>569.4</v>
+        <v>438</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -16235,19 +16235,19 @@
         <v>18.5</v>
       </c>
       <c r="L7" t="n">
-        <v>43344</v>
+        <v>45666</v>
       </c>
       <c r="M7" t="n">
-        <v>1197</v>
+        <v>3108</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>9397.5</v>
+        <v>10195.5</v>
       </c>
       <c r="P7" t="n">
-        <v>8160</v>
+        <v>7425</v>
       </c>
       <c r="Q7" t="n">
         <v>22097.07</v>
@@ -16276,7 +16276,7 @@
         <v>8248.5</v>
       </c>
       <c r="H8" t="n">
-        <v>51</v>
+        <v>408</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -16288,19 +16288,19 @@
         <v>4.42</v>
       </c>
       <c r="L8" t="n">
-        <v>26710.2</v>
+        <v>31524</v>
       </c>
       <c r="M8" t="n">
-        <v>1320</v>
+        <v>6121.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4360.5</v>
+        <v>6345</v>
       </c>
       <c r="P8" t="n">
-        <v>14489.4</v>
+        <v>16051.2</v>
       </c>
       <c r="Q8" t="n">
         <v>11478.15</v>
@@ -16341,19 +16341,19 @@
         <v>2.41</v>
       </c>
       <c r="L9" t="n">
-        <v>7314.3</v>
+        <v>18030.6</v>
       </c>
       <c r="M9" t="n">
-        <v>693</v>
+        <v>9345</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>379.5</v>
+        <v>990</v>
       </c>
       <c r="P9" t="n">
-        <v>19305</v>
+        <v>20925</v>
       </c>
       <c r="Q9" t="n">
         <v>1229.74</v>
@@ -16394,10 +16394,10 @@
         <v>0.87</v>
       </c>
       <c r="L10" t="n">
-        <v>3764.7</v>
+        <v>21947.4</v>
       </c>
       <c r="M10" t="n">
-        <v>306</v>
+        <v>8823</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>29529</v>
+        <v>46690.5</v>
       </c>
       <c r="Q10" t="n">
         <v>290.94</v>
@@ -16447,19 +16447,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3720</v>
+        <v>25440</v>
       </c>
       <c r="M11" t="n">
-        <v>216</v>
+        <v>11394</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="P11" t="n">
-        <v>23301</v>
+        <v>44334</v>
       </c>
       <c r="Q11" t="n">
         <v>271.86</v>
@@ -16488,7 +16488,7 @@
         <v>360</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,10 +16500,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2280</v>
+        <v>16590</v>
       </c>
       <c r="M12" t="n">
-        <v>484.5</v>
+        <v>2622</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>15600</v>
+        <v>27180</v>
       </c>
       <c r="Q12" t="n">
         <v>57.81</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>6420</v>
       </c>
       <c r="M13" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>11820</v>
+        <v>13110</v>
       </c>
       <c r="Q13" t="n">
         <v>18.08</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>270</v>
+        <v>6000</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>15360</v>
+        <v>28290</v>
       </c>
       <c r="Q14" t="n">
         <v>22.1</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>450</v>
+        <v>2670</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6330</v>
+        <v>17640</v>
       </c>
       <c r="Q15" t="n">
         <v>9.93</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>510</v>
+        <v>2520</v>
       </c>
       <c r="M16" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3150</v>
+        <v>6840</v>
       </c>
       <c r="Q16" t="n">
         <v>5.36</v>
@@ -16765,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>330</v>
+        <v>1110</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>540</v>
+        <v>900</v>
       </c>
       <c r="Q17" t="n">
         <v>0.89</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>26163000</v>
+        <v>26347680</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -17421,19 +17421,19 @@
         <v>1591131.56</v>
       </c>
       <c r="L5" t="n">
-        <v>9549414</v>
+        <v>9049320</v>
       </c>
       <c r="M5" t="n">
-        <v>103950</v>
+        <v>36750</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>330990</v>
+        <v>379695</v>
       </c>
       <c r="P5" t="n">
-        <v>54171</v>
+        <v>30771</v>
       </c>
       <c r="Q5" t="n">
         <v>1512505.87</v>
@@ -17462,7 +17462,7 @@
         <v>182493</v>
       </c>
       <c r="H6" t="n">
-        <v>18324360</v>
+        <v>20956050</v>
       </c>
       <c r="I6" t="n">
         <v>196943.14</v>
@@ -17474,19 +17474,19 @@
         <v>960097.79</v>
       </c>
       <c r="L6" t="n">
-        <v>9798192</v>
+        <v>9382608</v>
       </c>
       <c r="M6" t="n">
-        <v>192360</v>
+        <v>136920</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1187025</v>
+        <v>1185750</v>
       </c>
       <c r="P6" t="n">
-        <v>362992.5</v>
+        <v>305662.5</v>
       </c>
       <c r="Q6" t="n">
         <v>17272666.8</v>
@@ -17515,7 +17515,7 @@
         <v>336555</v>
       </c>
       <c r="H7" t="n">
-        <v>3245580</v>
+        <v>2496600</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -17527,19 +17527,19 @@
         <v>898383.11</v>
       </c>
       <c r="L7" t="n">
-        <v>7801920</v>
+        <v>8219880</v>
       </c>
       <c r="M7" t="n">
-        <v>418950</v>
+        <v>1087800</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1597575</v>
+        <v>1733235</v>
       </c>
       <c r="P7" t="n">
-        <v>530400</v>
+        <v>482625</v>
       </c>
       <c r="Q7" t="n">
         <v>13258240.7</v>
@@ -17568,7 +17568,7 @@
         <v>445419</v>
       </c>
       <c r="H8" t="n">
-        <v>290700</v>
+        <v>2325600</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -17580,19 +17580,19 @@
         <v>214423.3</v>
       </c>
       <c r="L8" t="n">
-        <v>4807836</v>
+        <v>5674320</v>
       </c>
       <c r="M8" t="n">
-        <v>462000</v>
+        <v>2142525</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>741285</v>
+        <v>1078650</v>
       </c>
       <c r="P8" t="n">
-        <v>941811</v>
+        <v>1043328</v>
       </c>
       <c r="Q8" t="n">
         <v>6886889.57</v>
@@ -17633,19 +17633,19 @@
         <v>116971.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1316574</v>
+        <v>3245508</v>
       </c>
       <c r="M9" t="n">
-        <v>242550</v>
+        <v>3270750</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>64515</v>
+        <v>168300</v>
       </c>
       <c r="P9" t="n">
-        <v>1254825</v>
+        <v>1360125</v>
       </c>
       <c r="Q9" t="n">
         <v>737845.63</v>
@@ -17686,10 +17686,10 @@
         <v>42243.72</v>
       </c>
       <c r="L10" t="n">
-        <v>677646</v>
+        <v>3950532</v>
       </c>
       <c r="M10" t="n">
-        <v>107100</v>
+        <v>3088050</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -17698,7 +17698,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1919385</v>
+        <v>3034882.5</v>
       </c>
       <c r="Q10" t="n">
         <v>174564.72</v>
@@ -17739,19 +17739,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>669600</v>
+        <v>4579200</v>
       </c>
       <c r="M11" t="n">
-        <v>75600</v>
+        <v>3987900</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="P11" t="n">
-        <v>1514565</v>
+        <v>2881710</v>
       </c>
       <c r="Q11" t="n">
         <v>163114.56</v>
@@ -17780,7 +17780,7 @@
         <v>19440</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,10 +17792,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>410400</v>
+        <v>2986200</v>
       </c>
       <c r="M12" t="n">
-        <v>169575</v>
+        <v>917700</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -17804,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1014000</v>
+        <v>1766700</v>
       </c>
       <c r="Q12" t="n">
         <v>34685.28</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>156600</v>
+        <v>1155600</v>
       </c>
       <c r="M13" t="n">
-        <v>52500</v>
+        <v>420000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>768300</v>
+        <v>852150</v>
       </c>
       <c r="Q13" t="n">
         <v>10847.52</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>48600</v>
+        <v>1080000</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>998400</v>
+        <v>1838850</v>
       </c>
       <c r="Q14" t="n">
         <v>13258.08</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>81000</v>
+        <v>480600</v>
       </c>
       <c r="M15" t="n">
-        <v>10500</v>
+        <v>31500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>411450</v>
+        <v>1146600</v>
       </c>
       <c r="Q15" t="n">
         <v>5959.44</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>91800</v>
+        <v>453600</v>
       </c>
       <c r="M16" t="n">
-        <v>105000</v>
+        <v>126000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>204750</v>
+        <v>444600</v>
       </c>
       <c r="Q16" t="n">
         <v>3214.08</v>
@@ -18057,7 +18057,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>59400</v>
+        <v>199800</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>35100</v>
+        <v>58500</v>
       </c>
       <c r="Q17" t="n">
         <v>535.6799999999999</v>
@@ -18648,7 +18648,7 @@
         <v>62070</v>
       </c>
       <c r="H4" t="n">
-        <v>4470</v>
+        <v>6120</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>225420</v>
+        <v>267960</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2370</v>
+        <v>2610</v>
       </c>
       <c r="O4" t="n">
-        <v>48240</v>
+        <v>53190</v>
       </c>
       <c r="P4" t="n">
-        <v>5520</v>
+        <v>2130</v>
       </c>
       <c r="Q4" t="n">
-        <v>21234.96</v>
+        <v>243317.25</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>13050</v>
       </c>
       <c r="H5" t="n">
-        <v>1140</v>
+        <v>1530</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>62580</v>
+        <v>81930</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1020</v>
+        <v>1860</v>
       </c>
       <c r="O5" t="n">
-        <v>21870</v>
+        <v>31200</v>
       </c>
       <c r="P5" t="n">
-        <v>4170</v>
+        <v>6600</v>
       </c>
       <c r="Q5" t="n">
-        <v>5350.58</v>
+        <v>61308.72</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>1500</v>
       </c>
       <c r="H6" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10350</v>
+        <v>17760</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>420</v>
       </c>
       <c r="O6" t="n">
-        <v>3390</v>
+        <v>5490</v>
       </c>
       <c r="P6" t="n">
-        <v>2730</v>
+        <v>5610</v>
       </c>
       <c r="Q6" t="n">
-        <v>506.04</v>
+        <v>5798.43</v>
       </c>
     </row>
     <row r="7">
@@ -18819,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>630</v>
+        <v>2610</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -18828,13 +18828,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="P7" t="n">
-        <v>3060</v>
+        <v>7530</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.75</v>
+        <v>993.96</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>960</v>
+        <v>3600</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.05</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="9">
@@ -18925,22 +18925,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>180</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>90</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>30</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>410.4</v>
+        <v>550.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>13141.8</v>
+        <v>17205.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10.2</v>
+        <v>18.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1093.5</v>
+        <v>1560</v>
       </c>
       <c r="P5" t="n">
-        <v>83.40000000000001</v>
+        <v>132</v>
       </c>
       <c r="Q5" t="n">
-        <v>267.53</v>
+        <v>3065.44</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>75</v>
       </c>
       <c r="H6" t="n">
-        <v>119.7</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3829.5</v>
+        <v>6571.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="O6" t="n">
-        <v>847.5</v>
+        <v>1372.5</v>
       </c>
       <c r="P6" t="n">
-        <v>409.5</v>
+        <v>841.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>379.53</v>
+        <v>4348.82</v>
       </c>
     </row>
     <row r="7">
@@ -20111,7 +20111,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>378</v>
+        <v>1566</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -20120,13 +20120,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>21</v>
+        <v>115.5</v>
       </c>
       <c r="P7" t="n">
-        <v>765</v>
+        <v>1882.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>69.40000000000001</v>
+        <v>795.17</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>127.8</v>
+        <v>340.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>364.8</v>
+        <v>1368</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.75</v>
+        <v>65.83</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>72.90000000000001</v>
+        <v>145.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>160.2</v>
+        <v>186.9</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2339280</v>
+        <v>3139560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>2365524</v>
+        <v>3096954</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1734</v>
+        <v>3162</v>
       </c>
       <c r="O5" t="n">
-        <v>185895</v>
+        <v>265200</v>
       </c>
       <c r="P5" t="n">
-        <v>5421</v>
+        <v>8580</v>
       </c>
       <c r="Q5" t="n">
-        <v>160517.38</v>
+        <v>1839261.6</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>4050</v>
       </c>
       <c r="H6" t="n">
-        <v>682290</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>689310</v>
+        <v>1182816</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>255</v>
+        <v>3570</v>
       </c>
       <c r="O6" t="n">
-        <v>144075</v>
+        <v>233325</v>
       </c>
       <c r="P6" t="n">
-        <v>26617.5</v>
+        <v>54697.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>227720.16</v>
+        <v>2609293.5</v>
       </c>
     </row>
     <row r="7">
@@ -21403,7 +21403,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>68040</v>
+        <v>281880</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -21412,13 +21412,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3570</v>
+        <v>19635</v>
       </c>
       <c r="P7" t="n">
-        <v>49725</v>
+        <v>122362.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>41637.89</v>
+        <v>477100.8</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>23004</v>
+        <v>61344</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>23712</v>
+        <v>88920</v>
       </c>
       <c r="Q8" t="n">
-        <v>3447.36</v>
+        <v>39501</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13122</v>
+        <v>26244</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28836</v>
+        <v>33642</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>16200</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>146512800</v>
+        <v>157285800</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -22589,22 +22589,22 @@
         <v>3889432.71</v>
       </c>
       <c r="L5" t="n">
-        <v>34384014</v>
+        <v>35453376</v>
       </c>
       <c r="M5" t="n">
-        <v>310800</v>
+        <v>274680</v>
       </c>
       <c r="N5" t="n">
-        <v>36720</v>
+        <v>53346</v>
       </c>
       <c r="O5" t="n">
-        <v>1469055</v>
+        <v>1651635</v>
       </c>
       <c r="P5" t="n">
-        <v>91728</v>
+        <v>63258</v>
       </c>
       <c r="Q5" t="n">
-        <v>4232772.61</v>
+        <v>43863812.96</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>671814</v>
       </c>
       <c r="H6" t="n">
-        <v>68521410</v>
+        <v>77196240</v>
       </c>
       <c r="I6" t="n">
         <v>393886.27</v>
@@ -22642,22 +22642,22 @@
         <v>2929529.15</v>
       </c>
       <c r="L6" t="n">
-        <v>39428532</v>
+        <v>41122836</v>
       </c>
       <c r="M6" t="n">
-        <v>602280</v>
+        <v>817320</v>
       </c>
       <c r="N6" t="n">
-        <v>43095</v>
+        <v>78795</v>
       </c>
       <c r="O6" t="n">
-        <v>4309500</v>
+        <v>4959750</v>
       </c>
       <c r="P6" t="n">
-        <v>670702.5</v>
+        <v>519187.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>47036403.54</v>
+        <v>487433697.98</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1241001</v>
       </c>
       <c r="H7" t="n">
-        <v>21470760</v>
+        <v>26963280</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22695,22 +22695,22 @@
         <v>2757106.79</v>
       </c>
       <c r="L7" t="n">
-        <v>38870280</v>
+        <v>42897600</v>
       </c>
       <c r="M7" t="n">
-        <v>1628025</v>
+        <v>3645600</v>
       </c>
       <c r="N7" t="n">
-        <v>8211</v>
+        <v>34986</v>
       </c>
       <c r="O7" t="n">
-        <v>4314345</v>
+        <v>4794510</v>
       </c>
       <c r="P7" t="n">
-        <v>1187062.5</v>
+        <v>972075</v>
       </c>
       <c r="Q7" t="n">
-        <v>39674228.54</v>
+        <v>411140190.96</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>4024566</v>
       </c>
       <c r="H8" t="n">
-        <v>26163000</v>
+        <v>27035100</v>
       </c>
       <c r="I8" t="n">
         <v>428846.59</v>
@@ -22748,22 +22748,22 @@
         <v>1572437.5</v>
       </c>
       <c r="L8" t="n">
-        <v>31714848</v>
+        <v>35253630</v>
       </c>
       <c r="M8" t="n">
-        <v>1917300</v>
+        <v>6369825</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O8" t="n">
-        <v>2464830</v>
+        <v>3993300</v>
       </c>
       <c r="P8" t="n">
-        <v>1976988</v>
+        <v>1938456</v>
       </c>
       <c r="Q8" t="n">
-        <v>32351981.8</v>
+        <v>335260456.52</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>3547152</v>
       </c>
       <c r="H9" t="n">
-        <v>24282000</v>
+        <v>28044000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>1247694.98</v>
       </c>
       <c r="L9" t="n">
-        <v>28050462</v>
+        <v>33019326</v>
       </c>
       <c r="M9" t="n">
-        <v>1256850</v>
+        <v>6960450</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>880770</v>
+        <v>1983135</v>
       </c>
       <c r="P9" t="n">
-        <v>2673450</v>
+        <v>3072225</v>
       </c>
       <c r="Q9" t="n">
-        <v>20656105.38</v>
+        <v>214057221.08</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>2493180</v>
       </c>
       <c r="H10" t="n">
-        <v>7353000</v>
+        <v>10089000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
         <v>506924.64</v>
       </c>
       <c r="L10" t="n">
-        <v>18387756</v>
+        <v>26322462</v>
       </c>
       <c r="M10" t="n">
-        <v>892500</v>
+        <v>7621950</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>481950</v>
+        <v>1435140</v>
       </c>
       <c r="P10" t="n">
-        <v>3991260</v>
+        <v>6162585</v>
       </c>
       <c r="Q10" t="n">
-        <v>13829985.36</v>
+        <v>143318799.9</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>1616760</v>
       </c>
       <c r="H11" t="n">
-        <v>5301000</v>
+        <v>6156000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -22907,22 +22907,22 @@
         <v>43627.57</v>
       </c>
       <c r="L11" t="n">
-        <v>9693000</v>
+        <v>16756200</v>
       </c>
       <c r="M11" t="n">
-        <v>982800</v>
+        <v>7210350</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>554880</v>
+        <v>654585</v>
       </c>
       <c r="P11" t="n">
-        <v>2918565</v>
+        <v>4878900</v>
       </c>
       <c r="Q11" t="n">
-        <v>8109391.68</v>
+        <v>84036841.2</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>578340</v>
       </c>
       <c r="H12" t="n">
-        <v>855000</v>
+        <v>2907000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3569400</v>
+        <v>8213400</v>
       </c>
       <c r="M12" t="n">
-        <v>608475</v>
+        <v>4129650</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>96900</v>
+        <v>198900</v>
       </c>
       <c r="P12" t="n">
-        <v>2404350</v>
+        <v>3927300</v>
       </c>
       <c r="Q12" t="n">
-        <v>3889706.4</v>
+        <v>40308651</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>131220</v>
       </c>
       <c r="H13" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,22 +23013,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1495800</v>
+        <v>4384800</v>
       </c>
       <c r="M13" t="n">
-        <v>346500</v>
+        <v>2299500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>15300</v>
+        <v>45900</v>
       </c>
       <c r="P13" t="n">
-        <v>1897350</v>
+        <v>2291250</v>
       </c>
       <c r="Q13" t="n">
-        <v>1577041.92</v>
+        <v>16342732.8</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>102060</v>
       </c>
       <c r="H14" t="n">
-        <v>513000</v>
+        <v>342000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23066,10 +23066,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>529200</v>
+        <v>2511000</v>
       </c>
       <c r="M14" t="n">
-        <v>52500</v>
+        <v>577500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -23078,10 +23078,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2599350</v>
+        <v>3617250</v>
       </c>
       <c r="Q14" t="n">
-        <v>1084082.4</v>
+        <v>11234241</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>22680</v>
       </c>
       <c r="H15" t="n">
-        <v>342000</v>
+        <v>1197000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>788400</v>
+        <v>1803600</v>
       </c>
       <c r="M15" t="n">
-        <v>945000</v>
+        <v>1291500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P15" t="n">
-        <v>1443000</v>
+        <v>2648100</v>
       </c>
       <c r="Q15" t="n">
-        <v>465572.88</v>
+        <v>4824686.7</v>
       </c>
     </row>
     <row r="16">
@@ -23172,10 +23172,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>237600</v>
+        <v>955800</v>
       </c>
       <c r="M16" t="n">
-        <v>304500</v>
+        <v>766500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23184,10 +23184,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>990600</v>
+        <v>1088100</v>
       </c>
       <c r="Q16" t="n">
-        <v>214338.96</v>
+        <v>2221173.9</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>213840</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,22 +23225,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>194400</v>
+        <v>891000</v>
       </c>
       <c r="M17" t="n">
-        <v>42000</v>
+        <v>504000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P17" t="n">
-        <v>1474200</v>
+        <v>2521350</v>
       </c>
       <c r="Q17" t="n">
-        <v>134991.36</v>
+        <v>1398902.4</v>
       </c>
     </row>
     <row r="18">
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>42000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>39000</v>
+        <v>228150</v>
       </c>
       <c r="Q18" t="n">
-        <v>16472.16</v>
+        <v>170699.4</v>
       </c>
     </row>
     <row r="19">
@@ -23334,7 +23334,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5155.92</v>
+        <v>53430.3</v>
       </c>
     </row>
     <row r="20">
@@ -23387,7 +23387,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23399,7 +23399,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>870.48</v>
+        <v>9020.700000000001</v>
       </c>
     </row>
     <row r="21">
@@ -23440,7 +23440,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>52500</v>
+        <v>105000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -23452,7 +23452,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4218.48</v>
+        <v>43715.7</v>
       </c>
     </row>
     <row r="22">
@@ -23816,7 +23816,7 @@
         <v>68970</v>
       </c>
       <c r="H4" t="n">
-        <v>15750</v>
+        <v>14910</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -23828,22 +23828,22 @@
         <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>198180</v>
+        <v>184230</v>
       </c>
       <c r="M4" t="n">
-        <v>30900</v>
+        <v>42150</v>
       </c>
       <c r="N4" t="n">
-        <v>19020</v>
+        <v>20190</v>
       </c>
       <c r="O4" t="n">
-        <v>15090</v>
+        <v>14820</v>
       </c>
       <c r="P4" t="n">
-        <v>3600</v>
+        <v>1260</v>
       </c>
       <c r="Q4" t="n">
-        <v>17967.37</v>
+        <v>176150.7</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>92580</v>
       </c>
       <c r="H5" t="n">
-        <v>23070</v>
+        <v>25560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>68</v>
       </c>
       <c r="L5" t="n">
-        <v>269340</v>
+        <v>267420</v>
       </c>
       <c r="M5" t="n">
-        <v>10590</v>
+        <v>23580</v>
       </c>
       <c r="N5" t="n">
-        <v>6900</v>
+        <v>11610</v>
       </c>
       <c r="O5" t="n">
-        <v>24660</v>
+        <v>25740</v>
       </c>
       <c r="P5" t="n">
-        <v>5040</v>
+        <v>3390</v>
       </c>
       <c r="Q5" t="n">
-        <v>29902.11</v>
+        <v>293157.9</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>103650</v>
       </c>
       <c r="H6" t="n">
-        <v>3240</v>
+        <v>3780</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -23934,22 +23934,22 @@
         <v>57</v>
       </c>
       <c r="L6" t="n">
-        <v>259890</v>
+        <v>269880</v>
       </c>
       <c r="M6" t="n">
-        <v>4890</v>
+        <v>15420</v>
       </c>
       <c r="N6" t="n">
-        <v>1050</v>
+        <v>2190</v>
       </c>
       <c r="O6" t="n">
-        <v>22530</v>
+        <v>25500</v>
       </c>
       <c r="P6" t="n">
-        <v>6750</v>
+        <v>5310</v>
       </c>
       <c r="Q6" t="n">
-        <v>30518.91</v>
+        <v>299205</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>82380</v>
       </c>
       <c r="H7" t="n">
-        <v>600</v>
+        <v>780</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23987,22 +23987,22 @@
         <v>57</v>
       </c>
       <c r="L7" t="n">
-        <v>201870</v>
+        <v>221340</v>
       </c>
       <c r="M7" t="n">
-        <v>3660</v>
+        <v>12180</v>
       </c>
       <c r="N7" t="n">
-        <v>180</v>
+        <v>390</v>
       </c>
       <c r="O7" t="n">
-        <v>22440</v>
+        <v>21360</v>
       </c>
       <c r="P7" t="n">
-        <v>9630</v>
+        <v>6210</v>
       </c>
       <c r="Q7" t="n">
-        <v>31515.22</v>
+        <v>308972.7</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>71730</v>
       </c>
       <c r="H8" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>133350</v>
+        <v>150660</v>
       </c>
       <c r="M8" t="n">
-        <v>4530</v>
+        <v>10620</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>18150</v>
+        <v>25920</v>
       </c>
       <c r="P8" t="n">
-        <v>13860</v>
+        <v>7140</v>
       </c>
       <c r="Q8" t="n">
-        <v>26837.36</v>
+        <v>263111.4</v>
       </c>
     </row>
     <row r="9">
@@ -24093,22 +24093,22 @@
         <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>86070</v>
+        <v>99900</v>
       </c>
       <c r="M9" t="n">
-        <v>2940</v>
+        <v>6180</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>7440</v>
+        <v>14670</v>
       </c>
       <c r="P9" t="n">
-        <v>14670</v>
+        <v>11340</v>
       </c>
       <c r="Q9" t="n">
-        <v>18753.55</v>
+        <v>183858.3</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>17310</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>47520</v>
+        <v>61770</v>
       </c>
       <c r="M10" t="n">
-        <v>1890</v>
+        <v>5280</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4050</v>
+        <v>11700</v>
       </c>
       <c r="P10" t="n">
-        <v>14550</v>
+        <v>13740</v>
       </c>
       <c r="Q10" t="n">
-        <v>11392.1</v>
+        <v>111687.3</v>
       </c>
     </row>
     <row r="11">
@@ -24199,22 +24199,22 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>19740</v>
+        <v>27960</v>
       </c>
       <c r="M11" t="n">
-        <v>2490</v>
+        <v>5160</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3840</v>
+        <v>4500</v>
       </c>
       <c r="P11" t="n">
-        <v>13620</v>
+        <v>12420</v>
       </c>
       <c r="Q11" t="n">
-        <v>7044.64</v>
+        <v>69065.10000000001</v>
       </c>
     </row>
     <row r="12">
@@ -24252,22 +24252,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4470</v>
+        <v>9810</v>
       </c>
       <c r="M12" t="n">
-        <v>900</v>
+        <v>3720</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>570</v>
+        <v>1170</v>
       </c>
       <c r="P12" t="n">
-        <v>13260</v>
+        <v>15600</v>
       </c>
       <c r="Q12" t="n">
-        <v>3093.38</v>
+        <v>30327.3</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1740</v>
+        <v>6420</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>1140</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="P13" t="n">
-        <v>14340</v>
+        <v>15360</v>
       </c>
       <c r="Q13" t="n">
-        <v>892.48</v>
+        <v>8749.799999999999</v>
       </c>
     </row>
     <row r="14">
@@ -24358,10 +24358,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>510</v>
+        <v>3720</v>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -24370,10 +24370,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>23250</v>
+        <v>25050</v>
       </c>
       <c r="Q14" t="n">
-        <v>375.55</v>
+        <v>3681.9</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>270</v>
+        <v>1890</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>15870</v>
+        <v>23100</v>
       </c>
       <c r="Q15" t="n">
-        <v>170.75</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="16">
@@ -24464,10 +24464,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>870</v>
       </c>
       <c r="M16" t="n">
-        <v>570</v>
+        <v>660</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -24476,10 +24476,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12120</v>
+        <v>9930</v>
       </c>
       <c r="Q16" t="n">
-        <v>121.27</v>
+        <v>1188.9</v>
       </c>
     </row>
     <row r="17">
@@ -24517,22 +24517,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>120</v>
+        <v>1860</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P17" t="n">
-        <v>22140</v>
+        <v>37890</v>
       </c>
       <c r="Q17" t="n">
-        <v>121.64</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="18">
@@ -24573,7 +24573,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>600</v>
+        <v>3510</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.96</v>
+        <v>146.7</v>
       </c>
     </row>
     <row r="19">
@@ -24626,7 +24626,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -24638,7 +24638,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.24</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="20">
@@ -24679,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24691,7 +24691,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.19</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="21">
@@ -24732,7 +24732,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -24744,7 +24744,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.78</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="22">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8305.200000000001</v>
+        <v>9201.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>22.51</v>
       </c>
       <c r="L5" t="n">
-        <v>56561.4</v>
+        <v>56158.2</v>
       </c>
       <c r="M5" t="n">
-        <v>211.8</v>
+        <v>471.6</v>
       </c>
       <c r="N5" t="n">
-        <v>69</v>
+        <v>116.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1233</v>
+        <v>1287</v>
       </c>
       <c r="P5" t="n">
-        <v>100.8</v>
+        <v>67.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1495.11</v>
+        <v>14657.9</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>5182.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1846.8</v>
+        <v>2154.6</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -25226,22 +25226,22 @@
         <v>28.9</v>
       </c>
       <c r="L6" t="n">
-        <v>96159.3</v>
+        <v>99855.60000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>391.2</v>
+        <v>1233.6</v>
       </c>
       <c r="N6" t="n">
-        <v>52.5</v>
+        <v>109.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5632.5</v>
+        <v>6375</v>
       </c>
       <c r="P6" t="n">
-        <v>1012.5</v>
+        <v>796.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>22889.18</v>
+        <v>224403.75</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>12357</v>
       </c>
       <c r="H7" t="n">
-        <v>438</v>
+        <v>569.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -25279,22 +25279,22 @@
         <v>36.37</v>
       </c>
       <c r="L7" t="n">
-        <v>121122</v>
+        <v>132804</v>
       </c>
       <c r="M7" t="n">
-        <v>1281</v>
+        <v>4263</v>
       </c>
       <c r="N7" t="n">
-        <v>12.6</v>
+        <v>27.3</v>
       </c>
       <c r="O7" t="n">
-        <v>7854</v>
+        <v>7476</v>
       </c>
       <c r="P7" t="n">
-        <v>2407.5</v>
+        <v>1552.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>25212.17</v>
+        <v>247178.16</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>46624.5</v>
       </c>
       <c r="H8" t="n">
-        <v>229.5</v>
+        <v>382.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>25.02</v>
       </c>
       <c r="L8" t="n">
-        <v>94678.5</v>
+        <v>106968.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2491.5</v>
+        <v>5841</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8167.5</v>
+        <v>11664</v>
       </c>
       <c r="P8" t="n">
-        <v>5266.8</v>
+        <v>2713.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>25495.49</v>
+        <v>249955.83</v>
       </c>
     </row>
     <row r="9">
@@ -25385,22 +25385,22 @@
         <v>19.27</v>
       </c>
       <c r="L9" t="n">
-        <v>69716.7</v>
+        <v>80919</v>
       </c>
       <c r="M9" t="n">
-        <v>2058</v>
+        <v>4326</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4092</v>
+        <v>8068.5</v>
       </c>
       <c r="P9" t="n">
-        <v>7335</v>
+        <v>5670</v>
       </c>
       <c r="Q9" t="n">
-        <v>18190.94</v>
+        <v>178342.55</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>17310</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>4.35</v>
       </c>
       <c r="L10" t="n">
-        <v>42292.8</v>
+        <v>54975.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1606.5</v>
+        <v>4488</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2835</v>
+        <v>8190</v>
       </c>
       <c r="P10" t="n">
-        <v>12367.5</v>
+        <v>11679</v>
       </c>
       <c r="Q10" t="n">
-        <v>11392.1</v>
+        <v>111687.3</v>
       </c>
     </row>
     <row r="11">
@@ -25491,22 +25491,22 @@
         <v>0.9</v>
       </c>
       <c r="L11" t="n">
-        <v>19740</v>
+        <v>27960</v>
       </c>
       <c r="M11" t="n">
-        <v>2241</v>
+        <v>4644</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3264</v>
+        <v>3825</v>
       </c>
       <c r="P11" t="n">
-        <v>12258</v>
+        <v>11178</v>
       </c>
       <c r="Q11" t="n">
-        <v>7044.64</v>
+        <v>69065.10000000001</v>
       </c>
     </row>
     <row r="12">
@@ -25544,22 +25544,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4470</v>
+        <v>9810</v>
       </c>
       <c r="M12" t="n">
-        <v>855</v>
+        <v>3534</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>570</v>
+        <v>1170</v>
       </c>
       <c r="P12" t="n">
-        <v>13260</v>
+        <v>15600</v>
       </c>
       <c r="Q12" t="n">
-        <v>3093.38</v>
+        <v>30327.3</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1740</v>
+        <v>6420</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>1140</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="P13" t="n">
-        <v>14340</v>
+        <v>15360</v>
       </c>
       <c r="Q13" t="n">
-        <v>892.48</v>
+        <v>8749.799999999999</v>
       </c>
     </row>
     <row r="14">
@@ -25650,10 +25650,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>510</v>
+        <v>3720</v>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -25662,10 +25662,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>23250</v>
+        <v>25050</v>
       </c>
       <c r="Q14" t="n">
-        <v>375.55</v>
+        <v>3681.9</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>270</v>
+        <v>1890</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>15870</v>
+        <v>23100</v>
       </c>
       <c r="Q15" t="n">
-        <v>170.75</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="16">
@@ -25756,10 +25756,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>870</v>
       </c>
       <c r="M16" t="n">
-        <v>570</v>
+        <v>660</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12120</v>
+        <v>9930</v>
       </c>
       <c r="Q16" t="n">
-        <v>121.27</v>
+        <v>1188.9</v>
       </c>
     </row>
     <row r="17">
@@ -25809,22 +25809,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>120</v>
+        <v>1860</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P17" t="n">
-        <v>22140</v>
+        <v>37890</v>
       </c>
       <c r="Q17" t="n">
-        <v>121.64</v>
+        <v>1192.5</v>
       </c>
     </row>
     <row r="18">
@@ -25865,7 +25865,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>600</v>
+        <v>3510</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.96</v>
+        <v>146.7</v>
       </c>
     </row>
     <row r="19">
@@ -25918,7 +25918,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -25930,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.24</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="20">
@@ -25971,7 +25971,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25983,7 +25983,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.19</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="21">
@@ -26024,7 +26024,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.78</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="22">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>47339640</v>
+        <v>52449120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>1092898.45</v>
       </c>
       <c r="L5" t="n">
-        <v>10181052</v>
+        <v>10108476</v>
       </c>
       <c r="M5" t="n">
-        <v>74130</v>
+        <v>165060</v>
       </c>
       <c r="N5" t="n">
-        <v>11730</v>
+        <v>19737</v>
       </c>
       <c r="O5" t="n">
-        <v>209610</v>
+        <v>218790</v>
       </c>
       <c r="P5" t="n">
-        <v>6552</v>
+        <v>4407</v>
       </c>
       <c r="Q5" t="n">
-        <v>897063.17</v>
+        <v>8794737</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>279855</v>
       </c>
       <c r="H6" t="n">
-        <v>10526760</v>
+        <v>12281220</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -26518,22 +26518,22 @@
         <v>1403219.84</v>
       </c>
       <c r="L6" t="n">
-        <v>17308674</v>
+        <v>17974008</v>
       </c>
       <c r="M6" t="n">
-        <v>136920</v>
+        <v>431760</v>
       </c>
       <c r="N6" t="n">
-        <v>8925</v>
+        <v>18615</v>
       </c>
       <c r="O6" t="n">
-        <v>957525</v>
+        <v>1083750</v>
       </c>
       <c r="P6" t="n">
-        <v>65812.5</v>
+        <v>51772.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>13733509.5</v>
+        <v>134642250</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>667278</v>
       </c>
       <c r="H7" t="n">
-        <v>2496600</v>
+        <v>3245580</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -26571,22 +26571,22 @@
         <v>1765787.5</v>
       </c>
       <c r="L7" t="n">
-        <v>21801960</v>
+        <v>23904720</v>
       </c>
       <c r="M7" t="n">
-        <v>448350</v>
+        <v>1492050</v>
       </c>
       <c r="N7" t="n">
-        <v>2142</v>
+        <v>4641</v>
       </c>
       <c r="O7" t="n">
-        <v>1335180</v>
+        <v>1270920</v>
       </c>
       <c r="P7" t="n">
-        <v>156487.5</v>
+        <v>100912.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>15127303.39</v>
+        <v>148306896</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>2517723</v>
       </c>
       <c r="H8" t="n">
-        <v>1308150</v>
+        <v>2180250</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>1215065.34</v>
       </c>
       <c r="L8" t="n">
-        <v>17042130</v>
+        <v>19254348</v>
       </c>
       <c r="M8" t="n">
-        <v>872025</v>
+        <v>2044350</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1388475</v>
+        <v>1982880</v>
       </c>
       <c r="P8" t="n">
-        <v>342342</v>
+        <v>176358</v>
       </c>
       <c r="Q8" t="n">
-        <v>15297296.8</v>
+        <v>149973498</v>
       </c>
     </row>
     <row r="9">
@@ -26677,22 +26677,22 @@
         <v>935771.23</v>
       </c>
       <c r="L9" t="n">
-        <v>12549006</v>
+        <v>14565420</v>
       </c>
       <c r="M9" t="n">
-        <v>720300</v>
+        <v>1514100</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>695640</v>
+        <v>1371645</v>
       </c>
       <c r="P9" t="n">
-        <v>476775</v>
+        <v>368550</v>
       </c>
       <c r="Q9" t="n">
-        <v>10914564.12</v>
+        <v>107005530.6</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>934740</v>
       </c>
       <c r="H10" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>211218.6</v>
       </c>
       <c r="L10" t="n">
-        <v>7612704</v>
+        <v>9895554</v>
       </c>
       <c r="M10" t="n">
-        <v>562275</v>
+        <v>1570800</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>481950</v>
+        <v>1392300</v>
       </c>
       <c r="P10" t="n">
-        <v>803887.5</v>
+        <v>759135</v>
       </c>
       <c r="Q10" t="n">
-        <v>6835262.76</v>
+        <v>67012380</v>
       </c>
     </row>
     <row r="11">
@@ -26783,22 +26783,22 @@
         <v>43627.57</v>
       </c>
       <c r="L11" t="n">
-        <v>3553200</v>
+        <v>5032800</v>
       </c>
       <c r="M11" t="n">
-        <v>784350</v>
+        <v>1625400</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>554880</v>
+        <v>650250</v>
       </c>
       <c r="P11" t="n">
-        <v>796770</v>
+        <v>726570</v>
       </c>
       <c r="Q11" t="n">
-        <v>4226784.12</v>
+        <v>41439060</v>
       </c>
     </row>
     <row r="12">
@@ -26836,22 +26836,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>804600</v>
+        <v>1765800</v>
       </c>
       <c r="M12" t="n">
-        <v>299250</v>
+        <v>1236900</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>96900</v>
+        <v>198900</v>
       </c>
       <c r="P12" t="n">
-        <v>861900</v>
+        <v>1014000</v>
       </c>
       <c r="Q12" t="n">
-        <v>1856030.76</v>
+        <v>18196380</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>313200</v>
+        <v>1155600</v>
       </c>
       <c r="M13" t="n">
-        <v>31500</v>
+        <v>399000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>15300</v>
+        <v>45900</v>
       </c>
       <c r="P13" t="n">
-        <v>932100</v>
+        <v>998400</v>
       </c>
       <c r="Q13" t="n">
-        <v>535487.76</v>
+        <v>5249880</v>
       </c>
     </row>
     <row r="14">
@@ -26942,10 +26942,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>91800</v>
+        <v>669600</v>
       </c>
       <c r="M14" t="n">
-        <v>10500</v>
+        <v>252000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -26954,10 +26954,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1511250</v>
+        <v>1628250</v>
       </c>
       <c r="Q14" t="n">
-        <v>225332.28</v>
+        <v>2209140</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>48600</v>
+        <v>340200</v>
       </c>
       <c r="M15" t="n">
-        <v>31500</v>
+        <v>21000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P15" t="n">
-        <v>1031550</v>
+        <v>1501500</v>
       </c>
       <c r="Q15" t="n">
-        <v>102448.8</v>
+        <v>1004400</v>
       </c>
     </row>
     <row r="16">
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10800</v>
+        <v>156600</v>
       </c>
       <c r="M16" t="n">
-        <v>199500</v>
+        <v>231000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -27060,10 +27060,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>787800</v>
+        <v>645450</v>
       </c>
       <c r="Q16" t="n">
-        <v>72760.67999999999</v>
+        <v>713340</v>
       </c>
     </row>
     <row r="17">
@@ -27101,22 +27101,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>21600</v>
+        <v>334800</v>
       </c>
       <c r="M17" t="n">
-        <v>42000</v>
+        <v>10500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P17" t="n">
-        <v>1439100</v>
+        <v>2462850</v>
       </c>
       <c r="Q17" t="n">
-        <v>72981</v>
+        <v>715500</v>
       </c>
     </row>
     <row r="18">
@@ -27157,7 +27157,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>42000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27166,10 +27166,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>39000</v>
+        <v>228150</v>
       </c>
       <c r="Q18" t="n">
-        <v>8978.040000000001</v>
+        <v>88020</v>
       </c>
     </row>
     <row r="19">
@@ -27210,7 +27210,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -27222,7 +27222,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3745.44</v>
+        <v>36720</v>
       </c>
     </row>
     <row r="20">
@@ -27263,7 +27263,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27275,7 +27275,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>716.04</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="21">
@@ -27316,7 +27316,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>52500</v>
+        <v>105000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -27328,7 +27328,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3470.04</v>
+        <v>34020</v>
       </c>
     </row>
     <row r="22">
@@ -27692,7 +27692,7 @@
         <v>130440</v>
       </c>
       <c r="H4" t="n">
-        <v>28080</v>
+        <v>29310</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -27704,7 +27704,7 @@
         <v>70</v>
       </c>
       <c r="L4" t="n">
-        <v>358890</v>
+        <v>408240</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>77220</v>
+        <v>79770</v>
       </c>
       <c r="P4" t="n">
-        <v>660</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>38172.81</v>
+        <v>531520.11</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>75900</v>
       </c>
       <c r="H5" t="n">
-        <v>25470</v>
+        <v>26310</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>166680</v>
+        <v>180210</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>48180</v>
+        <v>50700</v>
       </c>
       <c r="P5" t="n">
-        <v>2310</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>15402.04</v>
+        <v>214458.75</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>29280</v>
       </c>
       <c r="H6" t="n">
-        <v>4860</v>
+        <v>5490</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>64350</v>
+        <v>71460</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>23130</v>
+        <v>29070</v>
       </c>
       <c r="P6" t="n">
-        <v>2460</v>
+        <v>120</v>
       </c>
       <c r="Q6" t="n">
-        <v>5912.89</v>
+        <v>82331.37</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>600</v>
+        <v>960</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9030</v>
+        <v>11640</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8400</v>
+        <v>11970</v>
       </c>
       <c r="P7" t="n">
-        <v>4590</v>
+        <v>540</v>
       </c>
       <c r="Q7" t="n">
-        <v>360.76</v>
+        <v>5023.26</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>330</v>
       </c>
       <c r="H8" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2910</v>
+        <v>4650</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2970</v>
+        <v>9690</v>
       </c>
       <c r="P8" t="n">
-        <v>5130</v>
+        <v>2310</v>
       </c>
       <c r="Q8" t="n">
-        <v>63.56</v>
+        <v>885.0599999999999</v>
       </c>
     </row>
     <row r="9">
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>690</v>
+        <v>2190</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>780</v>
+        <v>3750</v>
       </c>
       <c r="P9" t="n">
-        <v>6300</v>
+        <v>8400</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.4</v>
+        <v>311.85</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>270</v>
+        <v>1920</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="P10" t="n">
-        <v>3240</v>
+        <v>7770</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.11</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28087,10 +28087,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2040</v>
+        <v>6270</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.92</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="12">
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>570</v>
+        <v>2220</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="13">
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,7 +28193,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>9169.200000000001</v>
+        <v>9471.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>13.24</v>
       </c>
       <c r="L5" t="n">
-        <v>35002.8</v>
+        <v>37844.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2409</v>
+        <v>2535</v>
       </c>
       <c r="P5" t="n">
-        <v>46.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>770.1</v>
+        <v>10722.94</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>1464</v>
       </c>
       <c r="H6" t="n">
-        <v>2770.2</v>
+        <v>3129.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>23809.5</v>
+        <v>26440.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5782.5</v>
+        <v>7267.5</v>
       </c>
       <c r="P6" t="n">
-        <v>369</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="n">
-        <v>4434.67</v>
+        <v>61748.53</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>148.5</v>
       </c>
       <c r="H7" t="n">
-        <v>438</v>
+        <v>700.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5418</v>
+        <v>6984</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2940</v>
+        <v>4189.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1147.5</v>
+        <v>135</v>
       </c>
       <c r="Q7" t="n">
-        <v>288.61</v>
+        <v>4018.61</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>214.5</v>
       </c>
       <c r="H8" t="n">
-        <v>229.5</v>
+        <v>280.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2066.1</v>
+        <v>3301.5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1336.5</v>
+        <v>4360.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1949.4</v>
+        <v>877.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>60.39</v>
+        <v>840.8099999999999</v>
       </c>
     </row>
     <row r="9">
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>558.9</v>
+        <v>1773.9</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>429</v>
+        <v>2062.5</v>
       </c>
       <c r="P9" t="n">
-        <v>3150</v>
+        <v>4200</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.72</v>
+        <v>302.49</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>240.3</v>
+        <v>1708.8</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="P10" t="n">
-        <v>2754</v>
+        <v>6604.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.11</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29379,10 +29379,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1836</v>
+        <v>5643</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.92</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="12">
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>570</v>
+        <v>2220</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="13">
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,7 +29485,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>52264440</v>
+        <v>53988120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>642881.4399999999</v>
       </c>
       <c r="L5" t="n">
-        <v>6300504</v>
+        <v>6811938</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>409530</v>
+        <v>430950</v>
       </c>
       <c r="P5" t="n">
-        <v>3003</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>462061.13</v>
+        <v>6433762.5</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>79056</v>
       </c>
       <c r="H6" t="n">
-        <v>15790140</v>
+        <v>17837010</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>172325.24</v>
       </c>
       <c r="L6" t="n">
-        <v>4285710</v>
+        <v>4759236</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>983025</v>
+        <v>1235475</v>
       </c>
       <c r="P6" t="n">
-        <v>23985</v>
+        <v>1170</v>
       </c>
       <c r="Q6" t="n">
-        <v>2660800.18</v>
+        <v>37049116.5</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>8019</v>
       </c>
       <c r="H7" t="n">
-        <v>2496600</v>
+        <v>3994560</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>975240</v>
+        <v>1257120</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>499800</v>
+        <v>712215</v>
       </c>
       <c r="P7" t="n">
-        <v>74587.5</v>
+        <v>8775</v>
       </c>
       <c r="Q7" t="n">
-        <v>173165.47</v>
+        <v>2411164.8</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>11583</v>
       </c>
       <c r="H8" t="n">
-        <v>1308150</v>
+        <v>1598850</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>371898</v>
+        <v>594270</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>227205</v>
+        <v>741285</v>
       </c>
       <c r="P8" t="n">
-        <v>126711</v>
+        <v>57057</v>
       </c>
       <c r="Q8" t="n">
-        <v>36231.14</v>
+        <v>504484.2</v>
       </c>
     </row>
     <row r="9">
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>100602</v>
+        <v>319302</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>72930</v>
+        <v>350625</v>
       </c>
       <c r="P9" t="n">
-        <v>204750</v>
+        <v>273000</v>
       </c>
       <c r="Q9" t="n">
-        <v>13034.76</v>
+        <v>181496.7</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1197000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>43254</v>
+        <v>307584</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>42840</v>
       </c>
       <c r="P10" t="n">
-        <v>179010</v>
+        <v>429292.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3668.76</v>
+        <v>51084</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>1368000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>221400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30671,10 +30671,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>119340</v>
+        <v>366795</v>
       </c>
       <c r="Q11" t="n">
-        <v>554.58</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="12">
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>91800</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>37050</v>
+        <v>144300</v>
       </c>
       <c r="Q12" t="n">
-        <v>127.98</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="13">
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,7 +30777,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5850</v>
+        <v>29250</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
